--- a/data/femverse_pregnancy_analytics_events.xlsx
+++ b/data/femverse_pregnancy_analytics_events.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emaan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emaan\events-retrieval-system\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1A4DA3-A051-448B-A86F-2142D8F99051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CC6895-99E1-48E4-A143-68A956505C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1727,367 +1727,367 @@
     <t>Detailed Event Description</t>
   </si>
   <si>
-    <t>The preg_dashboard_screen_shown event fires every single time the Pregnancy Dashboard screen, also referred to as the Week Home screen, becomes visible to the user. This includes the very first time a pregnant user lands on the dashboard after completing onboarding, every subsequent return visit when the user opens the app, arrivals via push notifications, deep links, and back navigation from child screens such as the week details or kick counter screens. The event captures the source_screen parameter indicating where the user came from (home tab, a notification, or a deep link), the current week_number and trimester of the pregnancy, the gestational_age in a weeks-and-days format like 12w3d, and a boolean is_first_time flag that distinguishes a brand-new user's inaugural dashboard view from all later visits. From a business perspective, this is a key event because it represents the primary entry point and engagement surface for the entire pregnancy module. Tracking how often the dashboard is shown answers questions like: How many daily and weekly active pregnant users does the app serve? What is the retention curve for pregnancy users across trimesters? Which traffic sources (organic open, notification, deep link) drive the most dashboard views? Are first-trimester users returning as frequently as third-trimester users? Product managers can use source_screen breakdowns to evaluate the effectiveness of push notification campaigns and deep-link strategies. The is_first_time flag enables cohort analysis of new pregnancy users versus returning ones, directly informing onboarding optimization. All users who have entered the pregnancy tracking mode will trigger this event, including users who are still setting up their pregnancy profile if the dashboard screen is shown to them. Synonyms and related concepts include pregnancy home screen, week home, pregnancy landing page, pregnancy main view, dashboard impression, pregnancy module entry, maternity tracker home. Related events that typically fire around this one include preg_dashboard_loading_shown and preg_dashboard_content_loaded which track the loading sequence immediately after the screen appears, preg_dashboard_screen_exited which marks the end of a dashboard session, and preg_week_transition_occurred which may fire on the same app open if the user's pregnancy has advanced to a new week since their last visit.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_screen_exited event fires the moment a user leaves the Pregnancy Dashboard screen, regardless of how they leave. This includes tapping the back button, navigating to another screen within the app such as the week details or kick counter, or backgrounding the app entirely. The event records the exit_method parameter which distinguishes between a deliberate back tap, an in-app navigation action, and the app going to the background, along with the time_spent_seconds parameter that captures exactly how long the user was on the dashboard before leaving. This event is not marked as a key event but is analytically critical for understanding session depth and engagement quality. By pairing it with preg_dashboard_screen_shown, analysts can compute per-visit dwell time on the dashboard, identify whether users are quickly bouncing or spending meaningful time engaging with content cards, and determine which exit methods are most common. If the majority of exits happen via app_background after only a few seconds, it may indicate the dashboard content is not compelling enough to hold attention. If most exits are navigations to child screens like week details or kick counter, that signals healthy deeper engagement. Product teams can use this data to answer questions such as: What is the average time spent on the dashboard? Do users who spend more time on the dashboard have higher feature adoption rates? Is there a correlation between trimester and time spent? All pregnant users who view the dashboard will trigger this event upon leaving it. Synonyms and related concepts include dashboard exit, screen leave, session end, time on screen, bounce, engagement duration, screen departure. The event fires after preg_dashboard_screen_shown and potentially after various card view and tap events, and before whatever screen the user navigates to next such as preg_week_details_screen_shown or preg_kick_counter_screen_shown.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_loading_shown event fires when the pregnancy dashboard displays a loading state to the user, typically a spinner or skeleton screen, while content is being fetched from the server. This event fires every time the dashboard needs to load or reload content, including on first visit, on return visits where cached data has expired, and on pull-to-refresh actions. It captures only the source_screen parameter. From a business and performance perspective, this event is important for measuring perceived app speed and identifying loading friction. By tracking how often users see a loading state and pairing this event with preg_dashboard_content_loaded, engineers and product managers can calculate actual load times and monitor for performance regressions. If the loading state is shown too frequently or for too long, it degrades the user experience and may contribute to churn, particularly for pregnant users who rely on the app daily. Key questions this event helps answer include: What percentage of dashboard visits show a loading state? Is the loading frequency increasing over time, suggesting backend degradation? Are users on certain networks or devices seeing loading states more often? All pregnant users who access the dashboard may trigger this event, though users with strong network connections and warm caches may skip it entirely. Synonyms and related concepts include loading spinner, skeleton screen, content loading, dashboard fetch, loading indicator, buffering state, content pending. This event fires between preg_dashboard_screen_shown and preg_dashboard_content_loaded in the screen rendering sequence.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_content_loaded event fires when the pregnancy dashboard has finished fetching all content from the server and has fully rendered it for the user to see and interact with. The event captures load_time_ms indicating how many milliseconds the content took to load, the current week_number, and cards_count showing how many dashboard content cards were rendered. This event is the counterpart to preg_dashboard_loading_shown and together they bracket the loading experience. From a technical performance standpoint, load_time_ms is one of the most actionable metrics the analytics team can track: it directly correlates with user satisfaction and retention. Product and engineering teams use this to answer questions like: What is the P50, P90, and P99 load time for the dashboard? Are load times degrading after a specific release? Do users in later pregnancy weeks experience slower loads because more content cards are served? Does cards_count affect load time linearly? If load_time_ms consistently exceeds acceptable thresholds (say, 2000ms), it becomes a prioritized engineering task. The cards_count parameter also helps the content team understand how much content is being served per week and whether certain weeks feel sparse or overloaded. All pregnant users trigger this event upon successful content load. Synonyms and related concepts include content render, page load complete, time to interactive, dashboard ready, content fetch complete, rendering finished, first meaningful paint. This event fires after preg_dashboard_loading_shown and before any user interaction events like preg_dashboard_scroll_depth or card tap events.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_scroll_depth event fires when the user scrolls the pregnancy dashboard to specific milestone thresholds, specifically at 25 percent, 50 percent, 75 percent, and 100 percent of the total scrollable content. Each threshold fires the event once per session, meaning a user who scrolls to 75 percent depth will trigger the event three times (at 25, 50, and 75 percent). The event captures scroll_percent and the current week_number. This is a standard engagement measurement pattern used to understand how much of the dashboard content users actually consume. It answers business questions such as: Do most users only see the top portion of the dashboard, suggesting that content below the fold is being wasted? Does scroll depth vary by trimester or week? Are users in their third trimester more or less likely to scroll through the entire dashboard compared to first-trimester users? If the drop-off between 25 and 50 percent is steep, the content team should consider reordering cards to place the most valuable ones higher. If 100 percent scroll depth is rare, elements placed at the bottom of the dashboard like the AI chatbot prompt or health checker card may need to be repositioned. All pregnant users who scroll on the dashboard will trigger this event. Users who view the dashboard but do not scroll will not trigger it at all. Synonyms and related concepts include scroll tracking, content consumption, fold analysis, scroll percentage, viewport depth, content exposure, page depth, engagement depth. This event fires after preg_dashboard_content_loaded and alongside various card_viewed events as the user scrolls through the dashboard.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_baby_card_viewed event fires when the baby illustration card enters the visible viewport on the pregnancy dashboard. This is an impression-based event triggered by the card becoming visible through scrolling or initial page render, not by the user tapping on it. It captures the current week_number and the position of the card in the dashboard layout. The business purpose of this event is to measure the visibility and reach of one of the most emotionally resonant elements of the pregnancy experience: the weekly baby illustration. This card is a key differentiator for the app and drives emotional engagement and social sharing. Tracking how often it is seen helps the product team understand whether the card is positioned effectively on the dashboard. If the baby card has a high view rate but low tap-through to the week details or See Your Baby feature, the team might experiment with different call-to-action copy or card design. Conversely, if the card has a low view rate, it may be positioned too far down the dashboard scroll. This event is triggered by all pregnant users whose scrolling or initial dashboard render causes the baby card to be visible. Synonyms and related concepts include baby illustration impression, fetal development card view, baby image visibility, baby card exposure, weekly baby visual, fetal growth illustration, pregnancy illustration impression. Related events include preg_dashboard_see_baby_tap which fires when the user actually taps the card, and preg_dashboard_scroll_depth which contextualizes how far the user scrolled.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_trimester_viewed event fires when the trimester progress card becomes visible in the viewport on the pregnancy dashboard. This is a passive impression event, not a tap. It captures the current trimester being displayed and days_to_birth, which shows the remaining days until the estimated delivery date. The business value of this event lies in understanding how often users see the trimester progress card, which provides a high-level sense of pregnancy progression and is designed to build anticipation and keep users coming back. The days_to_birth parameter is particularly valuable for segmentation: analysts can compare engagement patterns between users with 200+ days remaining versus users nearing their due date. Key questions include: Is the trimester card consistently visible to users, or is it frequently below the fold and missed? Do users in the third trimester (with fewer days_to_birth) engage more with the dashboard overall? Can the days_to_birth metric be correlated with notification open rates or daily active usage? All pregnant users who scroll past or land on the portion of the dashboard containing the trimester card will trigger this event. Synonyms and related concepts include trimester progress impression, pregnancy progress card view, countdown card visibility, due date countdown impression, trimester tracker exposure, pregnancy milestone card view. The related tap event is preg_dashboard_trimester_tap, and this event often fires alongside other card_viewed events during dashboard scrolling.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_trimester_tap event fires when the user actively taps on the trimester progress card or its See More link on the pregnancy dashboard. This is an intentional user interaction, distinct from the passive preg_dashboard_trimester_viewed impression event. It captures the trimester displayed and the current week_number. Tapping the trimester card navigates the user to the trimester details screen where they can read articles and content about their current trimester. From a business perspective, this event measures interest in trimester-level educational content and is a key indicator of content engagement depth. A high tap rate relative to views suggests the trimester card design and copy effectively encourage exploration. A low tap rate might indicate the card preview already satisfies user curiosity or that the call-to-action is not compelling enough. Product teams can use this data to answer: What percentage of trimester card views convert to taps? Do first-trimester users tap more often than third-trimester users, perhaps because everything is new to them? Does the tap rate change after content updates? All pregnant users who see and interact with the trimester card can trigger this event. Synonyms and related concepts include trimester card click, trimester details navigation, trimester progress tap, pregnancy phase tap, trimester content entry, trimester CTA tap. This event fires after preg_dashboard_trimester_viewed and before preg_trimester_details_shown.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_log_symptoms_tap event fires when the user taps the Log Symptoms button on a pregnancy dashboard card. It captures the current week_number and the button_label parameter (which will be log_symptoms). This event represents a deliberate user intent to record how they are feeling, which is one of the core value propositions of a pregnancy tracking app. From a business standpoint, symptom logging is central to user engagement and data completeness. Tracking this tap event answers questions like: What percentage of dashboard sessions result in a symptom logging attempt? Which pregnancy weeks see the highest symptom logging intent? Is there a drop-off between tapping Log Symptoms and actually submitting a log (by comparing this event to preg_symptom_log_submitted)? Are users who log symptoms regularly retained longer than those who do not? If the tap rate is low, the product team might experiment with more prominent placement, different button copy, or contextual nudges like You haven't logged symptoms today. This event is triggered by any pregnant user who taps the log symptoms button on the dashboard. Synonyms and related concepts include symptom logging entry, log symptoms button click, symptom tracker CTA, health logging intent, symptom entry point, symptom recording tap. This event fires after the dashboard is loaded and before preg_symptom_log_screen_shown when the symptom logging screen appears.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_see_baby_tap event fires when the user taps the See Your Baby button on the pregnancy dashboard card. It captures the current week_number and the button_label parameter set to see_your_baby. This tap navigates the user to the week details screen where they can see a larger baby illustration, developmental information, and weekly insights. This event is a strong signal of emotional engagement because users who tap See Your Baby are actively curious about their baby's development for the current week. From a business perspective, this is one of the primary engagement funnels from the dashboard, and its tap rate is a leading indicator of how well the dashboard drives deeper content consumption. Questions this answers include: What is the week-over-week tap rate for See Your Baby? Do users tap this more in early pregnancy when everything is new, or later when anticipation builds? Does the tap rate correlate with the quality or novelty of the baby illustration for that week? Can improvements to the baby card design increase the tap-through rate to week details? All pregnant users who see the dashboard baby card and choose to tap it will trigger this event. Synonyms and related concepts include baby development tap, see baby button click, fetal view CTA, baby illustration tap, weekly baby details entry, baby card interaction. This event fires after preg_dashboard_baby_card_viewed and before preg_week_details_screen_shown.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_see_details_tap event fires when the user taps the See Details link on the main pregnancy dashboard card. It captures the current week_number. This link serves as a general entry point to expanded pregnancy information for the current week, likely navigating to the week details screen or a similar detailed view. The business purpose is to track how many users want more information beyond what the dashboard card preview shows. A high tap rate indicates that the summary content on the dashboard is intriguing enough to prompt further exploration, while a very low rate might suggest the dashboard card already provides sufficient information or that the See Details link is not visually prominent enough. Product managers can ask: How does the See Details tap rate compare to the See Your Baby tap rate? Are they cannibalizing each other, or do they serve different user intents? Does the tap rate vary by trimester? All pregnant users who interact with the main dashboard card's See Details link trigger this event. Synonyms and related concepts include view more tap, details link click, expand card tap, read more CTA, pregnancy details entry, card expansion tap. This event fires after the dashboard is loaded and typically before preg_week_details_screen_shown or a similar detail screen event.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_detail_card_tap event fires when the user taps on one of the pregnancy detail cards displayed in the horizontal carousel on the dashboard. These detail cards represent different feature entry points such as Log your symptoms, Weekly guide, and Checklist. The event captures the card_id identifying which card was tapped, the card_title with the display name, and the position of the card in the carousel. This event is critically important for understanding which features users gravitate toward from the dashboard. The carousel is a key navigation pattern, and the position parameter allows analysts to measure position bias: do cards in position 0 get disproportionately more taps simply because they are visible first? The card_id and card_title parameters enable feature-level funnel analysis. Questions this event answers include: Which detail cards get the most taps? Is the log_symptoms card tapped more than the checklist card? Should the carousel order be personalized based on user behavior? Does the tap rate for later-position cards increase if the user has already swiped through the carousel? All pregnant users who interact with the horizontal carousel trigger this event. Synonyms and related concepts include feature card tap, carousel item click, quick action tap, pregnancy feature entry, horizontal scroll card tap, dashboard shortcut tap. This event fires after preg_dashboard_detail_card_viewed and before whatever feature screen the tapped card leads to, such as preg_symptom_log_screen_shown.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_detail_card_viewed event fires when one of the pregnancy detail cards in the horizontal carousel becomes visible in the viewport, either through the initial dashboard render or as the user scrolls the carousel horizontally. It captures the card_id and the position of the card in the carousel. This is an impression-based event and is the prerequisite for measuring tap-through rates on detail cards. The business purpose is to understand content exposure within the carousel. If a card in position 3 is rarely viewed, it means most users never scroll the carousel far enough to see it. This has direct implications for content strategy: important features should not be buried in positions that users rarely reach. Analysts can calculate view-to-tap conversion rates for each card by comparing this event with preg_dashboard_detail_card_tap, and can identify which cards attract attention just by being seen versus which require active interest. All pregnant users who see the carousel area will trigger this event for at least the first card. Synonyms and related concepts include carousel card impression, feature card visibility, horizontal scroll card view, detail card exposure, carousel item impression, quick action card view. This event fires as the user scrolls the dashboard or the carousel, often alongside preg_dashboard_scroll_depth, and before preg_dashboard_detail_card_tap if the user interacts with the card.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_daily_tip_viewed event fires when a daily tip card is displayed within the ViewPager component on the pregnancy dashboard. The ViewPager is a swipeable container that rotates through multiple tips. The event captures tip_id uniquely identifying the specific tip content, the position of the tip in the pager (0, 1, 2, etc.), and the current week_number. This event tracks content exposure for the daily tip feature, which is designed to provide bite-sized, relevant pregnancy advice. The business purpose includes measuring which tips are actually seen by users, understanding whether users primarily see only the first tip (position 0) or actively swipe through multiple tips, and evaluating whether tip content resonates differently across pregnancy weeks. Key questions include: What is the average number of unique tips viewed per dashboard session? Do certain tip topics (identifiable via tip_id) correlate with higher engagement or symptom logging? Are tips being refreshed frequently enough, or are users seeing stale content? All pregnant users who see the daily tip section of the dashboard will trigger this event for at least the initially displayed tip. Synonyms and related concepts include daily tip impression, tip card view, pregnancy advice view, tip pager impression, daily advice visibility, tip of the day view, health tip exposure. This event pairs with preg_dashboard_daily_tip_swiped which tracks active navigation between tips.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_daily_tip_swiped event fires when the user swipes between daily tips in the ViewPager component on the pregnancy dashboard. It captures the swipe direction (left or right), the from_position (the tip position before the swipe), and the to_position (the tip position after the swipe). This event represents active engagement with the daily tip content, as opposed to the passive impression tracked by preg_dashboard_daily_tip_viewed. A user who swipes through multiple tips is demonstrating curiosity and content hunger, which is a positive engagement signal. From a business perspective, this event answers questions such as: What percentage of users who see the first tip swipe to see additional tips? Is swiping more common in certain trimesters when users may feel more anxious or curious? Do users tend to swipe in one direction only, suggesting they browse linearly, or do they swipe back and forth? If very few users swipe, the team might consider auto-rotating tips or adding visual indicators that more tips are available. All pregnant users who interact with the tip pager will trigger this event. Synonyms and related concepts include tip navigation, tip carousel swipe, daily advice scroll, tip pager interaction, tip card swipe, ViewPager gesture, tip browsing. This event fires after preg_dashboard_daily_tip_viewed and triggers additional preg_dashboard_daily_tip_viewed events for each newly visible tip.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_baby_size_tap event fires when the user taps on the baby approximate size comparison card on the pregnancy dashboard. This card displays a fun, relatable size analogy for the baby such as your baby is the size of a potato or avocado or watermelon. The event captures the baby_size analogy text and the current week_number. This feature is one of the most shareable and emotionally engaging elements of pregnancy apps, and tracking taps on it measures user delight and curiosity. From a business perspective, this event helps answer: Which size analogies generate the most engagement? Do users tap the size card more in certain weeks, perhaps when the analogy is particularly surprising or amusing? Can the tap rate be improved with better illustrations or more creative analogies? Is there a correlation between baby size card engagement and social sharing or app recommendation behavior? The baby size comparison is often a conversation starter among pregnant users and their partners, making it a potential viral growth lever. All pregnant users who see and tap the baby size card trigger this event. Synonyms and related concepts include fetal size comparison tap, baby size analogy click, fruit size tap, baby growth comparison interaction, size reference card tap, pregnancy size metaphor. This event fires after the card becomes visible on the dashboard and may lead to preg_week_details_screen_shown or a size detail view.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_checkup_card_tap event fires when the user taps on the Add your reports or Did you have a checkup card on the pregnancy dashboard. This card prompts users to log medical checkup information and upload health reports. The event captures the button_label parameter (typically add_reports). This is a medically significant engagement event because it represents the intersection of the app's tracking features with real-world prenatal care. From a business perspective, this event measures how effectively the app motivates users to keep their pregnancy health records within the platform, which increases data completeness, deepens the app's value proposition, and creates switching costs that improve retention. Key questions include: What percentage of dashboard sessions result in a checkup card tap? Does the tap rate increase around common prenatal checkup schedules (e.g., every 4 weeks in early pregnancy, weekly in the third trimester)? Are users who log checkups more retained than those who do not? Can push notifications timed around typical checkup schedules boost this tap rate? All pregnant users who see the checkup card can trigger this event. Synonyms and related concepts include checkup logging entry, medical report upload tap, prenatal visit card tap, health report CTA, doctor visit logging, checkup tracker entry, medical records tap. This event fires on the dashboard and leads to whatever report uploading or checkup logging screen follows.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_kick_counter_tap event fires when the user taps on the Kick Counter card on the pregnancy dashboard. It captures the current week_number, which is important because kick counting is typically recommended starting around week 28 of pregnancy. This event represents a user's intent to monitor fetal movement, which is one of the most clinically relevant self-monitoring activities during the third trimester. From a business perspective, the kick counter is a high-value feature that keeps third-trimester users engaged daily. Tracking this tap event answers questions like: What percentage of users in weeks 28+ use the kick counter? Does the kick counter card tap rate increase as the due date approaches? Are users who engage with the kick counter more likely to remain daily active users through the end of pregnancy? Is the card visible and compelling enough for third-trimester users, or should it be promoted more aggressively? The week_number parameter helps validate that the feature is primarily used in the appropriate gestational period and can flag if the card is being shown too early. This event is triggered primarily by users in their third trimester (week 28+), though any pregnant user could theoretically trigger it if the card is displayed. Synonyms and related concepts include kick tracker entry, fetal movement counter tap, baby kick monitor tap, kick count CTA, movement tracker entry, third trimester kick card. This event fires on the dashboard and leads directly to preg_kick_counter_screen_shown.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_health_checker_viewed event fires when the health checker or PCOS self-assessment card becomes visible in the viewport on the pregnancy dashboard. It captures the assessment_type parameter (such as pcos). This is a passive impression event indicating that the health assessment feature was exposed to the user. The business purpose is to measure the reach of the health checker feature card. Understanding how many users see this card is essential for calculating the conversion funnel from impression to tap to assessment completion. If the card has high visibility but low tap-through, the design or copy may need improvement. If it has low visibility, it may be positioned too far down the dashboard. The assessment_type parameter helps track which health assessments are being promoted. Questions this event answers include: What is the impression rate for the health checker card across the user base? Does the card's position on the dashboard affect its visibility? Are users in certain trimesters more likely to see this card based on their scrolling behavior? All pregnant users who scroll to or load the portion of the dashboard containing the health checker card will trigger this event. Synonyms and related concepts include health assessment card impression, PCOS checker visibility, health screening card view, self-assessment exposure, symptom checker card impression, health evaluation card view. This event fires during dashboard scrolling and is followed by preg_dashboard_health_checker_tap if the user interacts with it.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_health_checker_tap event fires when the user taps the Check your symptoms button on the health checker card on the pregnancy dashboard. It captures the assessment_type (e.g., pcos) and the button_label (e.g., check_your_symptoms). This is an active engagement event indicating the user wants to take a health self-assessment. From a business perspective, health assessment features are high-value both for user health outcomes and for product stickiness. Completing a health assessment provides personalized insights that make the app feel indispensable. Tracking this tap event answers questions like: What is the tap-through rate from health checker impressions? Do certain assessment types attract more interest? Are users who complete health assessments more retained? Can the assessment be cross-promoted at optimal times, such as when users report relevant symptoms? This event also has potential monetization implications if health assessments lead to premium feature upsells or partnership referrals (e.g., telemedicine). All pregnant users who see and tap the health checker card trigger this event. Synonyms and related concepts include health assessment tap, PCOS check tap, symptom checker CTA, health screening entry, self-assessment start tap, health evaluation tap. This event fires after preg_dashboard_health_checker_viewed and before the health assessment screen or flow begins.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_ai_chatbot_tap event fires when the user taps the AI chatbot floating icon on the pregnancy dashboard. It captures the current week_number. The floating icon is a persistent UI element overlaying the dashboard, providing quick access to an AI-powered pregnancy assistant. This event is significant because it represents the entry point into the app's AI features, which are likely a key differentiator and potentially a premium or monetized feature. From a business perspective, this event answers questions like: What percentage of dashboard sessions result in an AI chatbot interaction? Which pregnancy weeks drive the highest AI usage, indicating when users have the most questions? Is AI chatbot usage growing over time as users discover the feature? Do users who engage with the AI chatbot show higher satisfaction or retention? Can the floating icon's design or position be optimized to increase discovery? If the tap rate is low, the team might consider adding contextual triggers or onboarding tooltips to introduce the feature. All pregnant users who see the floating icon and tap it trigger this event. Synonyms and related concepts include AI assistant tap, chatbot entry, pregnancy AI tap, virtual assistant click, AI chat entry, pregnancy chatbot launch, floating action button tap. This event fires on the dashboard and leads to the AI chatbot conversation screen.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_ai_prompt_shown event fires when an AI prompt suggestion card is displayed on the pregnancy dashboard. This card contains pre-written prompt suggestions like What should I eat this week or Is this normal that the user can tap to quickly start an AI conversation. The event captures the prompt_text showing exactly which suggestion was displayed. The business purpose of this event is to measure the exposure of AI prompt suggestions, which serve as a discovery mechanism for the AI chatbot feature. By tracking which prompts are shown and pairing this data with preg_dashboard_ai_prompt_tap, the team can calculate prompt-level conversion rates and optimize the prompt library. Questions include: Which prompt suggestions are shown most frequently? Do certain prompts have higher tap-through rates, indicating they resonate with user needs? Should prompts be personalized based on the user's current pregnancy week or recently logged symptoms? Are AI prompts effective at driving chatbot adoption among users who haven't used the AI feature before? All pregnant users who see the prompt suggestion card on the dashboard trigger this event. Synonyms and related concepts include AI suggestion impression, chatbot prompt display, AI quick action view, suggested question shown, AI conversation starter view, prompt card impression. This event fires during dashboard viewing and is followed by preg_dashboard_ai_prompt_tap if the user interacts with it.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_ai_prompt_tap event fires when the user taps on one of the AI prompt suggestions displayed on the pregnancy dashboard. It captures the prompt_text showing exactly which prompt the user selected. This event represents a direct, low-friction entry into the AI chatbot experience, as the user does not need to formulate their own question. From a business perspective, this is a key engagement event for the AI feature because it lowers the barrier to adoption. Tracking which prompts get tapped most helps the content and AI teams understand what pregnant users are most curious or concerned about, which informs both the AI training data and the editorial content strategy. Key questions include: Which prompt texts have the highest tap rates? Do prompts about nutrition get more taps than prompts about symptoms? Can prompt performance data inform the creation of new content articles or features? Are users who enter the AI chatbot via prompts more likely to have longer or more satisfying conversations than those who use the floating icon? All pregnant users who see and tap an AI prompt trigger this event. Synonyms and related concepts include AI suggestion tap, chatbot quick start, AI prompt click, suggested question tap, AI conversation entry, prompt CTA tap. This event fires after preg_dashboard_ai_prompt_shown and before the AI chatbot screen loads with the selected prompt pre-filled.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_insight_card_tap event fires when the user taps the personalized pregnancy insight card on the main dashboard. It captures the card_type parameter which can indicate whether the insight is a pregnancy-related insight or a calendar-related insight. Personalized insight cards are dynamically generated based on the user's pregnancy stage, logged data, and other contextual factors, making them a key personalization touchpoint. From a business perspective, this event measures the effectiveness of the personalization engine. If the insight card has a high tap rate, the personalization is resonating with users. If the tap rate is low, the insights may not be relevant or compelling enough. Key questions include: What is the tap rate for different card_type values? Do pregnancy insights perform differently than calendar insights? Does the tap rate vary across trimesters or user cohorts? Can the insight generation algorithm be improved based on which insight types perform best? Are users who engage with personalized insights more retained than those who ignore them? All pregnant users who see and tap the insight card trigger this event. Synonyms and related concepts include personalized content tap, pregnancy insight click, tailored advice tap, custom card interaction, personalized recommendation tap, contextual insight engagement. This event fires on the dashboard and leads to whatever detailed view the insight card links to.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_calendar_card_tap event fires when the user taps the pregnancy calendar card in the personalized insight horizontal scroll section of the dashboard. This card provides a quick visual entry point to the pregnancy calendar feature. The event has no additional parameters beyond the standard source_screen. The business purpose is to measure interest in the calendar feature from the dashboard, which is one of several ways users can access the pregnancy calendar (alongside toolbar actions and other navigation paths). Tracking this tap helps answer: Is the calendar card an effective discovery mechanism for the calendar feature? What percentage of calendar views originate from this card versus other entry points? Should the calendar card be more prominently placed if it drives high engagement? All pregnant users who see and tap the calendar card in the insight scroll trigger this event. Synonyms and related concepts include calendar entry tap, pregnancy calendar shortcut, calendar card click, timeline card tap, pregnancy schedule card tap, calendar CTA. This event fires on the dashboard and leads to preg_calendar_preview_shown.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_prompt_shown event fires when the Do you want to track pregnancy prompt card is displayed to a user on the dashboard. This is a discovery and conversion prompt shown to users who have not yet entered pregnancy tracking mode. The event has no additional parameters beyond source_screen. From a business perspective, this event is critical for measuring the top of the pregnancy module's conversion funnel. It represents the moment the app surfaces the pregnancy tracking option to a user who may or may not be pregnant. Tracking this event answers: How many users are exposed to the pregnancy tracking prompt? What is the conversion rate from seeing the prompt to selecting an option? Is the prompt being shown to the right user segments? Should the prompt be shown more aggressively or at different times? This event is typically triggered by users who are in the period tracking mode or general app mode and happen to navigate to or be shown the pregnancy dashboard area. It may appear for new users during onboarding or for existing users being cross-promoted. Synonyms and related concepts include pregnancy prompt impression, tracking offer shown, pregnancy mode discovery, mode switch prompt, pregnancy onboarding prompt, pregnancy suggestion card. This event fires before preg_dashboard_prompt_option_tap and is part of the pregnancy onboarding funnel.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_prompt_option_tap event fires when the user selects an option on the Do you want to track pregnancy prompt card. It captures the option_selected parameter, which can be yes (user is pregnant and wants to track), no (user is not interested), or want_to_be (user wants to get pregnant). This is a key event because it represents a critical user segmentation decision that determines the user's entire subsequent app experience. From a business perspective, this is one of the highest-impact events in the pregnancy module because it is the gateway to pregnancy mode activation. The distribution of responses directly informs product strategy: a high yes rate validates the pregnancy module's market, a high want_to_be rate suggests opportunity for a fertility or trying-to-conceive feature, and a high no rate might indicate the prompt is being shown to the wrong audience. Key questions include: What is the conversion rate for each option? Do users who select want_to_be eventually come back and select yes? How does the option distribution vary by user demographics or acquisition source? Is the prompt wording optimal for conversion? All users who see the pregnancy tracking prompt and interact with it trigger this event, including users who may be in the period tracking mode or general mode. Synonyms and related concepts include pregnancy mode selection, tracking opt-in, pregnancy confirmation, mode choice, pregnancy intent signal, pregnancy onboarding decision, fertility intent indicator. This event fires after preg_dashboard_prompt_shown and before the appropriate onboarding flow begins (e.g., preg_period_or_pregnant_shown or preg_personalize_screen_shown for yes selections).</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_empty_state_shown event fires when the pregnancy dashboard displays an empty state, indicating that the user has not completed pregnancy setup. This typically means the user entered the pregnancy section but has not yet provided their due date or last menstrual period information. The event has no additional parameters beyond source_screen. From a business perspective, this event identifies a critical drop-off point in the pregnancy onboarding funnel. Users who see the empty state have expressed some interest in pregnancy tracking but have not completed the necessary setup. Tracking this event answers: How many users reach the pregnancy dashboard without completing setup? Is the empty state design compelling enough to encourage completion? What is the conversion rate from empty state to setup completion? Is there a user segment that repeatedly sees the empty state without converting? The empty state screen is an opportunity to nudge users with clear instructions and an inviting call-to-action. All users who navigate to the pregnancy dashboard without a completed pregnancy profile will trigger this event. Synonyms and related concepts include pregnancy setup incomplete, onboarding not finished, empty dashboard, pregnancy not configured, setup required state, blank pregnancy screen, unconfigured pregnancy view. This event fires when the dashboard loads and is typically followed by preg_dashboard_empty_add_tap if the user decides to begin setup.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_empty_add_tap event fires when the user taps the add button on the pregnancy empty state card, initiating the pregnancy setup flow. The event has no additional parameters beyond source_screen. This is a crucial conversion event in the pregnancy onboarding funnel because it marks the transition from passive browsing of the empty state to active engagement with the setup process. From a business perspective, this event measures the effectiveness of the empty state's call-to-action design. The conversion rate from preg_dashboard_empty_state_shown to this tap event directly reflects how well the empty state communicates the value of setting up pregnancy tracking. Key questions include: What percentage of users who see the empty state tap the add button? How quickly after seeing the empty state do they tap? Does the tap rate improve with A/B testing different empty state designs or copy? Are there users who see the empty state multiple times before tapping? All users who see the pregnancy empty state and tap the add button trigger this event. Synonyms and related concepts include pregnancy setup start, begin tracking tap, add pregnancy tap, start pregnancy tracking, configure pregnancy tap, setup initiation, onboarding start tap. This event fires after preg_dashboard_empty_state_shown and before the pregnancy setup flow begins, likely leading to preg_period_or_pregnant_shown or preg_due_date_method_shown.</t>
-  </si>
-  <si>
-    <t>The preg_dashboard_milestone_viewed event fires when a pregnancy milestone card becomes visible to the user, either on the pregnancy dashboard or the calendar preview screen. It captures milestone_type (e.g., milestone) and milestone_title (e.g., First trimester complete or Anatomy scan). Milestones are significant moments in the pregnancy journey that the app highlights to keep users engaged and informed. From a business perspective, this event measures the visibility and reach of milestone content, which is designed to create anticipation, celebrate progress, and drive ongoing engagement. Milestones serve as emotional anchors that keep users coming back to the app. Key questions include: Which milestones are most frequently viewed? Are milestone views correlated with spikes in daily active usage? Do users who see milestones have higher retention rates? Should the app send push notifications when milestones are approaching? Can milestones be used as triggers for upsells or premium content? All pregnant users who scroll to a position where a milestone card is visible will trigger this event. Synonyms and related concepts include pregnancy milestone impression, milestone card view, pregnancy achievement view, progress milestone visibility, pregnancy landmark card, developmental milestone exposure, pregnancy checkpoint view. Related events include milestone-specific navigation events and preg_dashboard_scroll_depth for context on how the user reached the milestone card.</t>
-  </si>
-  <si>
-    <t>The preg_period_or_pregnant_shown event fires when the screen asking Do you get your period regularly or are you currently pregnant is displayed to the user. This is a key branching screen in the onboarding or mode-switching flow that determines whether the user enters period tracking or pregnancy tracking mode. The event captures the source_screen, which can be onboarding for new users or home for existing users switching modes. From a business perspective, this event marks the top of the pregnancy-specific onboarding funnel for users who have been identified as potentially pregnant or interested in pregnancy tracking. Measuring how many users reach this screen versus how many proceed to select an option (preg_period_or_pregnant_option_tap) reveals the drop-off rate at this critical decision point. Key questions include: How many users reach this screen from onboarding versus from the home screen? Is the screen's design clear enough that users don't abandon the flow? Do users who arrive from different sources have different completion rates? This event is triggered by new users going through initial app setup and by existing users who are switching from period tracking to pregnancy tracking or exploring the pregnancy option. Synonyms and related concepts include pregnancy or period screen, mode selection screen, pregnancy detection screen, menstrual status screen, onboarding branch point, pregnancy eligibility screen, reproductive status question. This event fires before preg_period_or_pregnant_option_tap and is part of the early onboarding sequence.</t>
-  </si>
-  <si>
-    <t>The preg_period_or_pregnant_option_tap event fires when the user selects one of the options on the period or pregnant screen, such as regular_period, pregnant, or irregular. It captures the option_selected value and the position of the selected item. This is a key event because the user's selection fundamentally changes their app experience. Selecting pregnant routes them into the pregnancy tracking module, regular_period keeps them in standard cycle tracking, and irregular may lead to additional assessment screens. From a business perspective, this is a critical segmentation event. The distribution of selections tells the business what percentage of their user base is pregnant, has regular periods, or has irregular cycles, which informs product roadmap prioritization, content strategy, and partnership opportunities (e.g., fertility clinics for irregular cycle users). Key questions include: What percentage of users who reach this screen select pregnant? Is the pregnant option selected more by users from certain acquisition channels? Do users who select irregular eventually switch to pregnant mode later? What is the abandonment rate at this step? This event is triggered by any user who sees the period-or-pregnant screen and makes a selection. Synonyms and related concepts include reproductive status selection, pregnancy confirmation, period status option, mode selection tap, onboarding branch decision, menstrual status choice, pregnancy opt-in. This event fires after preg_period_or_pregnant_shown and before the next onboarding step such as preg_personalize_screen_shown for pregnant users.</t>
-  </si>
-  <si>
-    <t>The preg_personalize_screen_shown event fires when the Personalize your journey screen is displayed during the pregnancy onboarding flow. This screen appears after the user has indicated they are pregnant and is about to set up their specific pregnancy parameters. The event captures the source_screen, typically preg_period_or_pregnant indicating it follows the initial status selection. From a business perspective, this event marks a user who has committed to pregnancy tracking and is now in the personalization phase. The conversion rate through this screen is important because drop-offs here mean the user wanted to track their pregnancy but found the setup process too demanding or confusing. Key questions include: What is the completion rate for this screen? How long do users spend on it? Do users drop off at this point, and if so, can the flow be simplified? Is the personalization messaging resonating with users? This event is triggered by users who have selected pregnant on the period-or-pregnant screen and are proceeding through the pregnancy onboarding flow. Synonyms and related concepts include pregnancy personalization, journey customization screen, pregnancy setup screen, onboarding personalization, pregnancy profile setup, customize pregnancy view. This event fires after preg_period_or_pregnant_option_tap (with pregnant selected) and before preg_due_date_method_shown.</t>
-  </si>
-  <si>
-    <t>The preg_due_date_method_shown event fires when the screen asking the user to choose their due date calculation method is displayed. Users can choose between LMP (last menstrual period), EDD (estimated due date from a doctor), IVF (in vitro fertilization transfer date), or other methods. The event captures the source_screen, which may be preg_personalize during initial onboarding or preg_settings if the user is updating their method later. This screen is a pivotal step in the pregnancy setup because the due date calculation method determines the accuracy of all week-by-week content, milestone timing, and countdown calculations throughout the pregnancy. From a business perspective, this event tracks the reach of the due date selection step, and the source_screen parameter distinguishes first-time setup from subsequent adjustments. Key questions include: What percentage of users who reach this screen complete the selection? Do users who come from settings (updating their method) change to a different method, suggesting initial confusion? Which calculation methods are most popular? Is the screen design clear enough for users who may not know their LMP? This event is triggered by users in the pregnancy onboarding flow and by existing pregnant users updating their settings. Synonyms and related concepts include due date calculation screen, EDD method selection, gestational age input method, due date setup screen, pregnancy date configuration, due date calculation choice. This event fires after preg_personalize_screen_shown (in onboarding) and before preg_due_date_method_selected.</t>
-  </si>
-  <si>
-    <t>The preg_due_date_method_selected event fires when the user selects a specific due date calculation method such as LMP, EDD, or IVF on the method selection screen. It captures the method chosen and the position of the selected item in the list. This is a key event because it determines how the app will calculate the user's pregnancy timeline, which affects all subsequent week-by-week content, milestones, and the estimated delivery date displayed throughout the app. From a business perspective, the distribution of method selections provides insight into the user base's pregnancy characteristics. A high LMP rate suggests most users are calculating from their period, while a high EDD rate means many have already had a doctor's confirmation. An IVF selection rate, even if small, indicates the app serves assisted reproduction users, which is a distinct and valuable segment. Key questions include: What is the distribution of method selections? Do certain methods correlate with better engagement or retention, possibly because they lead to more accurate dating? Do users who select IVF have different feature usage patterns? Can the app provide guidance to users who are unsure which method to choose? This event is triggered by users actively making a selection on the due date method screen. Synonyms and related concepts include due date method choice, EDD calculation selection, pregnancy dating method, gestational age method, LMP selection, IVF date method, due date input type. This event fires after preg_due_date_method_shown and before the corresponding date input screen such as preg_lmp_date_screen_shown or preg_edd_date_screen_shown.</t>
-  </si>
-  <si>
-    <t>The preg_lmp_date_screen_shown event fires when the LMP (last menstrual period) date calendar selection screen is displayed to the user. This screen presents a calendar interface where the user can select the first day of their last period. The event captures the source_screen, typically preg_due_date_method indicating it follows the method selection step. From a business perspective, this is a critical onboarding screen because the LMP date is the foundation for all pregnancy timeline calculations when the LMP method is selected. Users who abandon this screen without selecting a date will not complete pregnancy setup. Key questions include: What percentage of users who chose the LMP method reach this screen? What is the abandonment rate on this screen? Do users find the calendar interface intuitive, or do they struggle with date selection? Are there common patterns in how far back users need to scroll the calendar (indicating how far along they are when they start using the app)? This event is triggered by users who selected the LMP method and are now being asked to provide their LMP date. Synonyms and related concepts include LMP date picker, last period date screen, menstrual date calendar, period date input, LMP calendar view, last menstrual period entry, cycle start date screen. This event fires after preg_due_date_method_selected (with lmp method) and before preg_lmp_date_selected.</t>
-  </si>
-  <si>
-    <t>The preg_lmp_date_selected event fires when the user selects a specific date on the LMP calendar screen. It captures the selected_date in a standard date format. This is a key event because it provides the foundational data point for the entire pregnancy timeline when the LMP method is used. The selected date will be used to calculate the estimated due date, current pregnancy week, trimester, and all milestone timing. From a business perspective, the distribution of LMP dates reveals how early or late in pregnancy users typically start using the app. If most users select dates indicating they are already in the second trimester, it suggests the app is not capturing users early enough, and earlier marketing or acquisition strategies might be beneficial. Key questions include: At what pregnancy week do most users start tracking? Is there a spike in new user signups at any particular gestational age? Do users who start tracking earlier (first trimester) show better long-term retention? Are there date selection patterns that suggest users are guessing or unsure of their LMP? All users who interact with the LMP date calendar and select a date trigger this event. Synonyms and related concepts include LMP date entry, last period date selection, menstrual date confirmation, period date chosen, LMP calendar selection, last period input. This event fires after preg_lmp_date_screen_shown and is typically followed by the completion of onboarding or navigation to the pregnancy dashboard.</t>
-  </si>
-  <si>
-    <t>The preg_lmp_date_month_scrolled event fires when the user scrolls to a different month on the LMP date calendar. It captures the month_year the user scrolled to (e.g., 2025-01 or 2025-02). This event provides insight into how users navigate the calendar UI and how far back they need to scroll to find their LMP date. From a business perspective, this is a UX quality indicator. If users are scrolling through many months, they may be confused about what date to enter or may have had their LMP many months ago (indicating they are further along in pregnancy). Excessive scrolling could also indicate the calendar defaults to an inconvenient starting month. Key questions include: How many months do users scroll on average before selecting a date? Are there patterns of back-and-forth scrolling that suggest confusion? Does the default calendar month need to be adjusted to reduce scrolling? Do users who scroll more take longer to complete setup? This event is triggered by any user interacting with the LMP date calendar who changes the displayed month. Synonyms and related concepts include calendar navigation, month scroll, date picker navigation, calendar browsing, month change, date calendar scroll, LMP calendar browse. This event fires between preg_lmp_date_screen_shown and preg_lmp_date_selected.</t>
-  </si>
-  <si>
-    <t>The preg_edd_date_screen_shown event fires when the estimated due date (EDD) calendar selection screen is displayed to the user. This screen appears when the user has chosen the EDD method for calculating their pregnancy timeline, meaning they already know their due date from a healthcare provider. The event captures the source_screen, typically preg_due_date_method. From a business perspective, this event tracks the reach of the EDD input step in the onboarding flow. Users who choose EDD typically have more accurate pregnancy dating because they received a due date from a doctor or ultrasound. Key questions include: What is the completion rate for this screen? Is it higher than the LMP date selection screen, possibly because users with a known EDD are more confident in their input? Are there UX issues that cause abandonment? This event is triggered by users who selected the EDD method and are now providing their due date. Synonyms and related concepts include estimated due date input, EDD calendar screen, due date picker, doctor's due date entry, expected delivery date screen, EDD selection calendar. This event fires after preg_due_date_method_selected (with edd method) and before preg_edd_date_selected.</t>
-  </si>
-  <si>
-    <t>The preg_edd_date_selected event fires when the user selects an estimated due date on the EDD calendar screen. It captures the selected_date in a standard date format. This is a key event because it establishes the pregnancy timeline anchor when the EDD method is chosen. Unlike the LMP method, which requires calculation to derive the due date, the EDD method directly sets the expected delivery date. From a business perspective, the distribution of EDD dates reveals similar insights to LMP dates: how far along users are when they start tracking, and whether the app attracts users across all stages of pregnancy. The EDD also allows the business to forecast when users will complete their pregnancy journey and potentially transition to postpartum content or churn from the pregnancy module. Key questions include: What is the distribution of due dates? Can the business predict seasonal usage patterns from EDD data? Do users who enter an EDD show different engagement patterns than LMP users, possibly due to having more medical engagement overall? All users who interact with the EDD calendar and select a date trigger this event. Synonyms and related concepts include due date entry, EDD confirmation, expected delivery date selection, due date chosen, delivery date input. This event fires after preg_edd_date_screen_shown and leads to onboarding completion or the pregnancy dashboard.</t>
-  </si>
-  <si>
-    <t>The preg_calendar_preview_shown event fires when the pregnancy calendar preview screen is displayed to the user. This screen provides a visual calendar view of the pregnancy timeline with milestones, symptoms, and scheduled activities. It captures the source_screen (which may be preg_dashboard or preg_dashboard_calendar_card) and the current week_number. From a business perspective, the pregnancy calendar is a core engagement feature that gives users a longitudinal view of their pregnancy journey. Tracking how often the calendar preview is accessed answers questions like: How frequently do pregnant users check their calendar? Is the calendar accessed more from the dashboard directly or via the calendar card? Do certain pregnancy weeks drive more calendar views, perhaps around expected milestones or appointments? Is calendar engagement a leading indicator of overall app retention? The week_number parameter helps identify which phases of pregnancy drive the most calendar interest. All pregnant users who navigate to the calendar preview from any entry point will trigger this event. Synonyms and related concepts include pregnancy timeline view, calendar screen impression, pregnancy schedule view, timeline preview, pregnancy planner view, pregnancy calendar entry, gestational calendar view. This event fires after dashboard navigation and before any calendar interaction events like preg_calendar_preview_date_tap or preg_calendar_bottom_sheet_shown.</t>
-  </si>
-  <si>
-    <t>The preg_calendar_preview_close_tap event fires when the user taps the close or back button to leave the pregnancy calendar preview screen. The event captures only the source_screen parameter. This is a simple navigation event that marks the end of a calendar viewing session. From a business perspective, this event, paired with preg_calendar_preview_shown, allows calculation of calendar session duration and helps understand user flow patterns after viewing the calendar. Key questions include: How long do users spend on the calendar before closing it? Do they close it to return to the dashboard, or do they navigate elsewhere? Is the calendar being closed quickly, suggesting users got what they needed fast, or is it used for extended browsing? All pregnant users who exit the calendar preview via the close/back button trigger this event. Synonyms and related concepts include calendar exit, close calendar, calendar dismiss, back from calendar, calendar navigation end, calendar screen close. This event fires after various calendar interaction events and returns the user to their previous screen, typically triggering preg_dashboard_screen_shown.</t>
-  </si>
-  <si>
-    <t>The preg_calendar_preview_today_tap event fires when the user taps the Today button on the pregnancy calendar preview screen. This button snaps the calendar view to the current date, which is useful when the user has been scrolling through past or future dates and wants to return to today. The event captures only the source_screen parameter. From a business perspective, this event indicates that users are navigating away from the current date in the calendar and then wanting to return, which suggests they are actively exploring their pregnancy timeline rather than just checking today's status. Frequent use of the Today button validates that users browse the calendar broadly. Key questions include: How often is the Today button used? Does it correlate with users who explore future milestones or past entries? Is the button needed because the calendar navigation is not intuitive enough to find today's date naturally? All pregnant users who tap the Today button on the calendar preview trigger this event. Synonyms and related concepts include go to today, current date tap, today navigation, calendar today shortcut, return to today, today button click. This event fires during a calendar preview session, after the user has scrolled away from today's date.</t>
-  </si>
-  <si>
-    <t>The preg_calendar_preview_date_tap event fires when the user taps on a specific date in the pregnancy calendar preview grid. It captures the selected_date, the week_number corresponding to that date's pregnancy week, and has_logged_symptoms indicating whether the user has previously logged symptoms for that date. This event is important for understanding how users interact with the calendar at a granular level. From a business perspective, the date taps reveal browsing patterns: Do users mostly tap on the current date, or do they explore past and future dates? Are they tapping on dates where they have logged symptoms (to review them) or on dates without symptoms (perhaps to add entries retroactively)? The has_logged_symptoms parameter is particularly valuable because it distinguishes between review behavior and data entry intent. Key questions include: What is the distribution of tapped dates relative to today's date? Do users more frequently tap past or future dates? Does symptom presence on a date increase or decrease the likelihood of a tap? Can calendar date taps predict upcoming symptom logging activity? All pregnant users who tap on a date in the calendar trigger this event. Synonyms and related concepts include calendar date selection, date cell tap, calendar day click, timeline date interaction, calendar grid tap, pregnancy date click. This event fires during a calendar preview session and is typically followed by preg_calendar_bottom_sheet_shown displaying details for the selected date.</t>
-  </si>
-  <si>
-    <t>The preg_calendar_preview_edit_tap event fires when the user taps the Edit Dates button on the pregnancy calendar preview screen. This button allows the user to modify their pregnancy dates, such as adjusting the LMP or EDD, which recalculates their entire pregnancy timeline. The event captures only the source_screen parameter. From a business perspective, this event indicates that users feel the need to correct or update their pregnancy timeline, which can happen for various reasons: they received updated information from their doctor, they initially entered incorrect dates, or they want to recalculate based on a different method. Tracking this event answers: How often do users need to edit their dates? Is there a peak time when edits are most common, such as after the first ultrasound? Does frequent date editing correlate with user confusion during initial setup? All pregnant users who tap the edit dates button on the calendar preview trigger this event. Synonyms and related concepts include edit pregnancy dates, modify timeline, change due date, adjust pregnancy dates, recalculate dates, update pregnancy info, calendar edit entry. This event fires on the calendar preview and leads to preg_edit_calendar_shown.</t>
-  </si>
-  <si>
-    <t>The preg_calendar_bottom_sheet_shown event fires when the bottom sheet overlay displaying detailed information for a selected date appears on the pregnancy calendar preview screen. This bottom sheet typically shows the pregnancy week and day count, estimated due date, milestones for that date, and any logged symptoms. It captures the selected_date, the weeks into pregnancy, and the days within that week. From a business perspective, this event measures how often users drill into date-level detail on the calendar, which is a signal of deep engagement with the pregnancy timeline. The bottom sheet is where symptom review, milestone display, and scheduled activity information converge, making it a rich touchpoint. Key questions include: How often does a date tap convert to a bottom sheet view? Do users spend time reviewing the bottom sheet content? Are there dates where the bottom sheet has particularly rich content that drives engagement? All pregnant users who tap on a calendar date will trigger this event as the bottom sheet displays. Synonyms and related concepts include date detail sheet, calendar overlay, date information panel, calendar bottom panel, date detail view, date info sheet, calendar detail popup. This event fires immediately after preg_calendar_preview_date_tap and before interactions within the bottom sheet like preg_calendar_symptom_viewed or preg_calendar_bottom_sheet_toggled.</t>
-  </si>
-  <si>
-    <t>The preg_calendar_bottom_sheet_toggled event fires when the user expands or collapses the bottom sheet on the pregnancy calendar preview screen. It captures the action parameter which is either expand or collapse. The bottom sheet starts in a partially visible state showing summary information, and the user can expand it to see full details or collapse it back. From a business perspective, this event indicates the user's interest level in date-specific content. An expand action signals the user wants more detail, while a collapse suggests they have finished reviewing or want to return to the calendar grid. Key questions include: What percentage of bottom sheet views result in an expand? Do users expand and then collapse quickly (scanning) or stay expanded (reading thoroughly)? Is the partially visible state sufficient for most user needs, or do most users expand for full detail? All pregnant users who interact with the bottom sheet expand/collapse gesture trigger this event. Synonyms and related concepts include sheet expand, sheet collapse, bottom sheet interaction, detail panel toggle, sheet resize, overlay expand, detail drawer toggle. This event fires after preg_calendar_bottom_sheet_shown and alongside other bottom sheet interaction events.</t>
-  </si>
-  <si>
-    <t>The preg_calendar_symptom_viewed event fires when logged symptoms for a specific date are displayed within the calendar bottom sheet. It captures the selected_date and symptom_count showing how many symptoms were logged for that date. This event confirms that the user is reviewing their historical symptom data through the calendar interface. From a business perspective, this event measures the calendar's effectiveness as a symptom review tool. One of the key value propositions of a pregnancy tracker is helping users see patterns in their symptoms over time, and the calendar provides the longitudinal view needed for this. Key questions include: How often do users review past symptoms via the calendar? What is the average symptom_count per reviewed date? Are users looking at recent dates or dates from weeks ago? Do users who frequently review symptoms via the calendar also log symptoms more regularly? Can the symptom review experience be enhanced to show trends or patterns? All pregnant users who view a date with logged symptoms on the calendar will trigger this event. Synonyms and related concepts include symptom review, symptom history view, logged symptoms display, symptom data view, historical symptom check, symptom calendar review, past symptoms display. This event fires within the calendar bottom sheet after preg_calendar_bottom_sheet_shown and alongside preg_calendar_bottom_sheet_toggled if the user expands for more detail.</t>
-  </si>
-  <si>
-    <t>The preg_calendar_no_symptoms_shown event fires when the calendar bottom sheet displays a No symptoms logged empty state for a selected date. It captures the selected_date. This event identifies an opportunity for the app to prompt the user to log symptoms retroactively or to set up symptom logging reminders. From a business perspective, the frequency of this event versus preg_calendar_symptom_viewed reveals the gap between dates users explore on the calendar and dates with actual data. A high rate of no symptoms displays suggests users are not logging consistently, which may indicate friction in the logging process, lack of reminders, or users who track sporadically rather than daily. Key questions include: What ratio of date taps show no symptoms versus symptoms present? Is this ratio improving over time as users build logging habits? Can the no symptoms state be converted into a logging prompt to increase data completeness? Do users who see this state more often have lower retention? All pregnant users who tap on a calendar date without logged symptoms will trigger this event. Synonyms and related concepts include empty symptom state, no data logged, symptom gap, missing symptom data, empty date view, no log state, symptom void indicator. This event fires within the calendar bottom sheet as an alternative to preg_calendar_symptom_viewed.</t>
-  </si>
-  <si>
-    <t>The preg_calendar_symptom_chip_tap event fires when the user taps on a symptom chip within the calendar bottom sheet to log a symptom for a specific date. It captures the symptom_id (e.g., nausea, cramps, back_pain) and the selected_date for which the symptom is being logged. This event represents in-context symptom logging directly from the calendar, which is a secondary logging path compared to the dedicated symptom logging screen. From a business perspective, this event measures whether the calendar serves as an effective symptom logging interface. If users are logging symptoms from the calendar, it means the feature reduces friction by allowing users to log without navigating to a separate screen. Key questions include: How much symptom logging happens from the calendar versus the dedicated logging screen? Which symptoms are most commonly logged from the calendar? Does calendar-based logging fill in gaps (retroactive logging for past dates)? Should the calendar bottom sheet be enhanced as a primary logging interface? All pregnant users who interact with symptom chips on the calendar bottom sheet trigger this event. Synonyms and related concepts include quick symptom log, calendar symptom entry, symptom chip selection, in-context symptom logging, calendar-based logging, retroactive symptom entry, quick log tap. This event fires within the calendar bottom sheet and may trigger data save events or contribute to preg_symptom_log_submitted counts.</t>
-  </si>
-  <si>
-    <t>The preg_calendar_activity_viewed event fires when the scheduled activity section becomes visible within the calendar bottom sheet. It captures the activity_count showing how many activities are scheduled for the selected date. This event measures the visibility of scheduled activities like supplements, appointments, and checkups that appear in the calendar view. From a business perspective, the calendar's ability to show scheduled activities is part of its value as a comprehensive pregnancy organizer. If users are seeing and engaging with scheduled activities, the calendar is serving as more than just a symptom log viewer. Key questions include: How often do calendar date views include scheduled activities? What is the average activity_count per date? Do users with more scheduled activities have higher engagement? Are the activities useful enough that users are adding them, or are most dates empty? This event is triggered by all pregnant users who view a calendar date where the activity section is rendered. Synonyms and related concepts include scheduled event view, activity section impression, pregnancy task visibility, appointment display, scheduled reminder view, activity list visibility, calendar task view. This event fires within the calendar bottom sheet, often alongside preg_calendar_symptom_viewed, and may be followed by preg_calendar_reminder_tap.</t>
-  </si>
-  <si>
-    <t>The preg_calendar_reminder_tap event fires when the user taps on a reminder item in the scheduled activity section of the calendar bottom sheet. It captures the reminder_id and the reminder_type, which can be supplement, appointment, checkup, or other categories. This event represents a user engaging with their pregnancy schedule at a task level. From a business perspective, tracking reminder taps helps understand which types of scheduled activities users interact with most and whether the reminder system is driving meaningful engagement. Key questions include: Which reminder types get the most taps? Are supplement reminders tapped more than appointment reminders? Does tapping a reminder lead to a meaningful action (like marking it complete)? Can reminder engagement data inform personalized notification timing? Do users who engage with reminders have better adherence to prenatal care schedules? All pregnant users who tap on a reminder in the calendar bottom sheet trigger this event. Synonyms and related concepts include reminder interaction, scheduled item tap, activity item click, pregnancy task tap, supplement reminder tap, appointment reminder tap, schedule item interaction. This event fires within the calendar bottom sheet after preg_calendar_activity_viewed.</t>
-  </si>
-  <si>
-    <t>The preg_edit_calendar_shown event fires when the edit pregnancy calendar screen is displayed. This screen allows users to modify their pregnancy dates and recalculate their timeline. The event captures the source_screen, typically preg_calendar_preview. From a business perspective, this event tracks how often users access the date editing functionality, which is a maintenance and correction flow rather than a daily engagement feature. The frequency of this event relative to the total user base indicates how often pregnancy dates need adjustment. Key questions include: What percentage of users ever edit their calendar? How frequently do individual users edit their dates? Is there a pattern in when edits happen, such as after prenatal appointments? Does editing dates correlate with changes in engagement patterns? All pregnant users who navigate to the edit calendar screen trigger this event. Synonyms and related concepts include date editing screen, modify pregnancy dates, calendar modification, pregnancy date adjustment, edit timeline view, recalculate dates screen. This event fires after preg_calendar_preview_edit_tap and before interactions on the edit screen like preg_edit_calendar_date_tap or preg_edit_calendar_save_tap.</t>
-  </si>
-  <si>
-    <t>The preg_edit_calendar_close_tap event fires when the user taps the close button on the edit pregnancy calendar screen without saving changes. This is a simple navigation event capturing the user's decision to abandon the editing flow. From a business perspective, this event helps understand whether users who enter the edit flow actually make changes. If many users close without saving, they may have opened the screen accidentally, realized they don't need to change anything, or found the editing interface confusing. Key questions include: What is the close-without-save rate? Are users exploring the edit screen without actually needing to make changes? Does the screen need clearer guidance about what can be edited? All pregnant users who exit the edit calendar via the close button trigger this event. Synonyms and related concepts include cancel edit, close editor, dismiss edit screen, abandon editing, exit without save, edit cancel, editing abandoned. This event fires after preg_edit_calendar_shown and returns the user to preg_calendar_preview_shown.</t>
-  </si>
-  <si>
-    <t>The preg_edit_calendar_today_tap event fires when the user taps the Today button on the edit pregnancy calendar screen. Similar to the same functionality on the calendar preview, this button navigates the calendar view to the current date. From a business perspective, this event has minimal standalone value but contributes to understanding navigation patterns within the edit flow. If users frequently need the Today button while editing, it may indicate they are scrolling through many months to compare dates. All pregnant users who tap Today during the calendar editing session trigger this event. Synonyms and related concepts include edit today navigation, return to today in editor, today shortcut edit mode, current date navigation edit. This event fires during the edit calendar session between preg_edit_calendar_shown and either preg_edit_calendar_save_tap or preg_edit_calendar_close_tap.</t>
-  </si>
-  <si>
-    <t>The preg_edit_calendar_date_tap event fires when the user taps on a specific date cell in the edit calendar grid. It captures the selected_date. This event represents the user selecting a new date to replace their current pregnancy dates (LMP or EDD, depending on their method). From a business perspective, this event captures the specific date correction being made. Comparing the old date (from settings) with the newly tapped date reveals how much the user's pregnancy timeline is shifting, which has implications for content accuracy and user satisfaction. Key questions include: How far off are the new dates from the original dates? Do most edits move the date forward or backward? Are there common date corrections that suggest a systematic issue with the date input UX during onboarding? All pregnant users who tap a date on the edit calendar trigger this event. Synonyms and related concepts include date correction, new date selection, calendar date edit, pregnancy date change, timeline adjustment date, revised date tap. This event fires during the edit session and is typically followed by preg_edit_calendar_save_tap to confirm the change.</t>
-  </si>
-  <si>
-    <t>The preg_edit_calendar_save_tap event fires when the user taps the Save button on the edit pregnancy calendar screen, confirming their date changes. This is a key event because it represents a modification to the user's pregnancy timeline that will affect all week calculations, milestone timing, and content delivery throughout the app. From a business perspective, tracking saves versus close-without-save provides a conversion rate for the editing flow. The context of saves (how far into pregnancy, how much the date changed) helps the team understand why users need to edit and whether the initial setup process could be improved to reduce the need for corrections. Key questions include: What percentage of edit sessions result in a save? At what gestational age do most edits occur? Do saves cluster after specific weeks, possibly corresponding to dating ultrasounds? Does editing dates affect subsequent engagement positively (better content alignment) or negatively (confusion)? All pregnant users who confirm a date edit trigger this event. Synonyms and related concepts include save date changes, confirm edit, apply date correction, save pregnancy dates, confirm timeline change, date update save. This event fires after preg_edit_calendar_date_tap and leads to the updated calendar or dashboard view.</t>
-  </si>
-  <si>
-    <t>The preg_week_details_screen_shown event fires when the pregnancy week details screen is displayed, showing the baby illustration, heading, and weekly insights for a specific pregnancy week. It captures the week_number and trimester being viewed. This screen is a key content consumption surface that users reach from the dashboard (via See Your Baby or See Details taps) or from the trimester details screen. From a business perspective, this event measures content depth engagement. Users who view week details are actively seeking information about their baby's development and their pregnancy journey for a specific week. Key questions include: Which weeks attract the most detail views? Do users view details for their current week only, or do they browse ahead and behind? Is there a correlation between week detail views and overall retention? Which entry points (dashboard vs. trimester details) drive more week detail views? This event is triggered by all pregnant users who navigate to the week details screen. Synonyms and related concepts include weekly pregnancy details, baby development screen, week view, pregnancy week content, fetal development details, weekly update view, pregnancy week information screen. This event fires after navigation from the dashboard or trimester screen and before interaction events like preg_week_details_tab_tap or preg_week_details_insight_tap.</t>
-  </si>
-  <si>
-    <t>The preg_week_details_tab_tap event fires when the user taps a tab pill to switch between different pregnancy weeks on the week details screen. The tabs allow quick navigation between adjacent weeks without returning to the dashboard. It captures the selected_week the user navigated to and the previous_week they were viewing. This event provides insight into browsing behavior within the week details experience. From a business perspective, tab taps reveal whether users are curious about other weeks beyond their current one. If users frequently tab to future weeks, they are looking ahead at upcoming developments. If they tab to past weeks, they may be reviewing what they experienced previously. Key questions include: Do users mostly tap forward (future weeks) or backward (past weeks)? How many weeks do users browse in a single session? Does week browsing correlate with higher engagement or content satisfaction? Can the tab design be improved to encourage more exploration? All pregnant users who tap week tabs on the details screen trigger this event. Synonyms and related concepts include week navigation, week tab switch, pregnancy week browse, week selector tap, adjacent week tap, week pill navigation, week switching. This event fires during a week details session and triggers a new preg_week_details_bottom_sheet_shown for the selected week.</t>
-  </si>
-  <si>
-    <t>The preg_week_details_bottom_sheet_shown event fires when the bottom sheet containing detailed week content (heading, description, baby size, and insights) is displayed on the week details screen. It captures the week_number. This bottom sheet is the primary content delivery mechanism on the week details screen, presenting the rich editorial content that users came to see. From a business perspective, this event should fire nearly every time the week details screen is shown and whenever the user switches to a different week via tab taps. It confirms that content loaded and rendered successfully. Key questions include: Is the content loading rate 100 percent, or are there failures? Does the content rendering speed affect user engagement with the insights? How long do users keep the bottom sheet visible? All pregnant users who view the week details screen will trigger this event. Synonyms and related concepts include week content displayed, weekly detail sheet, pregnancy week info sheet, weekly content render, baby info sheet, week detail overlay, week content panel. This event fires immediately after preg_week_details_screen_shown or preg_week_details_tab_tap and before user interactions within the sheet.</t>
-  </si>
-  <si>
-    <t>The preg_week_details_sheet_toggled event fires when the user expands or collapses the bottom sheet on the week details screen. It captures the action parameter (either expand or collapse). This event mirrors the toggle functionality on the calendar bottom sheet and indicates the user's desire to see more or less content detail. From a business perspective, expand actions indicate active content consumption, while collapse actions may indicate the user is done reading or wants to see more of the baby illustration behind the sheet. Key questions include: What is the expand rate? Do most users expand the sheet to read full details? Is the collapsed state's summary content sufficient for casual users? Does the expand rate vary by week, suggesting some weeks have more compelling content? All pregnant users who interact with the sheet toggle trigger this event. Synonyms and related concepts include detail sheet expand, content panel toggle, week sheet resize, detail overlay expand, info sheet collapse, content drawer toggle. This event fires during the week details session alongside content viewing and insight interaction events.</t>
-  </si>
-  <si>
-    <t>The preg_week_details_insight_tap event fires when the user taps on an insight card in the horizontal insights list on the week details screen. It captures the insight_id, the position in the list, and the current week_number. Insights are curated pieces of content relevant to the user's current pregnancy week, such as nutrition tips, exercise recommendations, or developmental information. From a business perspective, this event measures which insights are most engaging and how the content resonates with users at different pregnancy stages. Key questions include: Which insight_ids get the most taps? Does position affect tap rate (are first-position insights tapped more)? Do certain categories of insights perform better in specific trimesters? Can insight content be personalized based on the user's logged symptoms or behavior? Are insight taps a leading indicator of feature adoption? All pregnant users who tap an insight on the week details screen trigger this event. Synonyms and related concepts include weekly insight tap, pregnancy tip click, insight card interaction, weekly advice tap, content card tap, pregnancy recommendation click. This event fires after preg_week_details_insight_viewed and may lead to a detailed article or content view.</t>
-  </si>
-  <si>
-    <t>The preg_week_details_insight_viewed event fires when an insight card becomes visible in the viewport on the week details screen, as the user scrolls through the horizontal insights list. It captures the insight_id and the position of the insight in the list. This is a passive impression event that pairs with preg_week_details_insight_tap to calculate insight-level tap-through rates. From a business perspective, understanding which insights are seen versus which are tapped reveals the effectiveness of insight titles and previews in attracting user attention. If an insight is frequently viewed but rarely tapped, its preview copy may need improvement. If an insight is rarely viewed, it may be positioned too far in the scroll. Key questions include: What is the view-to-tap conversion rate per insight? How many insights do users scroll through on average? Does insight content quality (measured by tap rate) vary by week? All pregnant users who scroll through insights on the week details screen will trigger this event for each visible insight. Synonyms and related concepts include insight impression, insight card visibility, pregnancy tip exposure, insight scroll view, weekly content impression, insight card exposure. This event fires during week detail browsing and precedes preg_week_details_insight_tap for insights that users interact with.</t>
-  </si>
-  <si>
-    <t>The preg_week_details_scroll_depth event fires when the user reaches scroll depth milestones (25, 50, 75, or 100 percent) on the week details content. It captures the scroll_percent and the week_number being viewed. This event mirrors the dashboard scroll depth tracking but applies specifically to the week details screen. From a business perspective, scroll depth on the week details screen measures content consumption depth for individual weeks. If users consistently reach 100 percent scroll depth, the content length is appropriate and engaging. If most users drop off at 25 percent, the content may be too long, not relevant, or poorly structured. Key questions include: What is the average scroll depth on the week details screen? Does it vary by week number or trimester? Are certain weeks particularly engaging or particularly boring based on scroll depth? Does the content format (text-heavy vs. card-based) affect scroll depth? All pregnant users who scroll on the week details screen trigger this event at each milestone they reach. Synonyms and related concepts include content depth tracking, week detail scroll, content consumption depth, page scroll tracking, week content engagement depth, scroll progress. This event fires during week detail viewing alongside insight viewed events.</t>
-  </si>
-  <si>
-    <t>The preg_week_details_back_tap event fires when the user taps the back or close button to leave the week details screen. This is a navigation event marking the end of a week details viewing session. From a business perspective, pairing this event with preg_week_details_screen_shown allows calculation of time spent on the week details screen, which is a measure of content engagement quality. Key questions include: How long do users spend on week details before going back? Does session duration vary by week or trimester? Do users who spend more time on week details also engage more with other features? All pregnant users who exit the week details screen via the back button trigger this event. Synonyms and related concepts include exit week details, close weekly view, back from week screen, leave pregnancy details, week detail session end. This event fires after various week detail interaction events and returns the user to the dashboard or trimester details screen.</t>
-  </si>
-  <si>
-    <t>The preg_trimester_details_shown event fires when the trimester details screen is displayed, showing articles and educational content specific to a trimester. It captures the trimester number being viewed. Users reach this screen from the dashboard trimester card or from the week details screen. From a business perspective, this event tracks access to trimester-level educational content, which is broader and more thematic than week-specific content. The trimester details screen serves as a content hub for users who want an overview of what to expect across an entire trimester. Key questions include: Which trimester's details are viewed most? Is first trimester more popular due to users being new to pregnancy? Do users who consume trimester content have higher retention? How does trimester content engagement compare to week-specific content engagement? All pregnant users who navigate to the trimester details screen trigger this event. Synonyms and related concepts include trimester content view, trimester overview screen, trimester education screen, pregnancy phase details, trimester articles view, trimester guide screen, pregnancy stage content. This event fires after navigation from the dashboard or week details and before content interaction events like preg_trimester_article_tap.</t>
-  </si>
-  <si>
-    <t>The preg_trimester_tab_tap event fires when the user taps a tab pill to switch between trimesters on the trimester details screen. It captures the selected_trimester and the previous_trimester. This event reveals whether users explore content beyond their current trimester. From a business perspective, browsing ahead to future trimesters indicates anticipation and curiosity, which are positive engagement signals. Looking back at past trimesters may indicate nostalgia or a desire to review information. Key questions include: Do users mostly view their current trimester or browse others? Is there a pattern of looking ahead as users approach trimester transitions? Do users in the first trimester browse the third trimester out of curiosity? Can the browsing patterns inform content recommendations? All pregnant users who switch trimester tabs trigger this event. Synonyms and related concepts include trimester navigation, trimester switch, phase tab tap, trimester selector, pregnancy stage navigation, trimester browse. This event fires on the trimester details screen between preg_trimester_details_shown and content interaction events.</t>
-  </si>
-  <si>
-    <t>The preg_trimester_article_tap event fires when the user taps on a trimester article or video item on the trimester details screen. It captures the article_id, article_title, position in the list, and the trimester context. This is a key content engagement event indicating the user wants to read a specific piece of educational content. From a business perspective, article taps measure which content topics resonate most with users at each trimester stage. The position parameter reveals whether list order affects tap rates, and the article_title provides direct insight into which topics attract the most interest. Key questions include: Which articles have the highest tap rates? Does position significantly impact tap likelihood? Are certain topics consistently popular across all trimesters? Can underperforming articles be improved or replaced? Does article engagement correlate with health outcomes like symptom management or care-seeking behavior? All pregnant users who tap an article on the trimester details screen trigger this event. Synonyms and related concepts include article click, trimester content tap, pregnancy article interaction, educational content tap, trimester article entry, pregnancy reading selection, content item click. This event fires after preg_trimester_article_viewed and leads to the article detail or video playback screen.</t>
-  </si>
-  <si>
-    <t>The preg_trimester_article_viewed event fires when a trimester article item becomes visible in the viewport on the trimester details screen. It captures the article_id and position. This is a passive impression event that pairs with preg_trimester_article_tap to calculate article-level tap-through rates. From a business perspective, understanding article visibility versus engagement helps optimize content ordering and design. If articles in later positions are rarely viewed, the content list may be too long or users may not scroll far enough. Key questions include: How many articles does the average user see per trimester view? What is the view-to-tap rate per article? Does article visibility drop sharply after a certain position? Should article ordering be personalized or dynamically reranked? All pregnant users who scroll through the trimester articles list trigger this event for each visible article. Synonyms and related concepts include article impression, content card visibility, trimester content exposure, article list impression, educational content view, article visibility tracking. This event fires during trimester details browsing and precedes preg_trimester_article_tap for articles the user taps.</t>
-  </si>
-  <si>
-    <t>The preg_trimester_back_tap event fires when the user taps the back button to leave the trimester details screen. This navigation event marks the end of a trimester content browsing session. From a business perspective, it enables session duration calculation for trimester content engagement. Key questions include: How long do users spend browsing trimester content? Do they view multiple articles before leaving? Is the session duration sufficient to indicate meaningful content consumption? All pregnant users who exit the trimester details screen via the back button trigger this event. Synonyms and related concepts include exit trimester screen, back from trimester content, leave trimester details, trimester session end, close trimester view. This event fires after trimester content interaction events and returns the user to the previous screen.</t>
-  </si>
-  <si>
-    <t>The preg_kick_counter_screen_shown event fires when the kick counter screen is displayed to the user. This is the dedicated fetal movement tracking interface where users can time their sessions and record individual kicks. It captures the source_screen (typically preg_dashboard or preg_kick_counter_card) and the current week_number. The kick counter is a clinically relevant feature typically recommended from week 28 onward. From a business perspective, this event tracks how many users access the kick counter feature, which is one of the app's most health-critical tools. A fetus that moves less than expected may need medical attention, making this feature potentially life-saving. Key questions include: What percentage of third-trimester users access the kick counter? At what week do users first access it? Does the access pattern suggest daily use (as recommended) or sporadic use? Is the kick counter discovered primarily from the dashboard card, and should other entry points be added? This event is primarily triggered by pregnant users in their third trimester (week 28+). Synonyms and related concepts include kick tracker screen, fetal movement counter view, baby kick monitor, movement tracking screen, kick counting entry, fetal kick logger view. This event fires after navigation from the dashboard and before preg_kick_counter_start_tap.</t>
-  </si>
-  <si>
-    <t>The preg_kick_counter_start_tap event fires when the user taps the Start button to begin a kick counting session. It captures the current week_number and an is_first_time flag indicating whether this is the user's inaugural kick counting session. This is a key event because it marks the beginning of an active health monitoring session. From a business perspective, the start tap rate relative to screen views reveals the conversion from intent to action. Users who view the kick counter but don't start a session may be confused by the interface, not ready to count, or just reviewing past data. The is_first_time flag is crucial for tracking the kick counter's adoption funnel: how many users try it for the first time, and do first-time users return? Key questions include: What is the screen-to-start conversion rate? Does the is_first_time flag correlate with higher or lower session completion rates? At what gestational week do most users start their first session? Do users who start their first session in week 28 have better adherence than those who start later? This event is triggered by pregnant users who initiate a kick counting session, primarily in the third trimester. Synonyms and related concepts include begin kick count, start tracking kicks, initiate kick session, fetal movement session start, kick timer start, baby kick tracking begin. This event fires after preg_kick_counter_screen_shown and before preg_kick_counter_kick_tap events.</t>
-  </si>
-  <si>
-    <t>The preg_kick_counter_kick_tap event fires each time the user taps the kick area during an active kick counting session to record a single kick. It captures the running kick_count for the current session and the elapsed_seconds since the session started. This event provides granular data about fetal movement patterns as perceived by the user. From a business perspective, the kick tap data enables rich health analytics: average kicks per session, time between kicks, total session duration, and comparisons across days and weeks. The kick_count parameter at each tap allows reconstruction of the full session timeline. Key questions include: What is the average number of kicks per session? What is the typical time between kicks? Do kick patterns change as pregnancy progresses? Can the data be used to identify concerning patterns (e.g., significantly fewer kicks than the user's baseline)? Is the kick recording UI responsive and easy to use during real-time counting? This event is triggered by pregnant users actively counting kicks during a session. Synonyms and related concepts include record kick, kick registration, fetal movement tap, kick log entry, kick count increment, baby kick record, movement registration. This event fires multiple times during a kick counting session between preg_kick_counter_start_tap and preg_kick_counter_session_saved.</t>
-  </si>
-  <si>
-    <t>The preg_kick_counter_session_saved event fires when a kick counting session is completed and the results are saved. It captures the total kick_count, the duration_seconds of the session, and the current week_number. This is a key event because it represents the successful completion of a health monitoring activity, producing a data point that can be tracked over time. From a business perspective, completed kick counting sessions are one of the strongest engagement signals in the pregnancy module and also contribute to the app's health data repository. Key questions include: What percentage of started sessions are completed and saved? What are the average kicks and durations per session? Do these metrics change by week (e.g., fewer kicks in later weeks as space decreases)? Is there a correlation between consistent kick counting and user retention? Can session data be aggregated to provide users with trends and alerts? This event is triggered by pregnant users who complete a kick counting session. Synonyms and related concepts include kick session complete, kick count saved, fetal movement logged, kick session finish, session data saved, kick tracking completed, movement session recorded. This event fires after the final preg_kick_counter_kick_tap and may be followed by preg_kick_prompt_sheet_shown if the kick count triggers a warning.</t>
-  </si>
-  <si>
-    <t>The preg_kick_counter_view_all_tap event fires when the user taps View All to see their full kick counter history. This event indicates the user wants to review past kick counting sessions beyond what is shown on the main kick counter screen. From a business perspective, this event measures interest in historical kick data, which is important because trending kick counts over time is more clinically meaningful than any single session. Key questions include: What percentage of kick counter users tap View All? Are users who review their history more consistent in daily kick counting? Does history review frequency increase as the due date approaches? All pregnant users who tap the View All button on the kick counter screen trigger this event. Synonyms and related concepts include kick history entry, view past sessions, kick count history, session history tap, all sessions view, kick data review entry. This event fires on the kick counter screen and leads to preg_kick_history_screen_shown.</t>
-  </si>
-  <si>
-    <t>The preg_kick_counter_history_tap event fires when the user taps on a specific kick history entry on the main kick counter screen to expand or view its details. It captures the session_date and the position in the history list. This event allows the user to review individual past sessions without navigating to the full history screen. From a business perspective, this event reveals which past sessions attract user attention and how far back users look. Key questions include: Do users tap the most recent sessions or scroll back further? Is the position bias strong? Does session date relate to specific concerns? All pregnant users who tap a history entry on the kick counter screen trigger this event. Synonyms and related concepts include session detail tap, kick history item click, past session view, history entry expand, session review tap. This event fires on the kick counter screen and may show expanded session details inline.</t>
-  </si>
-  <si>
-    <t>The preg_kick_counter_back_tap event fires when the user taps the back button to leave the kick counter screen. This is a navigation event that marks the end of a kick counter session (whether or not an actual counting session took place). From a business perspective, pairing this with preg_kick_counter_screen_shown enables session duration calculation. Key questions include: How long do users spend on the kick counter screen? Do they leave immediately if they are not ready to count, or do they spend time reviewing history? All pregnant users who exit the kick counter screen trigger this event. Synonyms and related concepts include exit kick counter, back from kick tracker, leave kick screen, kick counter session end. This event fires after kick counter interactions and returns the user to the dashboard.</t>
-  </si>
-  <si>
-    <t>The preg_kick_history_screen_shown event fires when the dedicated kick counter history screen is displayed, showing a comprehensive list of all past kick counting sessions. The source_screen is typically preg_kick_counter. From a business perspective, this screen serves users who want a complete view of their fetal movement tracking history, which is valuable for sharing with healthcare providers and for personal reassurance. Key questions include: How frequently is the full history screen accessed? Do users access it before medical appointments? Is the history screen design useful for identifying trends? All pregnant users who navigate to the kick history screen trigger this event. Synonyms and related concepts include kick session history, fetal movement log, kick data history, session archive view, kick counter log screen, movement history. This event fires after preg_kick_counter_view_all_tap and before history interaction events.</t>
-  </si>
-  <si>
-    <t>The preg_kick_history_item_tap event fires when the user taps on a specific history entry on the kick history screen to expand or collapse its details. It captures the session_date, position in the list, and the action (either expand or collapse). This event enables detailed analysis of how users interact with their kick counting history. From a business perspective, the expand/collapse actions reveal whether users are casually scanning the list or deeply reviewing specific sessions. Key questions include: How many items do users expand per visit? Are they expanding recent sessions or older ones? Does expanding a session with low kicks lead to any follow-up action? All pregnant users who interact with history items trigger this event. Synonyms and related concepts include history item expand, session detail toggle, kick history interaction, session expand collapse, history entry review. This event fires on the kick history screen between preg_kick_history_screen_shown and preg_kick_history_back_tap.</t>
-  </si>
-  <si>
-    <t>The preg_kick_history_back_tap event fires when the user taps the back button to leave the kick counter history screen. This is a navigation event marking the end of a history review session. From a business perspective, it enables calculation of time spent reviewing kick history. Key questions include: How long do users spend reviewing their history? Does the duration suggest thorough review or quick scanning? All pregnant users who exit the kick history screen trigger this event. Synonyms and related concepts include exit kick history, back from history, leave kick log, history session end. This event fires after history interaction events and returns the user to the kick counter screen.</t>
-  </si>
-  <si>
-    <t>The 'preg_kick_few_kicks_warning_shown' event fires when a warning indicator is displayed on a kick history entry, alerting the user that a particular session recorded fewer kicks than expected. This event is triggered within the 'preg_kick_counter' screen and captures two parameters: 'session_date' (the date of the flagged session, e.g. '2025-05-10') and 'kick_count' (the number of kicks recorded in that session, e.g. 2, 3, or 4). From an analytics and product perspective, this event is critical for understanding how often users encounter low-kick warnings—a feature designed to encourage timely clinical consultation if fetal movement declines. It answers questions such as: How frequently are low-kick warnings displayed across the user base? What is the distribution of kick counts that trigger warnings? Do users who see warnings tend to start new kick-counting sessions shortly after, or do they disengage from the feature? Are there temporal or gestational-age patterns in warning frequency? From a clinical safety standpoint, this event supports auditing the warning system's sensitivity and specificity: product and medical teams can assess whether the threshold for 'few kicks' is calibrated correctly by cross-referencing warning frequency with user feedback, support tickets, and any downstream clinical outcomes data. The event also enables cohort analysis—comparing engagement and retention metrics for users who have seen warnings versus those who have not—to gauge the emotional and behavioral impact of the warning UX. This is a non-key event but one of the most clinically significant signals in the kick-counter feature, directly tied to maternal-fetal health monitoring. Related events include 'preg_kick_history_screen_shown' (event 76), 'preg_kick_counter_session_completed' (event 73), and 'preg_kick_prompt_sheet_shown' (event 109).</t>
-  </si>
-  <si>
-    <t>The 'preg_settings_screen_shown' event fires whenever the pregnancy settings screen is displayed to the user. This is the entry-point event for the settings flow, which allows users to review and modify their pregnancy configuration—primarily their due date calculation method and the date itself. This event captures no additional parameters beyond the screen identifier ('preg_settings'). From an analytics standpoint, this event measures how often users access their pregnancy settings, which is a proxy for user intent to review or adjust their pregnancy profile. Key questions it answers include: What percentage of users visit settings at least once after initial onboarding? How frequently do users revisit settings (indicating possible confusion about their due date or a desire to correct it)? What is the ratio of settings views to actual updates (captured by event 88, 'preg_settings_update_tap')? Is there a spike in settings visits around certain gestational weeks—perhaps after an ultrasound appointment that provides a revised due date? This event is also valuable for funnel analysis: it serves as the top of the settings modification funnel, with downstream events including method selection (event 84), date changes (event 86), and the update action (event 88). By comparing the volume of settings screen views to the volume of successful updates, product teams can identify drop-off points and UX friction in the settings flow. Additionally, frequent settings visits without corresponding updates may signal confusion or dissatisfaction with the current settings interface. Related events include 'preg_settings_back_tap' (event 83) and all other preg_settings events (events 84–90).</t>
-  </si>
-  <si>
-    <t>The 'preg_settings_back_tap' event fires when the user taps the back button on the pregnancy settings screen, navigating away from settings without completing an update action. This event captures no additional parameters. Analytically, this event is important for understanding navigation patterns and potential abandonment in the settings flow. It answers questions such as: How many users open settings but leave without making changes? Is the back-tap rate higher on certain devices, OS versions, or for users at specific gestational ages? When combined with 'preg_settings_screen_shown' (event 82) and 'preg_settings_update_tap' (event 88), this event helps calculate the settings abandonment rate—a key UX health metric. A high ratio of back-taps to screen views (with few updates) could indicate that users are confused by the settings layout, cannot find what they are looking for, or visited settings by accident. Conversely, a healthy ratio might suggest users are simply reviewing their settings for confirmation without needing changes. This event also supports session-flow analysis: by examining what screen the user navigates to after tapping back, product teams can understand the broader navigation context and whether users return to the dashboard, calendar, or other features. Related events include 'preg_settings_screen_shown' (event 82) and 'preg_settings_update_tap' (event 88).</t>
-  </si>
-  <si>
-    <t>The 'preg_settings_method_selected' event fires when the user selects a due date calculation method within the pregnancy settings screen. It captures two parameters: 'method' (the calculation method chosen, e.g. 'lmp' for last menstrual period, 'edd' for estimated due date, or 'ivf' for IVF transfer date) and 'position' (the zero-indexed position of the selected item in the method list, e.g. 0, 1, or 2). This event is analytically significant because the due date calculation method directly affects all gestational-age-dependent content, week numbers, trimester boundaries, and milestone timing throughout the app. Understanding which methods users prefer—and whether they change methods over time—provides insight into the user demographic (e.g., IVF users represent a distinct and often highly engaged cohort) and helps the product team prioritize method-specific features or content. Key questions this event answers include: What is the distribution of calculation methods across the user base? Do users who initially selected LMP during onboarding later switch to EDD after receiving an ultrasound-confirmed date? Is the 'position' parameter correlated with selection frequency (i.e., do users tend to pick the first option)? This data also informs A/B testing of the method selector UI—for instance, testing whether reordering the options affects selection distribution. Related events include 'preg_settings_date_changed' (event 86), 'preg_settings_update_tap' (event 88), and the onboarding method selection event 'preg_due_date_method_selected' (event 35).</t>
-  </si>
-  <si>
-    <t>The 'preg_settings_date_picker_tap' event fires when the user taps on the date input field to open the date picker control within the pregnancy settings screen. It captures one parameter: 'current_date' (the date currently displayed in the field before the picker opens, e.g. '2025-01-15' or '2025-03-01'). This event indicates active intent to modify the pregnancy date and serves as a leading indicator for the 'preg_settings_date_changed' event (event 86). From an analytics perspective, it answers: How often do users interact with the date picker versus just reviewing it? What is the conversion rate from opening the date picker to actually changing the date? If users open the picker frequently but rarely change the date, it may suggest the picker is being used for reference or that the UX makes accidental taps likely. The 'current_date' parameter enables analysis of whether certain date ranges correlate with higher edit intent—for example, users in early pregnancy may be more likely to adjust dates as they receive updated clinical estimates. This event also supports performance monitoring: if the date picker has latency or rendering issues, a high picker-tap count with low date-change follow-through could point to a technical problem rather than a UX one. Related events include 'preg_settings_date_changed' (event 86) and 'preg_settings_update_tap' (event 88).</t>
-  </si>
-  <si>
-    <t>The 'preg_settings_date_changed' event fires when the user modifies the pregnancy date within the settings screen. It captures three parameters: 'old_date' (the previously set date, e.g. '2025-01-15'), 'new_date' (the newly selected date, e.g. '2025-01-20'), and 'method' (the calculation method in use, e.g. 'lmp', 'edd', or 'ivf'). This is one of the most consequential user actions in the pregnancy module because changing the date recalculates the user's gestational age, week number, trimester, and all date-dependent content throughout the app. Analytically, this event answers critical questions: How often do users change their pregnancy date? What is the typical magnitude and direction of date changes (earlier vs. later)? Do date changes cluster at specific gestational ages (e.g., after the 12-week or 20-week ultrasound appointments when clinical EDD is commonly revised)? Is there a correlation between calculation method and frequency of date changes? The delta between old_date and new_date is a powerful derived metric: large shifts may indicate initial setup errors or significant clinical revisions, while small shifts (1–3 days) may reflect fine-tuning after a dating scan. This event also supports data integrity monitoring—frequent or extreme date changes by the same user could indicate confusion or misuse. Product teams can use this data to decide whether to add guardrails (e.g., confirmation dialogs for large date shifts) or educational prompts explaining the impact of date changes. Related events include 'preg_settings_date_picker_tap' (event 85), 'preg_settings_method_selected' (event 84), and 'preg_settings_update_tap' (event 88).</t>
-  </si>
-  <si>
-    <t>The 'preg_settings_remove_tap' event fires when the user taps the 'Remove Pregnancy' text link within the settings screen, initiating the pregnancy deletion flow. It captures one parameter: 'week_number' (the user's current pregnancy week at the time of the tap, e.g. 12, 20, or 36). This event is a critical signal of user intent to leave or reset the pregnancy module entirely. Analytically, it answers: At what gestational week do users most commonly consider removing their pregnancy? Is there a correlation between remove-tap frequency and specific user journey patterns (e.g., users who never engaged with kick counting or symptom logging)? How many users who tap 'Remove' actually follow through to deletion (tracked by event 93, 'preg_delete_sheet_proceed_tap') versus canceling (event 92)? The 'week_number' parameter is especially valuable: a cluster of remove taps in very early weeks might indicate onboarding regret or accidental pregnancy module activation, while taps in late pregnancy could indicate delivery (the user is no longer pregnant) or dissatisfaction. This event feeds into churn analysis and can trigger retention interventions—if analytics shows a spike in remove taps at a certain week, the product team might introduce targeted content or features to re-engage users at that stage. Related events include 'preg_delete_sheet_shown' (event 91), 'preg_delete_sheet_cancel_tap' (event 92), and 'preg_delete_sheet_proceed_tap' (event 93).</t>
-  </si>
-  <si>
-    <t>The 'preg_settings_update_tap' event fires when the user taps the 'Update Settings' button to save their changes on the pregnancy settings screen. It captures two parameters: 'method' (the calculation method selected at the time of saving, e.g. 'lmp', 'edd', or 'ivf') and 'date_changed' (a boolean indicating whether the date was modified, e.g. 'true' or 'false'). This event represents the user's explicit intent to persist their settings changes and is the penultimate step before the system attempts the update (followed by success or failure events). Analytically, this event answers: What is the overall update rate among users who visit settings? What proportion of updates involve a date change versus only a method change? Do users who change both method and date in a single session have different retention profiles than those who change only one? The 'date_changed' boolean is particularly useful for segmentation: updates where date_changed is false may represent method-only switches (e.g., moving from LMP to EDD), which have different implications for content recalculation. This event also enables conversion funnel analysis from settings screen shown (event 82) → method selected (event 84) → date changed (event 86) → update tapped (event 88) → update succeeded (event 89) or failed (event 90). Drop-off at each step reveals specific UX or technical issues. Related events include all other preg_settings events (82–90).</t>
-  </si>
-  <si>
-    <t>The 'preg_settings_update_success' event fires when pregnancy settings are successfully saved to the backend after the user taps 'Update Settings.' It captures one parameter: 'method' (the calculation method that was saved, e.g. 'lmp', 'edd', or 'ivf'). This is a key event that confirms the completion of the settings update flow. From a product analytics perspective, it answers: What is the success rate of settings updates? What is the distribution of methods among successful saves? Is there a method-specific bias in success rates (e.g., do IVF users experience more failures due to additional validation logic)? The success rate (event 89 count / event 88 count) is a core reliability metric for the settings feature—any sustained drop in this ratio should trigger engineering investigation. This event also supports time-to-success analysis: by measuring the latency between the update tap (event 88) and the success confirmation, teams can assess backend performance and identify slowdowns. For business intelligence, the aggregate method distribution from this event provides a reliable, confirmed view of the user base's pregnancy dating method preferences (more reliable than event 84, which captures selections that may not be saved). Related events include 'preg_settings_update_tap' (event 88) and 'preg_settings_update_failed' (event 90).</t>
-  </si>
-  <si>
-    <t>The 'preg_settings_update_failed' event fires when a pregnancy settings update attempt fails. It captures two parameters: 'error_type' (the category of failure, e.g. 'network', 'server', or 'validation') and 'error_message' (the human-readable error string, e.g. 'No internet connection' or 'Server error'). This event is critical for reliability monitoring and user experience quality. It answers: What is the failure rate for settings updates, and what are the dominant failure modes? Are network errors more common in specific geographies or on certain carriers? Do validation errors indicate a bug in client-side input handling (e.g., allowing invalid dates to reach the server)? Is there a temporal pattern to server errors (e.g., correlated with backend deployments or peak load)? The 'error_type' parameter enables automated alerting: a spike in 'server' errors might trigger an incident response, while a steady baseline of 'network' errors is expected. The 'error_message' parameter provides additional debugging context and can be aggregated to identify new or unexpected error strings. Product teams should also track the retry behavior after failures—do users attempt the update again (by looking for a subsequent event 88), or do they abandon settings entirely (event 83, back tap)? This event feeds into overall app reliability dashboards and SLA monitoring. Related events include 'preg_settings_update_tap' (event 88), 'preg_settings_update_success' (event 89), and 'preg_error_state_shown' (event 116).</t>
-  </si>
-  <si>
-    <t>The 'preg_delete_sheet_shown' event fires when the 'Delete Pregnancy' confirmation bottom sheet is presented to the user. This bottom sheet appears after the user taps the 'Remove Pregnancy' link in settings (event 87) and serves as a confirmation gate before the irreversible deletion action. This event captures no additional parameters. Analytically, this event is important for measuring how many users reach the deletion confirmation step. By comparing volumes of event 87 (remove tap) to event 91 (sheet shown), product teams can verify that the navigation flow is working correctly (they should be approximately 1:1). More importantly, this event anchors the deletion decision funnel: sheet shown (event 91) → cancel (event 92) or proceed (event 93). The cancel-to-proceed ratio is a vital metric—a high cancel rate suggests the confirmation dialog is effective at preventing impulsive deletions, while a high proceed rate might indicate determined users who have already made their decision. This event also supports UX research: if the sheet shown count is significantly lower than the remove tap count, there may be a technical issue preventing the bottom sheet from rendering. Tracking this event over time can reveal trends in deletion intent across app versions, seasonal patterns, or responses to product changes. Related events include 'preg_settings_remove_tap' (event 87), 'preg_delete_sheet_cancel_tap' (event 92), and 'preg_delete_sheet_proceed_tap' (event 93).</t>
-  </si>
-  <si>
-    <t>The 'preg_delete_sheet_cancel_tap' event fires when the user taps 'Cancel' on the delete pregnancy confirmation bottom sheet, choosing not to proceed with deletion. This event captures no additional parameters. This is a positive signal event—it indicates that the user reconsidered the irreversible action of removing their pregnancy data. Analytically, this event answers: What percentage of users who see the deletion confirmation ultimately cancel? Is the cancel rate affected by the copy, design, or positioning of the cancel button? Do users who cancel deletion show different subsequent engagement patterns compared to the general population (e.g., do they become more engaged, or do they eventually return to delete)? By combining this event with 'preg_delete_sheet_shown' (event 91) and 'preg_delete_sheet_proceed_tap' (event 93), teams can calculate the precise save rate of the confirmation dialog. A/B testing different confirmation dialog designs can use this metric as the primary success criterion. This event is also relevant for retention analysis: users who reached the deletion confirmation but canceled represent an at-risk cohort that might benefit from targeted re-engagement (e.g., personalized content, feature education, or satisfaction surveys). Related events include 'preg_delete_sheet_shown' (event 91) and 'preg_delete_sheet_proceed_tap' (event 93).</t>
-  </si>
-  <si>
-    <t>The 'preg_delete_sheet_proceed_tap' event fires when the user taps 'Proceed' on the delete pregnancy confirmation bottom sheet, confirming the irreversible deletion of their pregnancy data. It captures one parameter: 'week_number' (the user's pregnancy week at the time of deletion, e.g. 12, 20, or 36). This is one of the most significant churn events in the pregnancy module—it represents a deliberate, confirmed decision to exit the pregnancy tracking experience entirely. Analytically, this event answers: How many pregnancies are deleted per day/week/month? At what gestational week do deletions peak? Are deletions concentrated among specific user segments (e.g., users who never completed onboarding, or users at 40+ weeks who have delivered)? The 'week_number' parameter is invaluable for distinguishing between different deletion motivations: deletions at weeks 38–42 likely represent post-delivery cleanup, while deletions at weeks 4–8 may indicate early pregnancy loss, false starts, or product dissatisfaction. This segmentation is critical for tailoring the post-deletion experience—users who delivered might be offered a newborn/postpartum module, while early deleters might receive a sensitive feedback prompt. This event feeds into churn dashboards, lifetime value calculations, and product-market fit analysis. It is a key event for business reporting. Related events include 'preg_delete_sheet_shown' (event 91), 'preg_delete_sheet_cancel_tap' (event 92), and 'preg_settings_remove_tap' (event 87).</t>
-  </si>
-  <si>
-    <t>The 'preg_water_intake_screen_shown' event fires when the pregnancy water intake settings screen is displayed to the user. This screen allows users to configure their daily water intake target and preferred container volume for hydration tracking during pregnancy. This event captures no additional parameters. From an analytics perspective, this event measures awareness and reach of the water intake feature. It answers: What percentage of pregnancy module users visit the water intake settings? At what gestational week do users first access this feature? Do users return to this screen multiple times (indicating adjustments) or set it once and forget? Is there a correlation between water intake feature adoption and overall app engagement? This event serves as the top of the water intake configuration funnel, with downstream events including target selection (event 97), container selection (event 99), save tap (event 100), and success/failure outcomes (events 101–102). The screen-shown-to-save-success conversion rate reveals how well the water intake setup flow guides users to completion. Hydration tracking is a wellness feature that may drive daily engagement—users who configure water intake are likely to return to the app throughout the day to log water consumption, making this feature a potential driver of retention and daily active usage. Related events include all preg_water_intake events (95–102).</t>
-  </si>
-  <si>
-    <t>The 'preg_water_intake_back_tap' event fires when the user taps the back button on the water intake settings screen, navigating away without saving. This event captures no additional parameters. Analytically, this event helps measure abandonment in the water intake configuration flow. When compared with 'preg_water_intake_screen_shown' (event 94) and 'preg_water_intake_save_tap' (event 100), it reveals the percentage of users who open water intake settings but leave without completing setup. Key questions include: Is the back-tap rate high enough to suggest UX friction (e.g., confusing dropdown options, unclear units, or missing context about recommended intake)? Do users who back out eventually return to complete setup, or do they permanently abandon the feature? Is the abandonment rate higher for first-time visitors versus returning users adjusting their settings? This data can inform UX improvements such as pre-filled defaults, inline guidance about recommended pregnancy hydration levels, or a simplified single-step setup. Related events include 'preg_water_intake_screen_shown' (event 94) and 'preg_water_intake_save_tap' (event 100).</t>
-  </si>
-  <si>
-    <t>The 'preg_water_target_dropdown_tap' event fires when the user taps the daily water target dropdown on the water intake settings screen. This event captures no additional parameters and indicates that the user is actively engaging with the target selection UI. Analytically, this event helps measure micro-interactions within the water intake setup flow. It answers: Do users interact with the target dropdown before selecting a value, or do they accept the default? How does the dropdown tap rate compare to the actual selection rate (event 97)—a significant gap might indicate a confusing or slow dropdown UI. This event is particularly useful for UX performance analysis: if the dropdown has rendering delays or touch-target issues, the tap count may be inflated relative to selections. It also supports funnel analysis as an intermediate step between screen shown (event 94) and target selected (event 97). Related events include 'preg_water_target_selected' (event 97) and 'preg_water_intake_screen_shown' (event 94).</t>
-  </si>
-  <si>
-    <t>The 'preg_water_target_selected' event fires when the user selects a specific daily water target value from the dropdown on the water intake settings screen. It captures one parameter: 'target_value' (the water target chosen, e.g. '2000ml', '2500ml', or '3000ml'). This event is analytically important because it captures the user's hydration goal, which directly affects the water tracking experience and daily reminders. Key questions it answers: What is the distribution of daily water targets among pregnant users? Do target preferences vary by trimester or geographic region? Is there a correlation between selected target values and completion rates (i.e., do users who set higher targets actually drink more or do they abandon tracking sooner)? The 'target_value' parameter enables segmentation of users by hydration ambition level, which can be cross-referenced with engagement metrics, retention, and health outcomes. Product teams can use this data to inform default value selection, recommend targets based on gestational stage, or provide educational content about pregnancy hydration needs. Related events include 'preg_water_target_dropdown_tap' (event 96) and 'preg_water_intake_save_tap' (event 100).</t>
-  </si>
-  <si>
-    <t>The 'preg_water_container_dropdown_tap' event fires when the user taps the water container volume dropdown on the water intake settings screen. This event captures no additional parameters and indicates the user is engaging with the container size selection. The container volume determines how much water is logged per 'drink' action in the daily tracker, so this setting directly affects the user's tracking experience. Analytically, this event mirrors 'preg_water_target_dropdown_tap' (event 96) but for the container configuration. It helps measure interaction depth within the setup flow and can reveal UX issues with the container dropdown specifically. If the dropdown-tap-to-selection ratio is low, the container options may be confusing or the UI may have usability issues. Related events include 'preg_water_container_selected' (event 99) and 'preg_water_intake_screen_shown' (event 94).</t>
-  </si>
-  <si>
-    <t>The 'preg_water_container_selected' event fires when the user selects a container volume from the dropdown on the water intake settings screen. It captures one parameter: 'container_volume' (the volume selected, e.g. '250ml', '500ml', or '750ml'). This parameter reveals user preference for tracking granularity: a 250ml container means more frequent logging throughout the day (higher engagement touchpoints), while a 750ml container means fewer but larger increments. Analytically, this event answers: What container sizes are most popular? Is there a correlation between container size and daily tracking completion rates? Do users who select larger containers find tracking easier or more cumbersome? The container volume distribution also provides indirect insight into users' drinking habits and preferred vessel types (e.g., 250ml suggests a glass, 500ml a standard water bottle, 750ml a large bottle). This data can inform product decisions about default container sizes, the addition of custom size options, or smart recommendations. Related events include 'preg_water_container_dropdown_tap' (event 98) and 'preg_water_intake_save_tap' (event 100).</t>
-  </si>
-  <si>
-    <t>The 'preg_water_intake_save_tap' event fires when the user taps the 'Save' button on the water intake settings screen to persist their hydration preferences. It captures two parameters: 'target_value' (the daily water target being saved, e.g. '2000ml', '2500ml') and 'container_volume' (the container size being saved, e.g. '250ml', '500ml'). This event represents the user's commitment to their hydration tracking configuration and is the penultimate step in the water intake setup funnel. Analytically, it answers: What is the save rate relative to screen views? What are the most common target-container combinations? Do users tend to customize both settings or only one? The dual-parameter capture enables analysis of configuration patterns—for example, whether users who set a 3000ml target tend to pair it with a 750ml container for fewer daily interactions. This event also serves as the basis for measuring save-to-success conversion (event 100 → event 101) and save-to-failure rates (event 100 → event 102), which are key reliability metrics. Related events include 'preg_water_intake_save_success' (event 101) and 'preg_water_intake_save_failed' (event 102).</t>
-  </si>
-  <si>
-    <t>The 'preg_water_intake_save_success' event fires when water intake settings are successfully saved to the backend. This event captures no additional parameters. It confirms the successful completion of the water intake configuration flow and represents a feature activation milestone—once settings are saved, the user can begin daily hydration tracking. Analytically, this event is critical for measuring the end-to-end success rate of the water intake setup flow (event 94 screen shown → event 101 save success). It answers: What is the overall feature activation rate? How does save success relate to subsequent daily water logging engagement? Do users who successfully save settings become regular trackers or do they drop off? This event also feeds into reliability monitoring: the ratio of save successes (event 101) to save attempts (event 100) should be near 1.0; any degradation indicates backend issues. For growth metrics, the cumulative count of unique users with a save success event represents the total activated hydration-tracking user base. Related events include 'preg_water_intake_save_tap' (event 100) and 'preg_water_intake_save_failed' (event 102).</t>
-  </si>
-  <si>
-    <t>The 'preg_water_intake_save_failed' event fires when the water intake settings fail to save. It captures two parameters: 'error_type' (the failure category, e.g. 'network', 'server', or 'validation') and 'error_message' (the human-readable error description, e.g. 'No internet' or 'Server error'). This event is important for reliability monitoring and user experience quality for the water intake feature. It answers: What is the failure rate for water intake saves? What are the dominant error types? Are validation errors occurring (which would suggest a client-side bug allowing invalid configurations to reach the server)? Do failures correlate with specific times, regions, or app versions? The error_type parameter enables automated alerting and categorized debugging. Product teams should track whether users retry after a failure (by looking for a subsequent event 100) or abandon the setup entirely (event 95, back tap, or session end). A high failure rate directly impacts feature adoption—users who cannot save their preferences cannot use the hydration tracker, making this event a gating metric for the feature's health. Related events include 'preg_water_intake_save_tap' (event 100), 'preg_water_intake_save_success' (event 101), and 'preg_error_state_shown' (event 116).</t>
-  </si>
-  <si>
-    <t>The 'preg_get_pregnant_sheet_shown' event fires when the 'Get Pregnant Mode' bottom sheet is displayed to the user. This bottom sheet offers users the option to switch from the pregnancy tracking module to a trying-to-conceive (TTC) or fertility mode within the FemVerse app. This event captures no additional parameters. Analytically, this event answers: How many pregnancy-mode users are presented with the option to switch to TTC mode? What user actions or navigation paths lead to this sheet appearing? Is this sheet shown proactively by the app (e.g., based on certain conditions) or triggered by user action? Understanding the volume and context of this event is important for measuring cross-module interest and identifying users who may be in a transitional reproductive phase—for instance, users who have experienced pregnancy loss and want to track fertility again, or users who activated pregnancy mode prematurely. This event anchors a micro-funnel: sheet shown (event 103) → close (event 104) or switch (event 105), revealing the conversion rate from exposure to mode-switching. Related events include 'preg_get_pregnant_sheet_close_tap' (event 104) and 'preg_get_pregnant_switch_tap' (event 105).</t>
-  </si>
-  <si>
-    <t>The 'preg_get_pregnant_sheet_close_tap' event fires when the user taps the close button on the 'Get Pregnant Mode' bottom sheet, dismissing the option to switch modes without taking action. This event captures no additional parameters. Analytically, it represents a rejection of the mode-switch offer and answers: What percentage of users who see the TTC mode sheet dismiss it? Is the dismissal rate consistent over time, or does it change with app updates or feature improvements to the pregnancy module? A high close rate suggests users are satisfied with their current pregnancy mode or that the TTC mode offer is not relevant to them. Conversely, if paired with subsequent navigation to settings or deletion events, it might indicate the user is exploring exit options. This event is important for optimizing the timing and targeting of cross-module promotions—showing this sheet to users who are unlikely to switch adds friction without value. Related events include 'preg_get_pregnant_sheet_shown' (event 103) and 'preg_get_pregnant_switch_tap' (event 105).</t>
-  </si>
-  <si>
-    <t>The 'preg_get_pregnant_switch_tap' event fires when the user taps the 'Switch Mode' button on the 'Get Pregnant Mode' bottom sheet, confirming their intent to switch from pregnancy tracking to trying-to-conceive mode. This event captures no additional parameters. This is a significant lifecycle event—the user is leaving the pregnancy module for the fertility module, which may indicate pregnancy loss, a change in reproductive plans, or product exploration. Analytically, this event answers: What is the conversion rate from sheet shown (event 103) to mode switch? What gestational week are users at when they switch (derivable by joining with session context)? Do users who switch to TTC mode eventually return to pregnancy mode? How does mode-switching affect long-term retention and lifetime value? This event is critical for user journey mapping across FemVerse modules and supports sensitive product decisions around how to handle the transition—for example, whether to offer supportive messaging for users who may have experienced loss. It also feeds into cross-module funnel analysis and helps quantify the bidirectional flow between pregnancy and fertility features. Related events include 'preg_get_pregnant_sheet_shown' (event 103), 'preg_get_pregnant_sheet_close_tap' (event 104), and the symmetric events 'preg_track_sheet_shown' (event 106) and 'preg_track_sheet_switch_tap' (event 108).</t>
-  </si>
-  <si>
-    <t>The 'preg_track_sheet_shown' event fires when the 'Discover Pregnancy Mode' bottom sheet is displayed to the user. This sheet offers users the option to switch into the pregnancy tracking module—likely shown to users who are currently in a different mode (e.g., period tracking or TTC) and indicates that the app has detected or the user has signaled a pregnancy. This event captures no additional parameters. Analytically, this event measures the reach and frequency of pregnancy mode onboarding prompts. It answers: How many users are presented with the option to enter pregnancy mode? What triggers this sheet (e.g., a missed period, a user self-report, or a manual navigation action)? What is the conversion rate from sheet shown to mode switch (event 108)? This event is the entry point of the pregnancy module acquisition funnel from other FemVerse modules and is vital for understanding cross-module conversion. High sheet-shown counts with low switch rates might indicate poor timing, irrelevant targeting, or UX issues with the bottom sheet. Related events include 'preg_track_sheet_close_tap' (event 107) and 'preg_track_sheet_switch_tap' (event 108).</t>
-  </si>
-  <si>
-    <t>The 'preg_track_sheet_close_tap' event fires when the user taps the close button on the 'Discover Pregnancy Mode' bottom sheet, dismissing the pregnancy module offer. This event captures no additional parameters. This dismissal event is important for understanding user intent and offer relevance. It answers: What percentage of users who see the pregnancy mode offer decline it? Is the decline rate consistent, or does it vary based on the user's current cycle phase, app usage patterns, or demographic segment? A high close rate may suggest the offer is being shown too aggressively, at the wrong time, or to users who are not actually pregnant. This data informs targeting optimization—reducing unnecessary sheet displays improves the user experience and preserves the offer's impact for users who are genuinely transitioning to pregnancy. The close rate also serves as a negative signal for the pregnancy mode acquisition funnel and can be combined with user segment data to build predictive models of pregnancy mode adoption likelihood. Related events include 'preg_track_sheet_shown' (event 106) and 'preg_track_sheet_switch_tap' (event 108).</t>
-  </si>
-  <si>
-    <t>The 'preg_track_sheet_switch_tap' event fires when the user taps the 'Switch Mode' button on the 'Discover Pregnancy Mode' bottom sheet, confirming their intent to enter the pregnancy tracking module. This event captures no additional parameters. This is a key acquisition event for the pregnancy module—it represents a new user entering the pregnancy tracking experience from another FemVerse module. Analytically, it answers: What is the conversion rate from the pregnancy mode offer (event 106) to actual adoption? How does this compare to users who enter pregnancy mode through other paths (e.g., direct onboarding)? Do users who switch via this sheet have different engagement and retention profiles compared to users who start in pregnancy mode from app installation? This event is critical for growth metrics—it quantifies the internal cross-sell pipeline from period/fertility tracking to pregnancy tracking. It also informs the post-switch onboarding experience: users arriving via this sheet may need a different onboarding flow than first-time app users, and tracking their entry path enables A/B testing of tailored experiences. Related events include 'preg_track_sheet_shown' (event 106), 'preg_track_sheet_close_tap' (event 107), and the onboarding flow events starting with 'preg_period_or_pregnant_screen_shown' (event 31).</t>
-  </si>
-  <si>
-    <t>The 'preg_kick_prompt_sheet_shown' event fires when a kick prompt bottom sheet is displayed to the user. It captures one parameter: 'heading' (the heading text of the prompt, e.g. 'Low kicks detected' or 'Session complete'). This bottom sheet is a contextual notification within the kick-counting feature that communicates important information or guidance based on the user's kick-counting session results. Analytically, this event answers: How often are kick prompts displayed? What is the distribution of prompt types (based on heading text)? Are 'Low kicks detected' prompts more common at certain gestational ages? Do users who see low-kick prompts subsequently start new sessions or seek medical attention (inferable from app re-engagement patterns)? The 'heading' parameter is critical for segmenting prompt types—clinical safety prompts ('Low kicks detected') have very different product and medical implications than informational prompts ('Session complete'). Product and clinical teams should monitor the ratio of safety prompts to total prompts and track whether safety-prompt frequency trends align with expected medical baselines. This event also supports UX effectiveness analysis: by measuring the time between prompt display and the user's response (event 110, okay tap), teams can assess whether users are reading and considering the prompt content. Related events include 'preg_kick_prompt_okay_tap' (event 110) and 'preg_kick_few_kicks_warning_shown' (event 81).</t>
-  </si>
-  <si>
-    <t>The 'preg_kick_prompt_okay_tap' event fires when the user taps the 'Okay' button on the kick prompt bottom sheet, acknowledging and dismissing the prompt. This event captures no additional parameters. Analytically, this event confirms user acknowledgment of the kick prompt and, when combined with event 109, enables measurement of prompt engagement: What percentage of prompts are acknowledged? What is the average time between prompt display and acknowledgment? Do users who see and acknowledge safety-related prompts ('Low kicks detected') behave differently afterward compared to those who see informational prompts? A prompt with a low okay-tap rate relative to its shown rate might indicate that users are dismissing the sheet through other means (e.g., tapping outside the sheet, pressing back) or that the sheet is auto-dismissing—both of which would warrant UX investigation to ensure important clinical messages are being seen and acknowledged. This event is also useful for compliance and audit purposes: in contexts where the app provides clinical guidance, documenting that the user acknowledged a safety prompt creates a record of informed engagement. Related events include 'preg_kick_prompt_sheet_shown' (event 109).</t>
-  </si>
-  <si>
-    <t>The 'preg_symptom_log_screen_shown' event fires when the pregnancy symptom logging screen or chatbot symptoms interface is displayed. It captures one parameter: 'week_number' (the user's current pregnancy week, e.g. 12, 20, or 36). This event marks the entry point of the symptom logging feature—a clinically significant tool that allows users to track and report pregnancy symptoms across categories like physical symptoms, mood, sleep, and appetite. Analytically, this event answers: What percentage of users access the symptom logger? At what gestational weeks is symptom logging most popular? Is there a correlation between symptom logging adoption and engagement with other features (e.g., kick counting, AI chatbot)? The 'week_number' parameter enables gestational-age-based analysis of symptom logging behavior—for example, first-trimester users may log more nausea-related symptoms while third-trimester users may focus on pain and discomfort. This event anchors the symptom logging funnel: screen shown → category viewed (event 112) → chip tapped (event 113) → log submitted (event 114) → triage shown (event 115, if triggered). The screen-shown-to-submission conversion rate is a key feature engagement metric. Related events include all preg_symptom events (112–115).</t>
-  </si>
-  <si>
-    <t>The 'preg_symptom_category_viewed' event fires when a symptom category section becomes visible on the symptom logging screen. It captures one parameter: 'category_name' (the name of the category, e.g. 'symptoms', 'mood', 'sleep', or 'appetite'). This event tracks which sections of the symptom logger users are exposed to, which may depend on scrolling behavior or screen layout. Analytically, it answers: Which symptom categories are most frequently viewed? Do users scroll through all categories or stop after the first one? Is there a category that users consistently skip (suggesting low relevance or poor placement)? The viewing pattern data informs UX decisions about category ordering, default expansion/collapse states, and whether to personalize the category display based on the user's gestational age or past logging patterns. For example, if 'mood' is rarely viewed but clinically important, the product team might consider promoting it higher in the list or adding contextual prompts. This event supports content strategy by revealing which wellness dimensions pregnant users prioritize in their self-tracking. Related events include 'preg_symptom_log_screen_shown' (event 111), 'preg_symptom_chip_tap' (event 113), and 'preg_symptom_log_submitted' (event 114).</t>
-  </si>
-  <si>
-    <t>The 'preg_symptom_chip_tap' event fires when the user taps a symptom chip to select or deselect it on the symptom logging screen. It captures four parameters: 'symptom_id' (the identifier of the symptom, e.g. 'nausea', 'cramps', 'back_pain', 'fatigue', 'headache'), 'category_name' (the category the symptom belongs to, e.g. 'symptoms' or 'mood'), 'action' (whether the tap selects or deselects the chip, e.g. 'select' or 'deselect'), and 'position' (the zero-indexed position of the chip within its category, e.g. 0, 1, 2, 3). This is the most granular interaction event in the symptom logging feature and provides rich data about user symptom profiles. Analytically, it answers: What are the most commonly selected symptoms across the user base? How does symptom prevalence vary by gestational week (joinable with session context)? What is the deselect rate—do users frequently change their mind after tapping, suggesting indecision or UI issues? Does chip position affect selection probability (a positional bias would suggest users are not fully reviewing all options)? The symptom-level data from this event is valuable for clinical research partnerships, population health insights, and content personalization. For example, if 'back_pain' is the most selected symptom in the third trimester, the app can proactively surface back pain relief content. The 'action' parameter also reveals interaction patterns: a high deselect rate for certain symptoms might indicate ambiguity in symptom definitions. Related events include 'preg_symptom_category_viewed' (event 112) and 'preg_symptom_log_submitted' (event 114).</t>
-  </si>
-  <si>
-    <t>The 'preg_symptom_log_submitted' event fires when the user submits their symptom log. It captures four parameters: 'symptom_count' (total number of symptoms logged, e.g. 1, 3, or 7), 'severity_max' (the maximum severity recorded across all logged symptoms, e.g. 'mild', 'moderate', or 'severe'), 'triage_shown' (a boolean indicating whether the submission triggered a safety triage template, e.g. 'true' or 'false'), and 'week_number' (the current pregnancy week, e.g. 12, 20, or 36). This is a key event and one of the most analytically rich events in the symptom logging feature. It answers: What is the average number of symptoms logged per session? How does symptom severity distribution vary across trimesters? What percentage of submissions trigger a safety triage? Is there a correlation between symptom count, severity, and subsequent healthcare-seeking behavior or app engagement? The 'triage_shown' boolean is especially important: it flags submissions that crossed a clinical threshold, enabling monitoring of the triage system's activation rate and sensitivity. The combination of symptom_count, severity_max, and week_number creates a powerful dataset for population-level pregnancy symptom epidemiology. Product teams can use this data to calibrate the triage system, personalize content recommendations, and identify user cohorts experiencing significant symptom burden who might benefit from additional support. Related events include 'preg_symptom_chip_tap' (event 113) and 'preg_symptom_triage_shown' (event 115).</t>
-  </si>
-  <si>
-    <t>The 'preg_symptom_triage_shown' event fires when a safety triage or 'when to seek care' template is displayed to the user after symptom logging. It captures three parameters: 'trigger_symptoms' (the specific symptoms that triggered the triage, e.g. 'heavy_bleeding' or 'severe_pain'), 'triage_level' (the severity classification of the triage recommendation, e.g. 'self_care', 'monitor', 'clinician', or 'urgent'), and 'week_number' (the current pregnancy week, e.g. 12, 20, or 36). This is the most clinically significant event in the symptom logging feature and arguably one of the most important events in the entire pregnancy module. It represents the app actively providing health guidance based on the user's reported symptoms. Analytically, it answers: How often is the triage system activated? What is the distribution of triage levels? Which symptoms most commonly trigger triage? Does triage frequency vary by gestational age? Do users who receive urgent triage recommendations take action (e.g., contact their provider, visit an ER—inferable from app disengagement or subsequent chatbot queries)? The 'triage_level' parameter is critical for clinical safety auditing: the system must not under-triage serious symptoms or over-triage benign ones. Regular analysis of trigger_symptoms × triage_level × week_number can validate the triage algorithm against clinical guidelines and flag potential calibration issues. This event also has medicolegal implications—maintaining records of triage recommendations and their contexts supports the app's duty-of-care obligations. Related events include 'preg_symptom_log_submitted' (event 114) and 'preg_symptom_chip_tap' (event 113).</t>
-  </si>
-  <si>
-    <t>The 'preg_error_state_shown' event fires when an error state is displayed on any screen within the pregnancy module. It captures two parameters: 'error_type' (the category of error, e.g. 'network', 'server', 'timeout', or 'unknown') and 'error_message' (the error message shown to the user, e.g. 'No internet connection' or 'Something went wrong'). This is a cross-cutting observability event that tracks all user-visible errors across the pregnancy experience. Analytically, it answers: What is the overall error rate in the pregnancy module? What are the dominant error types and messages? Are errors concentrated on specific screens or evenly distributed? Is there a temporal pattern (e.g., spikes during backend deployments, peak hours, or specific app versions)? How does error frequency correlate with user retention and satisfaction? This event is essential for engineering reliability dashboards, SLA monitoring, and incident detection. The 'error_type' parameter enables automated alerting rules (e.g., page if 'server' errors exceed a threshold), while 'error_message' provides debugging context for root cause analysis. Product teams should also track the relationship between error exposure and user churn—users who encounter multiple errors in a session may be at elevated risk of abandoning the app. Related events include 'preg_retry_tap' (event 117) and all feature-specific failure events (e.g., events 80, 90, 102).</t>
-  </si>
-  <si>
-    <t>The 'preg_retry_tap' event fires when the user taps a retry button after encountering an error on any pregnancy module screen. It captures one parameter: 'error_type' (the type of the original error that prompted the retry, e.g. 'network', 'server', or 'timeout'). This event measures user resilience and recovery behavior in the face of errors. Analytically, it answers: What percentage of users who see an error attempt a retry? Does retry behavior vary by error type (e.g., are users more likely to retry network errors than server errors)? How many retry attempts does a user make before giving up? What is the retry success rate (inferable by checking whether the error state is shown again shortly after)? The retry rate is a key UX health metric: a high retry rate indicates user persistence and trust in the app, while a low retry rate suggests users have lost confidence or expect the error to persist. The error_type parameter enables error-type-specific retry analysis—for example, network error retries may have a higher success rate than server error retries, which could inform the retry UX (e.g., showing different messaging based on error type). This event also supports automated reliability monitoring: a spike in retry taps is an early indicator of a systemic issue. Related events include 'preg_error_state_shown' (event 116).</t>
-  </si>
-  <si>
-    <t>The 'preg_toolbar_action_tap' event fires when the user taps an action item in the toolbar on any pregnancy module screen. It captures one parameter: 'action_id' (the identifier of the toolbar action tapped, e.g. 'settings', 'calendar', or 'notifications'). This event tracks global navigation interactions via the toolbar—a persistent UI element that provides quick access to key features. Analytically, it answers: Which toolbar actions are most frequently used? Is the toolbar the primary navigation path to features like settings and calendar, or do users reach those screens through other routes? Are there toolbar actions that are rarely tapped (suggesting they could be replaced with higher-value options)? Does toolbar usage vary by screen context (e.g., do users tap 'calendar' more often from the dashboard than from week details)? The 'action_id' parameter enables toolbar optimization: by ranking action popularity, the product team can ensure the most valuable actions occupy the most prominent positions. This event also supports navigation flow analysis—understanding how users move between screens helps identify the most common user journeys and optimize the information architecture. Related events include screen-shown events for the destination screens (e.g., 'preg_settings_screen_shown' event 82, 'preg_calendar_preview_screen_shown' event 41).</t>
-  </si>
-  <si>
-    <t>The 'preg_dashboard_dwell_threshold' event fires when the user exceeds a predefined dwell time threshold on the pregnancy dashboard, indicating sustained, engaged browsing rather than a quick glance. It captures two parameters: 'threshold_seconds' (the dwell time threshold that was crossed, e.g. 30, 60, or 120 seconds) and 'week_number' (the user's current pregnancy week, e.g. 12, 20, or 36). This event is a behavioral engagement signal that goes beyond simple screen views. Analytically, it answers: What percentage of dashboard visits result in sustained engagement (exceeding 30s, 60s, 120s)? How does dwell time distribution vary by gestational week? Is longer dwell time correlated with higher feature adoption (e.g., users who spend 60+ seconds on the dashboard are more likely to use kick counting or symptom logging)? Does dwell time change after product updates or content refreshes? The threshold-based design captures multiple levels of engagement in a single session, allowing teams to define and track light, moderate, and deep engagement cohorts. The 'week_number' parameter enables gestational-age-specific engagement analysis—early pregnancy users may dwell longer as they explore the app for the first time, while experienced users may spend less time but navigate more efficiently. This event supports retention modeling and can be used as a leading indicator of user satisfaction. Related events include 'preg_dashboard_screen_shown' (event 1) and 'preg_dashboard_scroll_depth' (event 4).</t>
-  </si>
-  <si>
-    <t>The 'preg_week_transition_occurred' event fires when the user's pregnancy advances to a new week, detected on app open or dashboard load. It captures four parameters: 'previous_week' (the prior pregnancy week, e.g. 11, 19, or 35), 'new_week' (the new pregnancy week, e.g. 12, 20, or 36), 'trimester' (the current trimester, e.g. 1, 2, or 3), and 'trimester_changed' (a boolean indicating whether the trimester boundary was crossed, e.g. 'true' or 'false'). This is a lifecycle progression event that marks the passage of gestational time within the app. Analytically, it answers: How many active users experience a week transition (a proxy for weekly active users in the pregnancy module)? Are there weeks where user drop-off is pronounced (i.e., fewer users transition from week N to week N+1 than expected)? Does the trimester_changed flag correlate with changes in engagement patterns? The week transition event also serves as a natural content refresh trigger—each new week brings new baby development information, tips, and milestones, making this event useful for measuring content consumption timing. The gap between previous_week and new_week can also reveal re-engagement patterns: if a user jumps from week 15 to week 18, they missed two weeks of active usage, which is an important retention signal. This event is foundational for cohort-based retention analysis in the pregnancy module. Related events include 'preg_trimester_changed' (event 121) and 'preg_dashboard_screen_shown' (event 1).</t>
-  </si>
-  <si>
-    <t>The 'preg_trimester_changed' event fires when the user transitions from one trimester to the next—a significant pregnancy milestone. It captures three parameters: 'previous_trimester' (the trimester the user is leaving, e.g. 1 or 2), 'new_trimester' (the trimester the user is entering, e.g. 2 or 3), and 'week_number' (the pregnancy week at the time of transition, e.g. 13 or 28). This is a landmark lifecycle event that occurs only twice during a pregnancy (1→2 and 2→3) and represents a major phase change in the user's experience. Analytically, it answers: How many users reach each trimester milestone (a high-level funnel metric for the pregnancy module)? Is there significant drop-off between trimesters (indicating churn at specific pregnancy stages)? Does the trimester transition trigger increased or decreased engagement? Do users who reach the third trimester have meaningfully different feature usage patterns than those in earlier trimesters? The 'week_number' parameter allows validation that trimester transitions are occurring at the correct gestational weeks based on the user's configured due date method. Product teams can use trimester transitions to trigger milestone celebrations, new feature introductions (e.g., kick counting becomes relevant in the third trimester), and targeted content campaigns. This event is key for longitudinal user journey analysis and pregnancy module retention reporting. Related events include 'preg_week_transition_occurred' (event 120), 'preg_milestone_card_shown' (event 21), and 'preg_dashboard_screen_shown' (event 1).</t>
+    <t>This event, preg_dashboard_screen_shown, is fired every time the Pregnancy Dashboard screen — also known as the Week Home screen — is displayed to the user. The precise trigger is the screen becoming visible in the foreground, which means it fires on initial navigation to the dashboard after onboarding, on returning via back navigation from deeper screens like week details or symptom logging, on resuming the app from the background if the dashboard was the last visible screen, and when arriving from a push notification tap or deep link. It carries the parameters source_screen (recording where the user navigated from), week_number (Current pregnancy week, for example 12, 20, 36), trimester (Current trimester, for example 1, 2, 3), gestational_age (Gestational age in weeks and days format, for example 12w3d, 20w0d, 36w5d), is_first_time (Whether this is the first time the user views the dashboard, for example true, false). The is_first_time parameter specifically distinguishes whether this is the very first time the user has ever seen the pregnancy dashboard after completing onboarding, which is critical for measuring activation against the PRD's 'First value completion rate' KPI. This event is marked as a Key Event because the dashboard is the central hub of the entire pregnancy module. According to the PRD, the dashboard displays the week header (e.g. Week 12, 12w3d, Trimester), a baby development card with size analogy, a 'your body this week' section, 1-3 recommended actions, quick log entry for symptoms and mood, a checklist highlight, and the Ask Femverse AI prompt. From a business and analytics perspective, this event answers critical questions: How many unique users reach the pregnancy dashboard daily and weekly? What is the D7 and D30 retention rate specifically for pregnancy module users? What percentage of users who complete onboarding actually land on the dashboard (activation funnel completion)? How does dashboard visit frequency vary by trimester — do third-trimester users visit more often due to anxiety, or less often due to familiarity? Which source_screen drives the most dashboard visits — organic opens, notifications, or deep links? This event is foundational for the PRD's primary activation funnel: Onboarding completion -&gt; Week dashboard view -&gt; first action. Without this event firing, the user has not entered the core product experience. All pregnancy users who have completed or are in the process of completing setup will trigger this event. Users who have not yet started pregnancy setup may see the empty state instead, tracked by preg_dashboard_empty_state_shown. New users who just finished onboarding will have is_first_time=true, while returning users will have is_first_time=false. Synonyms and related concepts that an analyst or developer might use when searching for this event include: pregnancy home screen view, week home page impression, pregnancy main screen load, dashboard pageview, pregnancy landing screen, weekly dashboard open, pregnancy module entry point, home screen shown, main pregnancy view, pregnancy hub screen. Related events that typically fire before this one include preg_onboarding_completed or preg_due_date_method_selected (for first-time users completing setup), app_open and navigation events (for returning users), or notification_opened (when arriving from a push). Events that commonly fire after this one include preg_dashboard_loading_shown and preg_dashboard_content_loaded (the load sequence), preg_dashboard_baby_card_viewed and preg_dashboard_trimester_viewed (impression events as content renders), preg_dashboard_scroll_depth (as the user browses), and various tap events like preg_dashboard_log_symptoms_tap, preg_dashboard_see_baby_tap, preg_dashboard_detail_card_tap, and preg_dashboard_ai_chatbot_tap as the user interacts with dashboard components.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_screen_exited, is fired when the user leaves the Pregnancy Dashboard screen by any means. It triggers at the precise moment the dashboard is no longer the active foreground screen, which includes when the user navigates forward to another screen (such as week details, symptom logging, or settings), when the user presses the back button to leave the pregnancy module, when the app goes to the background (the user switches apps, locks the phone, or receives a phone call), and potentially when the app is force-closed or crashes. It carries the parameters source_screen (recording where the user navigated from), exit_method (How the user exited, for example back, navigate, app_background), time_spent_seconds (Duration spent on the screen in seconds, for example 15, 45, 120). The exit_method parameter is particularly valuable because it distinguishes intentional forward navigation (the user found something to engage with) from backward navigation (the user is leaving) from app backgrounding (external interruption). The time_spent_seconds parameter records the total duration the user spent on the dashboard during this single visit, measured from the corresponding preg_dashboard_screen_shown event. This event is not marked as a Key Event but is essential for understanding session quality, engagement depth, and content effectiveness. From a business perspective, it answers several important questions: How long do users spend on the pregnancy dashboard per visit, and does this align with the PRD's goal of 'fast today value within 60 seconds'? If median dwell time is under 10 seconds, users may not be finding value; if over 3 minutes, the dashboard may be overwhelming. What is the most common exit method — do users navigate deeper into content (positive engagement) or bounce back or background the app (potential disengagement)? Does time_spent_seconds correlate with downstream actions like symptom logging or checklist completion? Are there specific pregnancy weeks or trimesters where time spent drops significantly, suggesting content gaps or fatigue? All pregnancy users who view the dashboard will trigger this event upon exit, making it universal for the pregnancy user base. Synonyms and related concepts include: dashboard leave, screen exit, page departure, session end on dashboard, bounce from dashboard, navigation away, dashboard time-on-screen, dwell time measurement, screen dismissal, dashboard session end. This event fires after preg_dashboard_screen_shown and any intermediate interaction events (scroll depth, card views, tip swipes, and taps). It precedes whatever screen the user navigates to next, such as preg_week_details_screen_shown, preg_symptom_log_screen_shown, preg_settings_screen_shown, or the app going to background state.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_loading_shown, is fired when the loading state — such as a spinner, skeleton placeholder, or loading animation — is displayed on the pregnancy dashboard while content is being fetched. It triggers at the moment the dashboard begins rendering its loading UI but before actual pregnancy content (baby card, weekly info, tips, action cards) has loaded and appeared. This event fires every time the dashboard needs to fetch data, including on first load after navigation, on pull-to-refresh if the user manually refreshes, when returning to the screen if cached content has expired, and on app resume if the dashboard content needs to be re-fetched from the server. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event, but it serves a critical performance monitoring purpose. The PRD explicitly requires the dashboard to 'load fast' and specifies that 'dashboard load' must be performant as a non-functional requirement. This event acts as the start timestamp for measuring perceived load time. From a business perspective, it answers important questions: How often do users see loading states, and is the frequency increasing over time (suggesting backend degradation)? When paired with preg_dashboard_content_loaded, what is the actual perceived load time (load_time_ms)? Are there time-of-day patterns, network conditions, or geographic regions where loading is notably slower? If this event fires but preg_dashboard_content_loaded never fires for the same session, it indicates a failed load, timeout, or crash — which is a serious issue that directly impacts retention and the user's ability to get their 'today value.' All pregnancy users trigger this event whenever the dashboard initiates a data load. Synonyms and related concepts include: loading spinner shown, skeleton screen displayed, content loading indicator, dashboard fetch start, page loading state, progress indicator, loading placeholder, content pending, data loading UI. This event fires immediately after or concurrent with preg_dashboard_screen_shown and is followed by either preg_dashboard_content_loaded (success) or preg_error_state_shown (failure). The time difference between this event and content_loaded is the user-perceived load duration.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_content_loaded, is fired when the dashboard content finishes loading and is fully rendered and visible for the user to interact with. It triggers at the precise moment the loading state disappears and actual pregnancy content — the baby development card, weekly information, daily tips, action cards, and all other dashboard components — becomes visible and interactive. It carries the parameters source_screen (recording where the user navigated from), load_time_ms (Time taken to load content in milliseconds, for example 200, 500, 1500), week_number (Current pregnancy week, for example 12, 20, 36), cards_count (Number of dashboard cards displayed, for example 3, 5, 7). The load_time_ms parameter is the primary performance measurement, capturing the duration from the start of the data request to full render completion in milliseconds. The cards_count parameter records how many dashboard cards were successfully rendered, which helps identify if content is missing or if certain pregnancy weeks produce fewer or more cards than expected. This is not a Key Event but is essential for performance monitoring and SLA tracking. The PRD mandates that the dashboard loads fast and that logging completes under 2 seconds. From a business perspective, this event answers: What is the p50 (median), p90, and p99 load time for the dashboard across the user base? Does load time degrade as pregnancy progresses (more content per week may increase payload)? Are there specific device types, OS versions, or network conditions where load times exceed acceptable thresholds? Is there a measurable correlation between slow load times (e.g., &gt;3 seconds) and higher exit rates or lower retention? What is the average number of cards rendered, and does it vary by trimester? All pregnancy users trigger this event on every successful dashboard load. If loading fails, this event does not fire — preg_error_state_shown fires instead. Synonyms and related concepts include: content render complete, page fully loaded, dashboard ready, content visible, first contentful paint, dashboard render time, performance metric, load completion, data display ready, page render finished. This event fires after preg_dashboard_loading_shown and before any user interaction events like preg_dashboard_scroll_depth, preg_dashboard_baby_card_viewed, preg_dashboard_detail_card_viewed, and any tap events on the dashboard.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_scroll_depth, is fired when the user scrolls through the pregnancy dashboard and reaches specific scroll depth milestones, typically at 25%, 50%, 75%, and 100% of the total scrollable content area. Each milestone fires only once per dashboard session — if the user scrolls down to 75%, scrolls back up, and scrolls down past 75% again, the 75% milestone does not re-fire in that session. A new session (navigating away and returning) resets the milestones. It carries the parameters source_screen (recording where the user navigated from), scroll_percent (Scroll depth milestone reached, for example 25, 50, 75, 100), week_number (Current pregnancy week, for example 12, 20, 36). The scroll_percent parameter records which milestone was crossed, and week_number provides context for which week's content was being scrolled through. This is not a Key Event, but it is a vital engagement quality metric that goes beyond simple screen views. From a business perspective, it answers: How far down the dashboard do users scroll on average? What percentage of users reach the bottom (100%) of the dashboard? Are dashboard cards placed in the lower portion being missed entirely by a majority of users? Does scroll depth vary by trimester or pregnancy week — for instance, do third-trimester users scroll less because they are more experienced, or more because they have increased anxiety? Is there a correlation between deeper scroll depth and higher action completion rates (logging, checklist, AI usage)? This data directly informs content prioritization and dashboard layout decisions. If analytics show that 60% of users only reach 50% scroll depth, then any important content or CTAs placed below the halfway point need to be promoted higher or the dashboard needs to be condensed. The PRD emphasizes 'no wall of text' and that the dashboard should be readable — scroll depth data validates whether these goals are being met. All pregnancy users who scroll the dashboard trigger this event. Users who do not scroll at all (only viewing above-the-fold content) will not trigger any scroll depth events, which is itself informative. Synonyms and related concepts include: scroll tracking, page depth, content consumption depth, fold visibility, below-the-fold engagement, scroll percentage, viewport reach, content discovery depth, scroll progress, page scroll analytics. This event fires after preg_dashboard_content_loaded as the user begins browsing, interleaved with impression events like preg_dashboard_baby_card_viewed, preg_dashboard_detail_card_viewed, and preg_dashboard_daily_tip_viewed. It fires before preg_dashboard_screen_exited.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_baby_card_viewed, is fired when the baby illustration card enters the visible viewport on the pregnancy dashboard. This is an impression-type event that triggers based on visibility — it fires when the card scrolls into view or is already visible in the initial viewport on page load. It does not require a tap or interaction, only that the card is rendered and visible to the user. It carries the parameters source_screen (recording where the user navigated from), week_number (Current pregnancy week, for example 12, 20, 36), position (Position of the card in the list, for example 0, 1). The position parameter records where the baby card sits in the dashboard layout. The baby development card is a key emotional anchor of the pregnancy module. The PRD describes it as a core dashboard component showing a 'baby development snapshot' with a size analogy (such as comparing baby's size to a fruit) and key developmental milestones for the current week. This content is what many pregnancy app users look forward to most each week. This is not a Key Event, but it measures exposure to one of the most emotionally engaging and retention-driving pieces of content on the dashboard. From a business perspective, it answers: What percentage of dashboard visits include viewing the baby card? Is the baby card placed optimally in the layout — if few users see it, it may be positioned too far down and should be elevated? Does baby card visibility correlate with longer session times, higher retention, or more downstream actions? Which pregnancy weeks generate the most baby card impressions (indicating those weeks have higher engagement)? All pregnancy users who view the dashboard and have the baby card within their visible viewport trigger this event. Synonyms and related concepts include: baby illustration impression, baby development card view, fetal development card visible, baby size card impression, baby growth visualization seen, pregnancy milestone card impression, baby image card exposure, fetal growth card seen. This event fires after preg_dashboard_content_loaded during the dashboard browsing session and may be followed by preg_dashboard_see_baby_tap or preg_dashboard_baby_size_tap if the user taps on the card to explore further.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_trimester_viewed, is fired when the trimester progress card becomes visible in the viewport on the pregnancy dashboard. It is an impression event triggered by the card entering the visible area, whether on initial load or through user scrolling. It carries the parameters source_screen (recording where the user navigated from), trimester (Current trimester displayed, for example 1, 2, 3), days_to_birth (Remaining days until estimated birth, for example 264, 180, 30). The days_to_birth parameter provides a countdown perspective showing how many days remain until the estimated due date, which is valuable for segmenting user behavior by proximity to delivery. This is not a Key Event, but it measures visibility of the trimester progress indicator, which is a core orientation element. The PRD's vision states that users should immediately see 'where they are (Week X, trimester, baby development)' when opening the app. The trimester card fulfills this orientation need. From a business perspective, it answers: How many users see the trimester progress card each session? Does awareness of the countdown (days_to_birth) correlate with higher engagement in preparation features like checklists and appointments? Is the trimester card driving navigation to the detailed trimester content? Do users in the third trimester (with fewer days_to_birth) show different engagement patterns? All pregnancy users trigger this when the trimester card is visible in their viewport. Synonyms and related concepts include: trimester progress impression, pregnancy progress card view, countdown card visible, trimester tracker seen, pregnancy timeline card impression, due date countdown visibility, pregnancy stage indicator, progress visualization seen. This event fires during dashboard browsing after content loads and may be followed by preg_dashboard_trimester_tap if the user interacts with the card.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_trimester_tap, is fired when the user taps on the trimester progress card or the 'See More' link within that card on the pregnancy dashboard. It carries the parameters source_screen (recording where the user navigated from), trimester (Trimester displayed, for example 1, 2, 3), week_number (Current pregnancy week, for example 12, 20, 36). This is not a Key Event, but it tracks intentional navigation from the high-level dashboard into deeper trimester-specific educational content. The PRD describes trimester details as containing articles, screening guidance, comfort items, and birth planning prompts organized by trimester. From a business perspective, it answers: What proportion of users who see the trimester card actually tap into it (view-to-tap conversion)? Which trimester generates the most curiosity and exploration — are first-trimester users more actively seeking information, or do third-trimester users tap more often due to preparation needs? Do first-time pregnant users (the 'Anxious Planner' persona) tap this more frequently than experienced mothers ('Busy Mum' persona)? All pregnancy users who tap the trimester card trigger this event. Synonyms and related concepts include: trimester card click, see more trimester tap, trimester detail navigation, pregnancy progress tap, trimester expansion, trimester drill-down, trimester info tap. This event fires after preg_dashboard_trimester_viewed (the impression event) and leads directly to preg_trimester_details_shown where the full trimester content is displayed.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_log_symptoms_tap, is fired when the user taps the 'Log Symptoms' button on the pregnancy dashboard. This button is a prominent call-to-action card on the dashboard designed to encourage daily symptom tracking. It carries the parameters source_screen (recording where the user navigated from), week_number (Current pregnancy week, for example 12, 20, 36), button_label (Label of the button tapped, for example log_symptoms). This is not formally marked as a Key Event in the instrumentation spec but represents one of the single most critical user actions on the dashboard. The PRD identifies symptom logging as a core P0 feature and specifies that the dashboard should provide 'one-tap access to log, checklist, appointments.' The 'Log Symptoms' button is the primary entry point into the symptom logging flow from the most-visited screen in the pregnancy module. From a business perspective, this event answers vital questions: What is the daily symptom logging click-through rate (CTR) from the dashboard, and how does it trend over time? How does this vary across pregnancy weeks — does logging interest peak during weeks with more uncomfortable symptoms (e.g., first-trimester nausea weeks, third-trimester discomfort weeks)? What is the conversion rate from this tap to a completed symptom log (preg_symptom_log_submitted) — a large drop-off suggests friction in the logging flow? Is the button sufficiently prominent — if CTR is consistently low, the button may need repositioning, resizing, or copy changes? This event feeds directly into multiple PRD KPIs: the activation metric 'Symptom log completed in first 48 hours,' the engagement metric 'Symptom logs per week,' and the retention funnel 'Symptom log submitted -&gt; return next day/week.' All pregnancy users who have reached the dashboard and interact with the symptom logging CTA trigger this event. It may be triggered by all four user personas, though the 'High concern Symptom Checker' and 'Anxious Planner' are most likely frequent triggers. Synonyms and related concepts include: symptom log CTA click, log symptoms button press, quick log tap, symptom tracker entry, daily log start from dashboard, symptom recording entry point, log health data tap, symptom button interaction. This event fires after the dashboard has loaded and the user has identified the logging button. It leads directly to preg_symptom_log_screen_shown. The downstream completion event is preg_symptom_log_submitted.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_see_baby_tap, is fired when the user taps the 'See Your Baby' button on the pregnancy dashboard card, navigating to a more detailed view of baby development for the current week. It carries the parameters source_screen (recording where the user navigated from), week_number (Current pregnancy week, for example 12, 20, 36), button_label (Label of the button tapped, for example see_your_baby). This is not a Key Event, but it captures user curiosity about fetal development, which is one of the strongest emotional hooks in any pregnancy app. The PRD describes the baby development snapshot as a core dashboard component, and this tap represents the user's desire to see more than the summary. From a business perspective, it answers: How many users want more baby detail beyond the dashboard snapshot? Which pregnancy weeks generate the most baby-related curiosity (e.g., weeks when major organs develop, or when the baby starts to look more human)? Does engagement with baby content correlate with overall retention and session frequency? Is baby content a sufficient hook to bring users back weekly? All pregnancy users who tap this button trigger the event. The 'Anxious Planner' persona is likely the most frequent trigger. Synonyms and related concepts include: view baby button click, baby development CTA, see baby details, fetal development view, baby illustration tap, baby growth button press, view fetal progress, baby detail navigation. This event fires after preg_dashboard_baby_card_viewed (the impression event) and leads to preg_week_details_screen_shown where detailed week-by-week baby development content is shown.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_see_details_tap, is fired when the user taps the 'See Details' link on the pregnancy main dashboard card, navigating to an expanded view of their current pregnancy week's information. It carries the parameters source_screen (recording where the user navigated from), week_number (Current pregnancy week, for example 12, 20, 36). This is not a Key Event, but it tracks navigation from the condensed dashboard summary into the full weekly content experience. The 'See Details' link serves as a secondary navigation path — while the dashboard shows a high-level snapshot, tapping this reveals the complete week-by-week guide including body changes, emotional wellbeing tips, actionable focus items, and safety information. From a business perspective, it answers: Do users want more detail than the dashboard provides? Is the dashboard summary sufficient for most users, or is there strong demand for deeper content? Which pregnancy weeks drive the most detail-seeking behavior — early weeks when everything is new, or later weeks when preparation becomes urgent? All pregnancy users who tap the 'See Details' link trigger this event. Synonyms and related concepts include: view more details, pregnancy detail link click, expand dashboard info, week detail navigation, read more about this week, dashboard detail drill-down, see full week info. This event fires after the dashboard loads and typically leads to preg_week_details_screen_shown.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_detail_card_tap, is fired when the user taps on a pregnancy detail card in the horizontal carousel on the dashboard. The carousel contains action-oriented cards like 'Log your symptoms,' 'Weekly guide,' 'Checklist,' and other recommended activities. It carries the parameters source_screen (recording where the user navigated from), card_id (Unique identifier of the detail card, for example log_symptoms, weekly_guide, checklist), card_title (Title of the detail card, for example Log your symptoms, Weekly guide, Checklist), position (Position of the card in the carousel, for example 0, 1, 2, 3). The card_id identifies which specific card was tapped (log_symptoms, weekly_guide, checklist, etc.), card_title provides the user-facing label, and position records the card's placement in the carousel (0-indexed). This is not a Key Event, but it is crucial for understanding which dashboard action recommendations drive the most user engagement. The PRD specifies the dashboard should show 'Your plan: 1-3 recommended actions (max 3),' and these carousel cards implement that recommendation system. From a business perspective, it answers: Which action cards get the most taps — is symptom logging more popular than checklists? Does card position in the carousel significantly affect tap rate (first-position bias)? Are certain card types consistently ignored, suggesting they should be removed or redesigned? Should the carousel card order be personalized based on user behavior patterns? This event directly feeds the PRD's 'Daily plan CTR' engagement KPI. All pregnancy users who interact with the horizontal carousel action cards trigger this event. Synonyms and related concepts include: action card click, carousel card tap, recommended action tap, plan card selection, dashboard shortcut tap, horizontal card interaction, suggested action click, quick action card, daily plan card tap. This event fires after preg_dashboard_detail_card_viewed (the impression event) and leads to the corresponding destination screen based on card_id — for example, preg_symptom_log_screen_shown for log_symptoms, preg_week_details_screen_shown for weekly_guide, or a checklist view for checklist cards.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_detail_card_viewed, is fired when a pregnancy detail card becomes visible in the horizontal carousel viewport on the dashboard. It is an impression event that triggers automatically when the card scrolls into the visible area of the carousel or is already visible upon initial load. It does not require any user tap or interaction. It carries the parameters source_screen (recording where the user navigated from), card_id (Unique identifier of the detail card, for example log_symptoms, weekly_guide, checklist), position (Position of the card in the carousel, for example 0, 1, 2, 3). This is not a Key Event, but it is the impression counterpart to preg_dashboard_detail_card_tap. Together, these two events form a view-to-tap ratio that measures the effectiveness of each carousel card at converting passive exposure into active engagement. From a business perspective, it answers: How many users see each carousel card? Do users scroll through the entire carousel, or do most only see the first card? What is the impression-to-click ratio for each card_id — a low ratio means many users see the card but few tap it, suggesting the card content or design needs improvement? Are certain cards never scrolled to, indicating they should be repositioned? All pregnancy users who have the carousel cards visible in their viewport trigger this event. Synonyms and related concepts include: carousel card impression, action card visibility, detail card exposure, recommended action seen, horizontal scroll card view, plan card impression. This event fires during dashboard browsing after content loads and may precede preg_dashboard_detail_card_tap if the user interacts.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_daily_tip_viewed, is fired when a daily tip is displayed in the ViewPager — a swipeable carousel of tips — on the pregnancy dashboard. It triggers each time a tip page becomes the active and visible page in the pager, whether from the initial page load showing the first tip or from the user swiping to subsequent tips. It carries the parameters source_screen (recording where the user navigated from), tip_id (Unique identifier of the tip, for example tip_001, tip_042), position (Position of the tip in the pager, for example 0, 1, 2), week_number (Current pregnancy week, for example 12, 20, 36). The tip_id uniquely identifies which tip content is being shown, and position records which page of the pager is active (0 for the first tip, 1 for the second, etc.). This is not a Key Event, but daily tips are a core engagement mechanism for the pregnancy module. The PRD describes the 'Today card' as showing a recommended action and a daily tip, forming part of the 'daily check-in' journey that should take only 10-30 seconds. From a business perspective, it answers: What percentage of dashboard visits result in at least one tip view? Which specific tips (by tip_id) get the most impressions? Do users engage with multiple tips by swiping, or only see the first one? Are tips tailored to the pregnancy week resonating (high view-to-action conversion), or are they generic and ignored? All pregnancy users who view the dashboard and have the tip section visible trigger this event. Synonyms and related concepts include: daily tip impression, today's tip visible, pregnancy tip displayed, wellness tip view, daily insight card shown, tip of the day impression, daily recommendation seen. This event fires after preg_dashboard_content_loaded and may be followed by preg_dashboard_daily_tip_swiped if the user swipes to see more tips.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_daily_tip_swiped, is fired when the user swipes between daily tips in the ViewPager carousel on the pregnancy dashboard, actively navigating from one tip to another. It triggers on each completed swipe gesture that results in a page change. It carries the parameters source_screen (recording where the user navigated from), direction (Swipe direction, for example left, right), from_position (Position before swipe, for example 0, 1, 2), to_position (Position after swipe, for example 1, 2, 0). The direction parameter records whether the user swiped left (forward) or right (backward), while from_position and to_position record the specific page transition. This is not a Key Event, but it measures active engagement with tip content that goes beyond passive viewing. A swipe indicates the user read or at least noticed the current tip and wanted to see what else was available. From a business perspective, it answers: How many tips do users browse per dashboard session? Do users swipe in both directions, exploring back and forth, or only forward? Is the number of tips optimal — if users rarely swipe, one tip per day may be sufficient; if they consistently swipe through all available tips, the content team should produce more? Which tip positions see the most swipe activity, and does swipe rate decline as position increases? All pregnancy users who actively swipe through the tip carousel trigger this event. Synonyms and related concepts include: tip carousel swipe, daily tip pagination, tip pager interaction, swipe through tips, tip browsing, horizontal tip scroll, tip navigation gesture, tip carousel navigation. This event fires after preg_dashboard_daily_tip_viewed (for the initial tip) and triggers a new preg_dashboard_daily_tip_viewed event for the newly visible tip after the swipe completes.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_baby_size_tap, is fired when the user taps on the baby approximate size card on the pregnancy dashboard. It carries the parameters source_screen (recording where the user navigated from), baby_size (Size analogy displayed, for example potato, avocado, watermelon), week_number (Current pregnancy week, for example 12, 20, 36). The baby_size parameter records the specific size analogy that was displayed when the user tapped — such as 'potato,' 'avocado,' or 'watermelon' — which is a beloved pregnancy app convention where baby's size is compared to familiar objects. This is not a Key Event, but the baby size analogy is one of the most emotionally resonant, memorable, and shareable pieces of content in any pregnancy app. Many users specifically look forward to seeing each week's new size comparison. From a business perspective, it answers: How engaging are the size analogies — does tapping indicate delight and curiosity? Which specific analogies (e.g., which weeks) drive the most interest? Does tapping the baby size card lead to deeper content engagement? Could baby size content become a hook for future social sharing features (e.g., 'Your baby is the size of an avocado — share with friends')? All pregnancy users who tap the baby size card trigger this event. Synonyms and related concepts include: baby size comparison tap, fruit size analogy click, baby growth comparison, fetal size card interaction, how big is my baby tap, size milestone tap, baby size analogy engagement. This event fires from the dashboard after preg_dashboard_baby_card_viewed and may lead to preg_week_details_screen_shown or a detailed baby development view.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_checkup_card_tap, is fired when the user taps on the 'Add your reports' or 'Did you have a checkup' prompt card on the pregnancy dashboard. It carries the parameters source_screen (recording where the user navigated from), button_label (Label of the CTA, for example add_reports). This is not a Key Event, but it represents engagement with the medical appointment and report tracking features. The PRD includes an appointments tracker as a P1 feature with capabilities to add appointments, set reminders, and receive 'questions to ask' suggestions per appointment type. This dashboard card serves as a proactive prompt encouraging users to record their medical interactions. From a business perspective, it answers: How many users engage with the checkup recording prompt? Is the dashboard an effective channel for driving appointment tracking adoption? Does prompting after likely checkup timing (e.g., known scan weeks) increase engagement? All pregnancy users who see and tap the checkup card trigger this event. Synonyms and related concepts include: checkup prompt tap, add reports button click, medical report card tap, appointment card interaction, doctor visit prompt, checkup reminder tap, medical tracking entry point, health record prompt. This event fires from the dashboard and leads to the appointment creation or report addition flow.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_kick_counter_tap, is fired when the user taps on the Kick Counter card on the pregnancy dashboard. It carries the parameters source_screen (recording where the user navigated from), week_number (Current pregnancy week, for example 28, 32, 38). The sample values for week_number (28, 32, 38) indicate this card is only shown in later pregnancy weeks, consistent with the PRD's specification that the kick counter is available 'only from a configured week (default later pregnancy; precise week thresholds should be clinically reviewed and configurable).' This is not a Key Event, but it is the primary entry point for the kick counter feature from the most visited screen. The PRD describes kick counting as a P1 feature that includes start session, tap counts, duration tracking, session notes, trend display, and educational content about fetal movement. From a business perspective, it answers: What percentage of late-pregnancy users engage with the kick counter via the dashboard card? At which specific week do users first show interest in kick counting? Is the dashboard card effective at driving kick counter adoption compared to other entry points? Does kick counter usage from the dashboard increase as users get closer to their due date? Only pregnancy users in later weeks who have the kick counter card displayed on their dashboard trigger this event. Users in earlier pregnancy weeks will not see this card and cannot trigger this event. Synonyms and related concepts include: kick counter card click, baby movement tracker tap, fetal movement counter entry, kick tracking start from dashboard, baby kicks card interaction, movement counter CTA, kick counter access. This event fires from the dashboard and leads directly to preg_kick_counter_screen_shown.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_health_checker_viewed, is fired when the health checker or PCOS self-assessment card becomes visible on the pregnancy dashboard viewport. It is an impression event that triggers based on the card entering the user's visible screen area. It carries the parameters source_screen (recording where the user navigated from), assessment_type (Type of health assessment, for example pcos). The assessment_type parameter (e.g., 'pcos') identifies which type of health self-assessment is being presented. This is not a Key Event. The health checker card appears to offer self-assessment tools for specific health conditions, and its presence on the pregnancy dashboard suggests cross-module health awareness features that extend beyond standard pregnancy tracking. From a business perspective, it answers: How many pregnancy users are exposed to the health checker card? What is the impression-to-tap conversion rate? Is this card positioned effectively — too high may feel intrusive, too low may be unseen? Is a PCOS assessment relevant to pregnant users, or does it feel out of context? All pregnancy users who scroll to or see the health checker card position trigger this event. Synonyms and related concepts include: health assessment card impression, PCOS checker card visible, self-assessment card view, health screening prompt seen, condition checker exposure, health risk assessment shown. This event fires during dashboard browsing and may be followed by preg_dashboard_health_checker_tap if the user engages.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_health_checker_tap, is fired when the user taps 'Check your symptoms' on the health checker card displayed on the pregnancy dashboard. It carries the parameters source_screen (recording where the user navigated from), assessment_type (Type of health assessment, for example pcos), button_label (Label of the CTA, for example check_your_symptoms). This is not a Key Event, but it tracks active interest in health self-assessment tools during pregnancy. From a business perspective, it answers: What percentage of users who see the health checker card interact with it? Is there a specific trimester or pregnancy week where interest in self-assessment is highest? Does engagement with health assessments correlate with more frequent symptom logging? All pregnancy users who tap the health checker CTA trigger this event. Synonyms and related concepts include: symptom checker tap, health assessment start, PCOS self-check click, condition assessment begin, health screening CTA click, health risk check tap. This event fires after preg_dashboard_health_checker_viewed and leads to the health checker or assessment flow screen.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_ai_chatbot_tap, is fired when the user taps the AI chatbot floating action button (FAB) icon on the pregnancy dashboard, opening the AI assistant conversation interface. It carries the parameters source_screen (recording where the user navigated from), week_number (Current pregnancy week, for example 12, 20, 36). This is not a Key Event, but it captures the primary entry point into the 'Ask Femverse' AI assistant from the dashboard. The PRD designates the AI assistant as a core P0 feature with capabilities including explaining symptoms in general educational terms, summarizing user logs from the last 7 days, suggesting safe actions, recommending content and checklists, and providing trimester-specific guidance — all while adhering to strict guardrails: no diagnosis, mandatory disclaimers for symptom questions, triage template triggers when risk patterns appear, and no medication advice except generic suggestions paired with 'consult clinician.' From a business perspective, it answers: What is the AI chatbot adoption rate from the dashboard? At which pregnancy weeks do users seek AI assistance most frequently — early pregnancy (uncertainty and anxiety) vs late pregnancy (preparation and concern)? Does AI usage correlate with higher retention or session frequency? How does the floating icon compare to the AI prompt suggestions (preg_dashboard_ai_prompt_tap) as an entry point? This feeds the PRD KPI 'AI assistant usage + helpfulness rating.' All pregnancy users who tap the floating AI chatbot icon trigger this event. The 'High concern Symptom Checker' persona is likely the heaviest user of this feature. Synonyms and related concepts include: AI assistant tap, chatbot icon click, Ask Femverse entry, virtual assistant open, AI helper tap, pregnancy chatbot launch, floating action button tap, AI conversation start, chatbot FAB click. This event fires from the dashboard and leads to the AI chatbot conversation screen. Downstream related events include ai_preg_query_submitted (when the user sends a message) and ai_response_rated (when the user rates the AI's response as helpful or not).</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_ai_prompt_shown, is fired when the AI prompt suggestion card is shown on the pregnancy dashboard, presenting the user with a pre-written question they can tap to ask the AI assistant. It carries the parameters source_screen (recording where the user navigated from), prompt_text (Text of the suggested prompt, for example What should I eat this week?, Is this normal?). The prompt_text records the specific suggested question displayed, such as 'What should I eat this week?' or 'Is this normal?' These prompts are designed to lower the barrier to AI engagement by showing users what kinds of questions they can ask. This is an impression event and not a Key Event. The PRD specifies that the dashboard should include 'Ask Femverse (AI): prompt + suggested questions' as a component. From a business perspective, it answers: Are AI prompts being seen by users on the dashboard? Which prompts are shown most frequently (rotation effectiveness)? Does prompt exposure correlate with AI adoption — do users who see prompts use the chatbot more than those who don't? This helps the team optimize prompt selection, wording, and placement for maximum AI engagement. All pregnancy users who have the AI prompt card visible on their dashboard trigger this event. Synonyms and related concepts include: AI suggestion impression, chatbot prompt displayed, suggested question visible, AI prompt card view, Ask Femverse suggestion shown, pre-filled question shown. This event fires during dashboard browsing after content loads and may be followed by preg_dashboard_ai_prompt_tap if the user interacts with the suggestion.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_ai_prompt_tap, is fired when the user taps on one of the AI prompt suggestions displayed on the pregnancy dashboard, initiating a conversation with the AI assistant using the pre-written question. It carries the parameters source_screen (recording where the user navigated from), prompt_text (Text of the prompt tapped, for example What should I eat this week?, Is this normal?). This is not a Key Event, but it captures a specific, curated path into the AI assistant — the user didn't just open the chatbot generically, they selected a pre-suggested question that resonated with their current need. This is a lower-friction entry compared to the chatbot FAB tap because the user doesn't have to formulate their own question. From a business perspective, it answers: Which suggested prompts drive the most engagement — is 'Is this normal?' more compelling than 'What should I eat this week?'? Is the prompt-based entry more effective than the generic chatbot icon at driving AI usage? What topics are users most curious about at different pregnancy stages? This data directly informs the personalisation engine — prompts that get tapped frequently should be shown more often and in more prominent positions, and the content team can prioritize creating deeper educational content around popular question topics. All pregnancy users who tap a suggested AI prompt trigger this event. Synonyms and related concepts include: AI suggestion tap, suggested question click, chatbot prompt interaction, pre-filled question tap, Ask Femverse prompt selection, AI question shortcut. This event fires after preg_dashboard_ai_prompt_shown and leads to the AI chatbot screen with the selected prompt pre-filled. The downstream event is ai_preg_query_submitted.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_insight_card_tap, is fired when the user taps the personalized pregnancy insight card on the main dashboard. It carries the parameters source_screen (recording where the user navigated from), card_type (Type of insight card, for example pregnancy, calendar). The card_type distinguishes between different insight categories — for example, pregnancy-specific pattern insights versus calendar-related insights. This is not a Key Event, but personalized insights are a key differentiator for Femverse. The PRD describes a pattern detection system that identifies correlations in user data — for example, nausea peaking at specific times, back pain spiking after activity days, or poor sleep correlating with heartburn logs. The insights card surfaces these patterns to the user. From a business perspective, it answers: Are personalized insights driving engagement? Which types of insight cards (by card_type) resonate most? Do users who interact with insights have higher retention or take more recommended actions? Is the personalisation engine producing insights that feel valuable? All pregnancy users who tap an insight card trigger this event. Synonyms and related concepts include: personalized insight click, pregnancy pattern card tap, your insights interaction, tailored recommendation tap, personal data insight click, AI-generated insight tap. This event fires from the dashboard and leads to a detailed insight view or related screen.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_calendar_card_tap, is fired when the user taps the pregnancy calendar card located in the personalized insight horizontal scroll section of the dashboard. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event, but it tracks a specific entry point into the pregnancy calendar from the dashboard's insight area. The calendar card may show upcoming milestones, recent symptom activity, or gestational age information that entices the user to explore the full calendar view. From a business perspective, it answers: How many users access the calendar from the dashboard insights section? Is the calendar card positioned effectively in the horizontal scroll — does its position affect tap rates? Do users who access the calendar from insights interact with it differently than those who use the toolbar? All pregnancy users who tap the calendar card trigger this event. Synonyms and related concepts include: calendar shortcut tap, pregnancy calendar entry from insights, calendar card click, pregnancy timeline tap, calendar access from dashboard. This event fires after dashboard content loads and leads to preg_calendar_preview_shown.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_prompt_shown, is fired when the 'Do you want to track pregnancy' prompt card is shown on the dashboard. This is a special onboarding or mode-selection prompt that appears for users who have not yet confirmed whether they want to activate pregnancy tracking. It fires as an impression event when the prompt card becomes visible. It may appear for users who are browsing the dashboard without having committed to the pregnancy module, or for period-module users who are being offered pregnancy tracking. This is not a Key Event, but it captures a critical decision point in the user journey. The PRD states that pregnancy and period modules are mutually exclusive, so this prompt represents the fork between two fundamentally different app experiences. From a business perspective, it answers: How many users see the pregnancy tracking prompt? What is the conversion rate from seeing this prompt to selecting an option (preg_dashboard_prompt_option_tap)? Are users ignoring this prompt — if so, should it be redesigned, made more prominent, or shown at a different time? How many exposures does it take before a user acts on it? This event is triggered by users in an ambiguous or transitional state regarding pregnancy tracking — they may have installed the app but not selected a module, or they may be being cross-promoted from the period module. Synonyms and related concepts include: pregnancy mode prompt impression, track pregnancy question shown, module selection prompt, pregnancy opt-in card, pregnancy mode discovery prompt, pregnancy activation prompt. This event fires on the dashboard and is followed by preg_dashboard_prompt_option_tap if the user makes a selection.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_prompt_option_tap, is fired when the user selects an option on the pregnancy tracking prompt card, responding to the question of whether they want to track pregnancy. It carries the parameters source_screen (recording where the user navigated from), option_selected (Option the user selected, for example yes, no, want_to_be). The option_selected values include 'yes' (the user confirms they want to track pregnancy), 'no' (the user does not want pregnancy tracking), and 'want_to_be' (the user is trying to conceive, representing a distinct user segment). This is marked as a Key Event because it represents a major user self-segmentation decision that determines the entire subsequent app experience. The PRD explicitly states that pregnancy and period modules are mutually exclusive, so this choice fundamentally redirects the user's journey and the content they receive. From a business perspective, it answers critical questions: What percentage of users who see the pregnancy prompt opt in to pregnancy tracking? What share of users are trying to conceive ('want_to_be') — is this a large enough segment to warrant a dedicated TTC (trying-to-conceive) experience? What is the refusal rate ('no'), and does it indicate that the prompt is being shown to the wrong audience or at the wrong time? Does the distribution of selections align with the app's user acquisition and marketing strategy? This event feeds directly into the activation metric 'Pregnancy onboarding completion rate' from the PRD. Users who see the pregnancy tracking prompt and interact with it trigger this event. Synonyms and related concepts include: pregnancy mode selection, tracking opt-in decision, pregnancy module choice, module switch decision, pregnancy confirmation tap, conception mode selection, TTC selection, pregnancy opt-in response. This event fires after preg_dashboard_prompt_shown. If 'yes' is selected, it leads to the pregnancy onboarding flow starting with preg_personalize_screen_shown or preg_due_date_method_shown. If 'want_to_be' is selected, it may lead to a conception or fertility tracking flow. If 'no' is selected, the user remains in their current module.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_empty_state_shown, is fired when the pregnancy dashboard displays an empty state, meaning the user has navigated to the pregnancy section but has not yet completed the required pregnancy setup process — specifically, they have not entered their pregnancy dates (LMP or EDD). It fires as an impression event every time this empty state screen is rendered. This is not a Key Event, but it identifies a critical friction point in the user journey. From a business perspective, it answers: How many users land on the pregnancy dashboard in an incomplete setup state? Is there a significant drop-off between selecting pregnancy mode and finishing the date entry onboarding? How long do users remain in the empty state before either completing setup or abandoning? Is the empty state CTA clear enough to guide users to complete onboarding? Users who have entered the pregnancy module path but haven't finished onboarding (specifically haven't provided a due date or LMP date) will see this empty state and trigger this event. This could include users who abandoned onboarding midway, users who navigated directly to the pregnancy section without going through the guided flow, or users experiencing edge cases in the module switching process. Synonyms and related concepts include: empty dashboard shown, setup incomplete state, blank pregnancy screen, onboarding not finished, pregnancy setup required state, no data state, first-run empty state, unconfigured dashboard. This event fires instead of the normal dashboard content load sequence (preg_dashboard_loading_shown and preg_dashboard_content_loaded are not expected to fire). It may be followed by preg_dashboard_empty_add_tap if the user initiates setup from the empty state.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_empty_add_tap, is fired when the user taps the add button or setup CTA on the pregnancy empty state card, initiating the pregnancy configuration flow. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event, but it represents recovery from the empty state — the user is choosing to start or resume pregnancy setup after seeing the incomplete dashboard. From a business perspective, it answers: What percentage of users who see the empty state proceed to set up their pregnancy? Is the empty state CTA sufficiently clear, compelling, and well-positioned? How does this conversion rate compare to users who enter setup through the standard onboarding flow? Users who are on the empty pregnancy dashboard and actively choose to begin setup trigger this event. Synonyms and related concepts include: start setup from empty state, add pregnancy tap, begin onboarding from dashboard, setup CTA click, empty state action button, pregnancy configuration start, complete setup tap. This event fires after preg_dashboard_empty_state_shown and leads to the onboarding flow, typically starting with preg_due_date_method_shown or preg_personalize_screen_shown.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_milestone_viewed, is fired when a pregnancy milestone card becomes visible to the user, either on the main dashboard or on the calendar preview screen. It carries the parameters source_screen (recording where the user navigated from), milestone_type (Type of milestone, for example milestone), milestone_title (Title of the milestone, for example First trimester complete, Anatomy scan). The milestone_title captures the specific milestone content, such as 'First trimester complete,' 'Anatomy scan,' or other significant pregnancy events. This is not a Key Event, but milestones are a key emotional and motivational element in the pregnancy journey. The PRD's memory system explicitly tracks 'important events: trimester change, scan dates, symptom spikes, week milestones,' recognizing that these moments are psychologically significant for users. Milestones serve as the 'weekly anchors' described in the PRD that help drive habit formation and give users a reason to return to the app. From a business perspective, it answers: Are milestone cards being seen by users? Which milestones generate the most engagement or emotional response? Do milestone views correlate with increased session time, more logging, or sharing behavior? Do users who see milestones have higher weekly return rates? All pregnancy users who have a milestone card visible in their viewport trigger this event. The source_screen can be either the main dashboard or the calendar preview. Synonyms and related concepts include: pregnancy milestone impression, achievement card seen, pregnancy progress milestone visible, developmental milestone view, pregnancy celebration card, journey milestone impression, pregnancy achievement exposure. This event fires during dashboard or calendar browsing and serves as a positive reinforcement touchpoint in the user's pregnancy journey.</t>
+  </si>
+  <si>
+    <t>This event, preg_period_or_pregnant_shown, is fired when the screen asking 'Do you get your period regularly or are you currently pregnant?' is displayed to the user. This is typically one of the earliest screens in the app's onboarding or module selection flow, serving as the fundamental fork that directs users into either pregnancy tracking or period tracking. It fires every time this screen is rendered, including if the user navigates back to it from a later onboarding step. This is not a Key Event, but it captures the very first major decision point in the user journey. The PRD states that pregnancy and period modules are mutually exclusive, making this screen the definitive branching point for the entire product experience. From a business perspective, it answers: How many users reach this critical decision screen during onboarding? What is the drop-off rate at this point — users who see this screen but never select an option? Is the screen's design clear enough to prevent confusion between the options? This event is triggered by all new users during initial onboarding and potentially by existing users who navigate back to switch modules. Synonyms and related concepts include: module selection screen, period or pregnant choice, reproductive status question, onboarding fork, pregnancy vs period decision, cycle status screen, initial mode selection, reproductive health module picker. This event fires early in the onboarding sequence and is followed by preg_period_or_pregnant_option_tap when the user makes their selection.</t>
+  </si>
+  <si>
+    <t>This event, preg_period_or_pregnant_option_tap, is fired when the user selects an option on the 'period or pregnant' screen, choosing between regular period tracking, pregnancy tracking, or irregular cycle. It carries the parameters source_screen (recording where the user navigated from), option_selected (The option the user picked, for example regular_period, pregnant, irregular), position (Position of the selected item, for example 0, 1, 2). The option_selected parameter records the user's fundamental choice: 'regular_period' routes them to period tracking, 'pregnant' routes them into the pregnancy module, and 'irregular' may trigger a different accommodating flow. The position parameter records which option in the list was tapped. This is marked as a Key Event because it is the single most important user segmentation decision in the entire app — it determines whether the user enters the pregnancy module (with week-by-week guides, symptom logging, kick counters, and triage) or the period module (with cycle tracking and predictions). This binary choice shapes every subsequent screen, notification, content piece, and AI interaction the user will experience. From a business perspective, it answers: What is the proportion of pregnant users vs period users vs irregular users? Does this distribution match the app's marketing positioning and acquisition channels? If a disproportionate number select 'irregular,' does the app adequately serve that segment? What percentage of users who reach this screen successfully complete a selection (versus abandoning)? All users who reach the module selection screen and make a choice trigger this event. Synonyms and related concepts include: module choice, reproductive status selection, pregnancy opt-in, period tracking selection, onboarding segmentation, user type classification, cycle status decision, health module selection. This event fires after preg_period_or_pregnant_shown. If 'pregnant' is selected, it leads to preg_personalize_screen_shown and the pregnancy onboarding flow. If 'regular_period' is selected, it leads to the period module onboarding.</t>
+  </si>
+  <si>
+    <t>This event, preg_personalize_screen_shown, is fired when the 'Personalize your journey' screen is shown during pregnancy onboarding. This screen is part of the pregnancy setup flow where users configure their personal preferences and areas of focus. According to the PRD, personalization includes questions about whether this is a first pregnancy (yes/no) and key focus areas as a multi-select: nausea, sleep, anxiety, back pain, nutrition, exercise, and weight. These selections feed the personalisation engine that tailors daily recommendations, AI responses, and content prioritization. This is not a Key Event, but it represents a critical step in the onboarding funnel. From a business perspective, it answers: How many users reach the personalization step after selecting pregnancy? What is the drop-off rate between the module selection (preg_period_or_pregnant_option_tap) and personalization? Does the personalization screen cause any friction — is it too long or confusing? Users who have selected 'pregnant' in the previous step and are progressing through the onboarding flow trigger this event. Synonyms and related concepts include: personalization screen, pregnancy preferences, onboarding customization, journey setup, pregnancy profile configuration, focus area selection screen, pregnancy preference questionnaire, personalize onboarding step. This event fires after preg_period_or_pregnant_option_tap (with 'pregnant' selected) and leads to preg_due_date_method_shown as the next onboarding step.</t>
+  </si>
+  <si>
+    <t>This event, preg_due_date_method_shown, is fired when the 'Choose the method for calculating due date' screen is displayed. This screen presents the user with options for how to calculate their estimated due date and gestational age. The PRD specifies the required inputs as 'Pregnancy start method: LMP date OR EDD,' and the implementation supports LMP (last menstrual period date), EDD (estimated due date from a doctor), and IVF (transfer date for in-vitro fertilization). The user must select one of these methods before entering the actual date. This is not a Key Event, but it captures a critical setup step that determines how the entire pregnancy timeline is computed. From a business perspective, it answers: How many users reach the due date method selection during onboarding? Is the screen also accessed from settings (preg_settings) for users who want to change their method? What is the drop-off at this step? Users in the pregnancy onboarding flow or those editing settings trigger this event. Synonyms and related concepts include: due date calculation choice, EDD method selection screen, pregnancy dating screen, gestational age input method, due date entry screen, LMP or EDD selection, pregnancy calculation method, due date options screen. This event fires after preg_personalize_screen_shown (during onboarding) or from preg_settings_screen_shown (when editing), and is followed by preg_due_date_method_selected when the user picks a method.</t>
+  </si>
+  <si>
+    <t>This event, preg_due_date_method_selected, is fired when the user selects a due date calculation method from the available options on the method selection screen. It carries the parameters source_screen (recording where the user navigated from), method (The calculation method selected, for example lmp, edd, ivf), position (Position of the selected item, for example 0, 1, 2). The method parameter records which approach was chosen: 'lmp' for Last Menstrual Period date, 'edd' for directly entering the Estimated Due Date, or 'ivf' for IVF transfer date. The position parameter records the option's visual placement. This is marked as a Key Event because the method choice fundamentally determines how the app computes gestational age, trimester mapping, and all 42 weeks of pregnancy content scheduling. A wrong or imprecise method could misalign the entire pregnancy guide with the user's actual gestational progress. From a business perspective, it answers: What is the distribution of calculation methods among users — do most use LMP, EDD, or IVF? Does the method choice correlate with user persona (first-time mothers may be more likely to use EDD from a doctor's confirmation, while experienced mothers may know their LMP)? Are IVF users a significant segment that warrants specialized content or flows? Do users who start with LMP later switch to EDD after a dating scan (trackable via preg_settings_method_selected)? Users in the onboarding flow or editing their pregnancy settings trigger this event. Synonyms and related concepts include: pregnancy dating method choice, EDD calculation selection, LMP method pick, gestational age method, due date approach selected, pregnancy start method chosen, dating method confirmed. This event fires after preg_due_date_method_shown and leads to either preg_lmp_date_screen_shown (if method=lmp), preg_edd_date_screen_shown (if method=edd), or an IVF-specific date entry screen (if method=ivf).</t>
+  </si>
+  <si>
+    <t>This event, preg_lmp_date_screen_shown, is fired when the LMP (Last Menstrual Period) date calendar selection screen is shown to the user. This screen presents a full calendar interface where the user picks the first day of their last menstrual period, which the app uses to calculate gestational age (current date minus LMP date) and estimated due date (LMP + 280 days typically). This is not a Key Event, but it is a required step for users who chose the LMP calculation method. From a business perspective, it answers: How many users proceed to the LMP calendar after selecting the LMP method (drop-off between method selection and date entry)? Is the calendar UI intuitive, or does it cause confusion (detectable via excessive month scrolling or abandonment)? Users who selected LMP as their due date calculation method trigger this event. Synonyms and related concepts include: LMP calendar shown, last period date picker, menstrual period date screen, LMP entry UI, period start date calendar, LMP date input. This event fires after preg_due_date_method_selected (with method=lmp) and is followed by preg_lmp_date_month_scrolled (if the user navigates months) and preg_lmp_date_selected (when a date is chosen).</t>
+  </si>
+  <si>
+    <t>This event, preg_lmp_date_selected, is fired when the user selects a specific date on the LMP calendar, confirming the first day of their last menstrual period. It carries the parameters source_screen (recording where the user navigated from), selected_date (The date the user selected, for example 2025-01-15, 2025-03-01). The selected_date parameter records the exact date chosen in YYYY-MM-DD format. This is marked as a Key Event because the LMP date is the foundational clinical input from which the entire pregnancy timeline is calculated — gestational age, current trimester, week number, all 42 weeks of content scheduling, estimated due date, and milestone dates all derive from this single date. An incorrect LMP date would misalign the entire user experience. From a business perspective, it answers: What is the distribution of LMP dates among users who use this method? How far in the past are most LMP dates (indicating how early or late in pregnancy users discover and start using the app)? Do users who enter LMP dates early in pregnancy (few weeks ago) show different engagement patterns than those who enter dates further back (already well into pregnancy)? Users who are on the LMP calendar screen and select a date trigger this event. Synonyms and related concepts include: last period date confirmed, LMP date entry, menstrual period date set, period start date selection, pregnancy baseline date, LMP date picked, pregnancy anchor date. This event fires after preg_lmp_date_screen_shown and leads to the next onboarding step, eventually reaching preg_dashboard_screen_shown with fully calculated pregnancy data.</t>
+  </si>
+  <si>
+    <t>This event, preg_lmp_date_month_scrolled, is fired when the user scrolls to a different month on the LMP calendar picker while looking for their last menstrual period date. It carries the parameters source_screen (recording where the user navigated from), month_year (Month and year scrolled to, for example 2025-01, 2025-02). The month_year parameter records which month was scrolled to. This is not a Key Event, but it provides micro-interaction data about calendar usability and user behavior. From a business perspective, it answers: How many months do users scroll through to find their LMP date — excessive scrolling suggests the default starting month is wrong and should be optimized? Is there a pattern in scroll direction (mostly backward, suggesting the default month is too recent)? Do users who scroll many months have higher abandonment rates? Users who are browsing the LMP calendar and navigate between months trigger this event on each month change. Synonyms and related concepts include: calendar month navigation, month scroll on date picker, calendar pagination, date picker month change, calendar browsing. This event fires during interaction with the LMP calendar, between preg_lmp_date_screen_shown and preg_lmp_date_selected.</t>
+  </si>
+  <si>
+    <t>This event, preg_edd_date_screen_shown, is fired when the estimated due date (EDD) calendar selection screen is shown to the user. This screen presents a calendar for users who chose to enter their due date directly, rather than calculating it from their LMP. Users who know their EDD typically have it from a doctor's appointment, an ultrasound dating scan, or prior experience with pregnancy dating. This is not a Key Event, but it captures an important onboarding step for a significant user segment. From a business perspective, it answers: How many users opt for direct EDD entry versus LMP calculation? Are EDD users more likely to be further along in pregnancy (having already had a dating scan that confirmed their due date)? Is the EDD calendar UI as straightforward as the LMP calendar? Users who selected EDD as their due date method trigger this event. Synonyms and related concepts include: due date calendar shown, EDD entry screen, expected delivery date picker, due date input UI, baby arrival date screen. This event fires after preg_due_date_method_selected (with method=edd) and is followed by preg_edd_date_selected.</t>
+  </si>
+  <si>
+    <t>This event, preg_edd_date_selected, is fired when the user selects an estimated due date on the EDD calendar. It carries the parameters source_screen (recording where the user navigated from), selected_date (The EDD the user selected, for example 2025-09-15, 2025-11-01). The selected_date parameter records the chosen due date in YYYY-MM-DD format. This is marked as a Key Event because the EDD is the anchor date from which the entire pregnancy timeline is reverse-calculated — gestational age (today minus 280 days before EDD gives the conception estimate), current week number, trimester, and all content scheduling derive from this date. From a business perspective, it answers: What is the distribution of due dates among EDD users? How far in the future are most due dates, indicating how early in their pregnancy users start using the app? If most users join with due dates 4-5 months away (second trimester), the first-trimester weekly content may need to be adapted for retrospective catch-up reading rather than real-time delivery. Users who are on the EDD calendar and select a date trigger this event. Synonyms and related concepts include: due date confirmed, EDD entry completed, expected delivery date set, baby arrival date selected, due date input completed, EDD picked. This event fires after preg_edd_date_screen_shown and leads to the next onboarding step or returns to settings, eventually reaching the pregnancy dashboard.</t>
+  </si>
+  <si>
+    <t>This event, preg_calendar_preview_shown, is fired when the pregnancy calendar preview screen is displayed. It carries the parameters source_screen (recording where the user navigated from), week_number (Current pregnancy week, for example 12, 20, 36). This screen shows a full calendar view with pregnancy-related dates, milestones, symptom log indicators, and scheduled activities mapped onto it, providing a temporal overview of the entire pregnancy journey. This is not a Key Event, but the calendar is an important planning, review, and tracking tool. From a business perspective, it answers: How often do users visit the calendar? Which pregnancy weeks drive the most calendar usage? Is the calendar used more for reviewing past activity (checking symptom history for doctor visits) or planning ahead (viewing upcoming milestones and appointments)? All pregnancy users who navigate to the calendar preview from the dashboard, toolbar, or insight cards trigger this event. Synonyms and related concepts include: pregnancy calendar opened, calendar view shown, pregnancy timeline calendar, date overview screen, pregnancy planner view, calendar screen loaded. This event fires after navigation from preg_dashboard_calendar_card_tap, preg_toolbar_action_tap (with action_id=calendar), or other entry points. It is followed by user interactions like preg_calendar_preview_date_tap, preg_calendar_bottom_sheet_shown, preg_calendar_preview_edit_tap, and preg_calendar_preview_close_tap.</t>
+  </si>
+  <si>
+    <t>This event, preg_calendar_preview_close_tap, is fired when the user taps the close or back button on the calendar preview screen, dismissing it and returning to the previous screen. This is not a Key Event. From a business perspective, it answers: How quickly do users leave the calendar after opening it? Are they finding the information they need, or is the calendar not providing enough value? When compared with time spent and interactions before closing, it helps measure calendar effectiveness. All pregnancy users who close the calendar preview trigger this event. Synonyms and related concepts include: calendar dismiss, close calendar view, exit calendar, calendar back button, leave calendar screen. This event fires after preg_calendar_preview_shown and any intermediate interactions, returning the user to the previous screen (usually the dashboard).</t>
+  </si>
+  <si>
+    <t>This event, preg_calendar_preview_today_tap, is fired when the user taps the 'Today' button on the calendar preview to quickly navigate back to the current date. This is not a Key Event, but it indicates the user has scrolled away from today's date (browsing past or future dates) and wants to re-orient. From a business perspective, it answers: How often do users need to re-center on today? Are users exploring future dates (anticipating upcoming milestones) or past dates (reviewing history)? Is this navigation aid frequently used, suggesting the calendar is hard to navigate without it? All pregnancy users who use the Today shortcut on the calendar trigger this event. Synonyms and related concepts include: jump to today, today button click, current date navigation, calendar today shortcut, return to present date, re-center calendar. This event fires during calendar interaction after the user has scrolled away from the current date.</t>
+  </si>
+  <si>
+    <t>This event, preg_calendar_preview_date_tap, is fired when the user taps on a specific date cell in the pregnancy calendar preview, selecting it to view details for that day. It carries the parameters source_screen (recording where the user navigated from), selected_date (The date tapped, for example 2025-05-10, 2025-06-01), week_number (Pregnancy week of the tapped date, for example 12, 20, 36), has_logged_symptoms (Whether there are logged symptoms for the date, for example true, false). The has_logged_symptoms parameter is particularly valuable because it reveals whether users are tapping on dates with existing symptom data (reviewing past logs) or on empty dates (potentially looking to log retroactively or check what happened). This is not a Key Event, but it measures active calendar engagement. From a business perspective, it answers: Which dates do users tap — do they focus on today, recent past, or far-off future dates? Do users preferentially tap dates that have logged symptoms (reviewing their history) or empty dates (prompting them to log)? Does tapping a date with no symptoms lead to logging from the calendar bottom sheet? All pregnancy users who interact with specific calendar dates trigger this event. Synonyms and related concepts include: calendar date selection, date cell click, specific date tap, calendar day interaction, date detail view trigger, day selection. This event fires during calendar browsing and is immediately followed by preg_calendar_bottom_sheet_shown to display the selected date's details.</t>
+  </si>
+  <si>
+    <t>This event, preg_calendar_preview_edit_tap, is fired when the user taps the 'Edit Dates' button on the calendar preview screen, initiating a flow to modify their pregnancy dates (LMP or EDD). This is not a Key Event, but it captures user intent to modify their fundamental pregnancy timeline. This is significant because changing dates recalculates the entire pregnancy — gestational age, trimester, week number, and all content scheduling shift. The PRD specifically addresses this scenario: 'User updates due date after scan → recalc weeks without losing logs.' From a business perspective, it answers: How many users need to edit their pregnancy dates after initial setup? At what pregnancy week do most date corrections happen — likely after the first-trimester dating scan? Does date editing correlate with improved engagement afterward (because the content now aligns better with their actual pregnancy stage)? Users who want to correct or update their pregnancy dates trigger this event. Synonyms and related concepts include: edit dates button, modify pregnancy dates, correct due date, recalculate dates, update EDD, change LMP, pregnancy date correction, timeline edit. This event fires from the calendar preview and leads to preg_edit_calendar_shown.</t>
+  </si>
+  <si>
+    <t>This event, preg_calendar_bottom_sheet_shown, is fired when the bottom sheet with detailed date information is displayed on the calendar preview after the user taps a date. It carries the parameters source_screen (recording where the user navigated from), selected_date (Date for which details are shown, for example 2025-05-10), weeks (Weeks displayed, for example 12, 20), days (Days displayed, for example 3, 0, 5). The sheet shows the gestational age for that date (weeks and days), estimated due date, any milestones associated with that date, and any logged symptoms or scheduled activities. This is not a Key Event, but it captures deeper calendar interaction where users are seeking specific date-level details. From a business perspective, it answers: How often do users drill into date details on the calendar? What combination of information is available — are most dates empty (suggesting more prompts to log), or do they have symptom data? All pregnancy users who tap a date on the calendar and see the bottom sheet trigger this event. Synonyms and related concepts include: date detail sheet shown, calendar detail popup, date info bottom sheet, pregnancy date details overlay, calendar day information panel. This event fires after preg_calendar_preview_date_tap and may be followed by preg_calendar_symptom_viewed (if symptoms exist), preg_calendar_no_symptoms_shown (if no symptoms), preg_calendar_symptom_chip_tap (if the user logs from the sheet), or preg_calendar_activity_viewed (if activities are scheduled).</t>
+  </si>
+  <si>
+    <t>This event, preg_calendar_bottom_sheet_toggled, is fired when the user expands or collapses the bottom sheet on the calendar preview by dragging it up or down. It carries the parameters source_screen (recording where the user navigated from), action (Expand or collapse, for example expand, collapse). The action parameter records whether the user expanded (pulled up to see more content) or collapsed (pushed down to see less). This is not a Key Event. From a business perspective, it answers: Do users typically expand the sheet to see more details, or collapse it to return to the calendar grid? What is the expand-to-collapse ratio — a high expand rate suggests users want more information than the default sheet height shows? All pregnancy users who interact with the bottom sheet toggle trigger this event. Synonyms and related concepts include: bottom sheet expand, collapse detail sheet, sheet toggle, expand date details, minimize calendar sheet, pull up sheet, resize bottom panel. This event fires during calendar bottom sheet interaction.</t>
+  </si>
+  <si>
+    <t>This event, preg_calendar_symptom_viewed, is fired when logged symptoms for a selected date are displayed within the calendar bottom sheet. It carries the parameters source_screen (recording where the user navigated from), selected_date (Date with symptoms, for example 2025-05-10), symptom_count (Number of symptoms logged, for example 0, 3, 7). The symptom_count records how many symptoms were logged on the selected date. This is not a Key Event, but it tracks users actively reviewing their past symptom data through the calendar interface. From a business perspective, it answers: How often do users review past symptoms via the calendar? What is the average symptom count per date when users check? Are users using the calendar as a historical reference tool — for instance, preparing for a doctor's appointment by reviewing recent symptoms? Users who select a date that has existing symptom logs trigger this event. Synonyms and related concepts include: symptom history view on calendar, past symptoms displayed, logged symptoms review, symptom calendar lookup, historical symptom check, date symptom summary seen. This event fires after preg_calendar_bottom_sheet_shown for dates that have logged symptom data.</t>
+  </si>
+  <si>
+    <t>This event, preg_calendar_no_symptoms_shown, is fired when the 'No symptoms logged' empty state is displayed for a calendar date that has no symptom data. It carries the parameters source_screen (recording where the user navigated from), selected_date (The date with no symptoms, for example 2025-05-10). This is not a Key Event, but it identifies opportunities to prompt retroactive logging. From a business perspective, it answers: How often do users tap on dates that have no logged symptoms? Does seeing 'no symptoms logged' prompt users to log retroactively (followed by preg_calendar_symptom_chip_tap)? Is the empty state accompanied by a compelling CTA to log, and if so, what is its conversion rate? Users who tap a date with no logged symptoms on the calendar trigger this event. Synonyms and related concepts include: no data empty state, blank date view, empty symptom day, no log found, empty calendar date, unlogged day, missing symptom data state. This event fires after preg_calendar_bottom_sheet_shown for empty dates and may be followed by preg_calendar_symptom_chip_tap if the user decides to log retroactively.</t>
+  </si>
+  <si>
+    <t>This event, preg_calendar_symptom_chip_tap, is fired when the user taps a symptom chip in the calendar bottom sheet to log or toggle a symptom for the selected date. It carries the parameters source_screen (recording where the user navigated from), symptom_id (Identifier of the symptom, for example nausea, cramps, back_pain), selected_date (Date for which symptom is being logged, for example 2025-05-10). The symptom_id identifies which symptom was toggled, and selected_date records which calendar date the symptom is being logged for. This is not a Key Event, but it represents a unique and low-friction logging path — the user can log symptoms for any date directly from the calendar without opening the full symptom logging screen. From a business perspective, it answers: Are users retroactively logging symptoms from the calendar for past dates? Which symptoms are most commonly logged through this interface? How much does calendar-based logging contribute to overall symptom log volume? Does the availability of quick logging from the calendar improve the 'Symptom logs per week' KPI? The PRD mentions that 'edits allowed for past days' should be supported, and this calendar-based chip logging is one implementation of that requirement. Users who interact with symptom chips in the calendar bottom sheet trigger this event. Synonyms and related concepts include: calendar symptom toggle, quick symptom log from calendar, retroactive symptom entry, calendar-based logging, past date symptom chip, calendar quick log. This event fires from the calendar bottom sheet and may contribute to preg_symptom_log_submitted or a similar log completion metric.</t>
+  </si>
+  <si>
+    <t>This event, preg_calendar_activity_viewed, is fired when the scheduled activity section becomes visible on the calendar bottom sheet for the selected date. It carries the parameters source_screen (recording where the user navigated from), activity_count (Number of scheduled activities, for example 0, 1, 3). The activity_count records how many activities are scheduled for that date. This is not a Key Event. From a business perspective, it answers: How many users see scheduled activities via the calendar? What is the typical number of activities per date? Are users using the calendar as their primary interface for reviewing upcoming and past activities? Users who view the activity section in the calendar bottom sheet trigger this event. Synonyms and related concepts include: scheduled activities visible, calendar activity impression, upcoming activities shown, reminders visible on calendar, planned activities view, calendar schedule section. This event fires during calendar bottom sheet browsing.</t>
+  </si>
+  <si>
+    <t>This event, preg_calendar_reminder_tap, is fired when the user taps on a reminder item in the scheduled activity section of the calendar bottom sheet. It carries the parameters source_screen (recording where the user navigated from), reminder_id (Identifier of the reminder, for example rem_001, rem_002), reminder_type (Type of reminder, for example supplement, appointment, checkup). The reminder_type distinguishes between different kinds of reminders such as supplement reminders, appointments, and checkups, while reminder_id uniquely identifies the specific reminder. This is not a Key Event, but it tracks engagement with the scheduling and reminder system from the calendar context. From a business perspective, it answers: Which reminder types get the most interaction from the calendar? Are users effectively managing their reminders through the calendar view? Is the calendar a useful secondary access point for appointment and supplement management? Users who tap reminder items in the calendar bottom sheet trigger this event. Synonyms and related concepts include: reminder interaction from calendar, scheduled activity tap, calendar reminder click, appointment reminder tap, supplement reminder interaction, calendar schedule item click. This event fires during calendar bottom sheet interaction and may lead to appointment details, supplement settings, or reminder editing screens.</t>
+  </si>
+  <si>
+    <t>This event, preg_edit_calendar_shown, is fired when the edit pregnancy calendar screen is displayed, allowing the user to modify their pregnancy dates (LMP, EDD, or IVF date). This is not a Key Event. From a business perspective, it answers: How many users enter the date editing flow? Is this action typically triggered after a dating ultrasound (common at weeks 8-12)? How does the number of date edits compare to the total user base? Users who want to change their pregnancy dates and have navigated to the edit screen trigger this event. Synonyms and related concepts include: edit dates screen opened, pregnancy date editor, modify due date screen, recalculate pregnancy dates, date correction UI, timeline editor. This event fires after preg_calendar_preview_edit_tap and leads to user interactions including preg_edit_calendar_date_tap (selecting a new date), preg_edit_calendar_save_tap (saving changes), and preg_edit_calendar_close_tap (canceling).</t>
+  </si>
+  <si>
+    <t>This event, preg_edit_calendar_close_tap, is fired when the user taps the close button on the edit calendar screen without saving changes, abandoning the date modification. This is not a Key Event. From a business perspective, it answers: How many users abandon the date editing flow? Did they change their mind about editing, find the interface confusing, or realize their current dates are correct? Users who open the edit calendar and then close without saving trigger this event. Synonyms and related concepts include: cancel date edit, close edit screen, abandon date change, dismiss date editor, exit without saving. This event fires after preg_edit_calendar_shown and returns the user to the calendar preview.</t>
+  </si>
+  <si>
+    <t>This event, preg_edit_calendar_today_tap, is fired when the user taps the 'Today' button on the edit calendar screen to navigate to the current date in the calendar grid. This is not a Key Event. It is a navigation convenience for users editing their pregnancy dates. From a business perspective, it provides minor usability insight — frequent use suggests the calendar defaults to an unhelpful starting position. Users editing their pregnancy dates who use the Today shortcut trigger this event. Synonyms and related concepts include: today navigation in edit mode, jump to today in editor, edit calendar today shortcut, re-center edit calendar. This event fires during the edit calendar interaction.</t>
+  </si>
+  <si>
+    <t>This event, preg_edit_calendar_date_tap, is fired when the user taps a date cell in the edit calendar grid, selecting a new date for their pregnancy timeline (new LMP or EDD). It carries the parameters source_screen (recording where the user navigated from), selected_date (The date tapped, for example 2025-05-10). This is not a Key Event, but it captures the actual new date selection within the editing flow. From a business perspective, it answers: What specific dates are users changing to? How far from the original date do users typically adjust — minor corrections of a few days, or significant shifts of weeks? Users actively editing their pregnancy dates trigger this event on each date cell tap. Synonyms and related concepts include: new date selection in editor, date cell tap, corrected date pick, pregnancy date change tap, revised date selection. This event fires during the edit calendar interaction and precedes preg_edit_calendar_save_tap.</t>
+  </si>
+  <si>
+    <t>This event, preg_edit_calendar_save_tap, is fired when the user taps the 'Save' button on the edit calendar screen to confirm their pregnancy date changes. This is marked as a Key Event because saving edited dates triggers a complete recalculation of the entire pregnancy timeline — gestational age, trimester assignment, week number, weekly content schedule, milestone dates, and all future projections are recomputed based on the new date. The PRD specifically addresses this scenario: 'User updates due date after scan → recalc weeks without losing logs,' meaning existing symptom logs and checklist completions must be preserved even as the timeline shifts. From a business perspective, it answers: How many users modify their pregnancy dates after initial setup? At what pregnancy week do most corrections happen — is it clustered around weeks 8-12 when dating scans typically occur? Do users who correct their dates show better subsequent engagement (because content now accurately matches their pregnancy stage)? What is the average magnitude of date corrections? Users who complete the date editing process and confirm their changes trigger this event. Synonyms and related concepts include: save date changes, confirm pregnancy date edit, apply new dates, date correction saved, timeline recalculation trigger, pregnancy date update confirmed. This event fires after preg_edit_calendar_date_tap and leads back to preg_calendar_preview_shown or preg_dashboard_screen_shown with the updated pregnancy timeline data.</t>
+  </si>
+  <si>
+    <t>This event, preg_week_details_screen_shown, is fired when the pregnancy week details screen is displayed, showing the baby illustration, week heading, and detailed insights for a specific pregnancy week. It carries the parameters source_screen (recording where the user navigated from), week_number (The week number being viewed, for example 12, 20, 36), trimester (Current trimester, for example 1, 2, 3). This screen corresponds to the 'Weekly Guide System (Week 1-42)' described in the PRD, which provides per-week content including baby development (2-3 points), body changes (2-3 points), emotional wellbeing (1-2 points), one actionable 'this week's focus' tip, a 'what to watch' safety section, and one recommended checklist item. This is not a Key Event, but it measures consumption of the core weekly content that is the backbone of the pregnancy module's value proposition. From a business perspective, it answers: What is the weekly guide open rate — a primary engagement KPI from the PRD? Which weeks get the most views? Do users read week details every week they're pregnant, or is engagement sporadic? Is there a drop-off at certain pregnancy weeks? Which entry points (dashboard, trimester details, notifications) drive the most week detail views? This event is central to the PRD funnel: 'Weekly push opened → weekly guide read → checklist action.' All pregnancy users who navigate to the week details screen trigger this event. Synonyms and related concepts include: weekly guide opened, week details view, pregnancy week page, week-by-week content screen, weekly update screen, baby development page, weekly pregnancy guide, week information screen. This event fires after preg_dashboard_see_details_tap, preg_dashboard_see_baby_tap, preg_trimester_details_shown, or notification navigation, and is followed by preg_week_details_bottom_sheet_shown, preg_week_details_insight_viewed, preg_week_details_scroll_depth, and various interaction events.</t>
+  </si>
+  <si>
+    <t>This event, preg_week_details_tab_tap, is fired when the user taps a tab pill to switch between weeks on the week details screen, navigating from one pregnancy week's content to another. It carries the parameters source_screen (recording where the user navigated from), selected_week (The week number selected, for example 11, 12, 13), previous_week (The week previously viewed, for example 12, 11, 14). The selected_week and previous_week parameters together reveal the user's browsing pattern — whether they're moving forward, backward, or jumping multiple weeks. This is not a Key Event, but it measures content exploration behavior beyond the current week. From a business perspective, it answers: Do users browse adjacent weeks or jump far ahead? Is there a pattern of users looking forward (anticipating what's coming) versus reviewing past weeks (catching up on missed content)? Do users in early pregnancy browse many weeks ahead? Do users who explore multiple weeks have higher retention? Users who switch between weeks via the tab pills on the week details screen trigger this event. Synonyms and related concepts include: week tab switch, week navigation, pregnancy week change, browse different week, week selector tap, week pill navigation. This event fires during week details browsing and triggers the loading of new week content, followed by preg_week_details_bottom_sheet_shown for the newly selected week.</t>
+  </si>
+  <si>
+    <t>This event, preg_week_details_bottom_sheet_shown, is fired when the bottom sheet containing detailed week content is shown on the week details screen. It carries the parameters source_screen (recording where the user navigated from), week_number (Week number displayed, for example 12, 20, 36). The bottom sheet displays the week heading, description, baby size information, and horizontally scrollable insight cards for the selected week. This is not a Key Event. From a business perspective, it answers: Is the bottom sheet rendering correctly for all 42 pregnancy weeks? Are users seeing the detailed content layer? Do certain weeks have content issues (missing data or rendering errors)? Users viewing week details who have the bottom sheet displayed trigger this event. Synonyms and related concepts include: week content sheet displayed, week details bottom sheet, weekly info panel shown, week detail overlay, week content panel. This event fires after preg_week_details_screen_shown or preg_week_details_tab_tap.</t>
+  </si>
+  <si>
+    <t>This event, preg_week_details_sheet_toggled, is fired when the user expands or collapses the bottom sheet on the week details screen by dragging it. It carries the parameters source_screen (recording where the user navigated from), action (Expand or collapse, for example expand, collapse). The action parameter records whether the user expanded (to see more content) or collapsed (to see the baby illustration more prominently). This is not a Key Event. From a business perspective, it answers: Do users prefer the expanded or collapsed view of week content? Is the default sheet height appropriate, or do users consistently need to expand it? Users who toggle the week details bottom sheet trigger this event. Synonyms and related concepts include: sheet expand, sheet collapse, detail panel toggle, content expansion, bottom sheet resize, week content panel adjustment. This event fires during week details screen interaction.</t>
+  </si>
+  <si>
+    <t>This event, preg_week_details_insight_tap, is fired when the user taps on an insight card in the horizontal insights list on the week details screen. It carries the parameters source_screen (recording where the user navigated from), insight_id (Unique identifier of the insight, for example ins_001, ins_042), position (Position in the insights list, for example 0, 1, 2), week_number (Current week number, for example 12, 20, 36). The insight_id uniquely identifies the insight content, position records its placement in the horizontal list, and week_number provides context. This is not a Key Event, but insights are a core personalisation mechanism. The PRD describes a pattern detection engine that surfaces correlations like nausea timing, back pain after activity, and sleep-heartburn relationships. These insight cards make those patterns actionable. From a business perspective, it answers: Which insights generate the most interaction? Is there a positional bias where the first insight always gets more taps? Do insights about specific topics (nutrition, symptoms, emotional wellbeing) perform differently? Do users who engage with insights take more recommended actions? Users who tap insight cards on the week details screen trigger this event. Synonyms and related concepts include: weekly insight tap, personalized tip click, week recommendation interaction, insight card engagement, pattern insight click. This event fires after preg_week_details_insight_viewed (the impression event) and leads to an expanded insight detail view or related content.</t>
+  </si>
+  <si>
+    <t>This event, preg_week_details_insight_viewed, is fired when an insight card becomes visible in the viewport on the week details screen's horizontal insights carousel. It is an impression event that fires automatically based on visibility. It carries the parameters source_screen (recording where the user navigated from), insight_id (Unique identifier of the insight, for example ins_001, ins_042), position (Position in the insights list, for example 0, 1, 2). This is not a Key Event. Combined with preg_week_details_insight_tap, it enables calculation of the insight impression-to-click ratio, a key metric for measuring insight relevance and engagement. From a business perspective, it answers: How many insights are visible to users per week? Are insights being scrolled past without interaction? Users who scroll to or load insight cards on the week details screen trigger this event. Synonyms and related concepts include: insight impression, weekly insight visible, tip card seen, recommendation card exposure, insight card visibility. This event fires during week details browsing and may precede preg_week_details_insight_tap if the user interacts.</t>
+  </si>
+  <si>
+    <t>This event, preg_week_details_scroll_depth, is fired when the user reaches scroll depth milestones on the week details content, similar to the dashboard scroll depth tracking. It carries the parameters source_screen (recording where the user navigated from), scroll_percent (Scroll depth milestone reached, for example 25, 50, 75, 100), week_number (Week being viewed, for example 12, 20, 36). Milestones fire at 25%, 50%, 75%, and 100% thresholds. This is not a Key Event, but it measures how much of the weekly guide content users actually consume. From a business perspective, it answers: Are users reading the full weekly guide or abandoning partway? Is the 'what to watch' safety section (likely near the bottom) being reached? Does scroll depth vary by pregnancy week — do weeks with more concerning symptoms drive deeper reading? Does content length per week need adjustment? Users scrolling through week details content trigger this event at each milestone. Synonyms and related concepts include: week guide scroll depth, content read depth, weekly content consumption, page scroll progress, reading depth, week content engagement depth. This event fires during week details browsing and precedes preg_week_details_back_tap.</t>
+  </si>
+  <si>
+    <t>This event, preg_week_details_back_tap, is fired when the user taps the back or close button on the week details screen, ending their current session with the weekly guide. This is not a Key Event. From a business perspective, it confirms the user has finished browsing week details. The time between preg_week_details_screen_shown and this event represents the total session duration on the weekly guide, which indicates content engagement depth. All users who exit the week details screen trigger this event. Synonyms and related concepts include: close week details, back from weekly guide, exit week view, leave week screen, dismiss week content. This event fires after all week details interactions and returns the user to the previous screen, typically the pregnancy dashboard.</t>
+  </si>
+  <si>
+    <t>This event, preg_trimester_details_shown, is fired when the trimester details screen is displayed, showing articles, educational content, and resources organized by trimester. It carries the parameters source_screen (recording where the user navigated from), trimester (Trimester number being viewed, for example 1, 2, 3). This is not a Key Event, but it measures engagement with trimester-level educational content. The PRD includes trimester checklists covering screening discussions, comfort items, and birth planning prompts, and the trimester details screen houses this content alongside related articles and videos. From a business perspective, it answers: How many users explore trimester-level content? Which trimester generates the most interest — first trimester (new and uncertain), second (relatively comfortable, preparing), or third (imminent delivery, high anxiety)? Is this screen effective at driving checklist completion and article reading? Users who navigate to trimester details (usually via preg_dashboard_trimester_tap) trigger this event. Synonyms and related concepts include: trimester content screen, trimester articles view, trimester education page, trimester overview opened, trimester resources screen. This event fires after preg_dashboard_trimester_tap and is followed by interactions like preg_trimester_tab_tap, preg_trimester_article_tap, and preg_trimester_back_tap.</t>
+  </si>
+  <si>
+    <t>This event, preg_trimester_tab_tap, is fired when the user taps a tab pill to switch between trimesters on the trimester details screen. It carries the parameters source_screen (recording where the user navigated from), selected_trimester (Trimester selected, for example 1, 2, 3), previous_trimester (Trimester previously viewed, for example 1, 2, 3). The selected_trimester and previous_trimester parameters reveal which direction the user is exploring — looking ahead to future trimesters or back at earlier ones. This is not a Key Event. From a business perspective, it answers: Do users explore trimesters beyond their current one? Is there a pattern of looking ahead (e.g., second-trimester users exploring third-trimester content for preparation)? Which trimester transitions are most common? Users who switch between trimester tabs trigger this event. Synonyms and related concepts include: trimester switch, trimester tab navigation, browse other trimesters, trimester selector, trimester content switch. This event fires during trimester details browsing.</t>
+  </si>
+  <si>
+    <t>This event, preg_trimester_article_tap, is fired when the user taps on a trimester article or video item on the trimester details screen. It carries the parameters source_screen (recording where the user navigated from), article_id (Unique identifier of the article, for example art_001, art_042), article_title (Title of the article, for example Common Symptoms and Management), position (Position in the list, for example 0, 1, 2), trimester (Trimester context, for example 1, 2, 3). The article_id and article_title identify the specific content, position records its placement in the list, and trimester provides the context. This is not a Key Event, but it measures content engagement with the educational library. From a business perspective, it answers: Which articles are most popular per trimester? Does article position in the list significantly affect tap rate? Are video content items more engaging than text articles? Which topics drive the most interest? This data directly informs the content strategy, editorial calendar, and resource allocation for content production. Users who tap articles on the trimester details screen trigger this event. Synonyms and related concepts include: article click, trimester content tap, educational article open, pregnancy article interaction, content piece selection, trimester resource tap. This event fires after preg_trimester_article_viewed (the impression event) and leads to a full article or video detail view.</t>
+  </si>
+  <si>
+    <t>This event, preg_trimester_article_viewed, is fired when a trimester article item becomes visible in the viewport on the trimester details screen. It is an impression event that fires based on visibility. It carries the parameters source_screen (recording where the user navigated from), article_id (Unique identifier of the article, for example art_001, art_042), position (Position in the list, for example 0, 1, 2). This is not a Key Event. Combined with preg_trimester_article_tap, it calculates the article impression-to-tap ratio, indicating how compelling article titles, thumbnails, and descriptions are at converting passive exposure into active reading. From a business perspective, it answers: How many articles are visible to users per trimester? Are articles lower in the list being seen at all? Is the article list length appropriate — too many articles may cause decision paralysis, too few may leave users wanting more? Users scrolling through the trimester details screen who see article items trigger this event. Synonyms and related concepts include: article impression, trimester content visible, article card exposure, educational content seen, article list item view. This event fires during trimester details browsing and may precede preg_trimester_article_tap.</t>
+  </si>
+  <si>
+    <t>This event, preg_trimester_back_tap, is fired when the user taps the back button on the trimester details screen, ending their session with trimester content. This is not a Key Event. From a business perspective, it confirms exit from the trimester content area and helps measure the total session duration on trimester details (time between preg_trimester_details_shown and this event). All users exiting the trimester details screen trigger this event. Synonyms and related concepts include: exit trimester details, back from trimester, leave trimester screen, close trimester view, dismiss trimester content. This event fires after all trimester details interactions and returns the user to the previous screen.</t>
+  </si>
+  <si>
+    <t>This event, preg_kick_counter_screen_shown, is fired when the kick counter screen is displayed to the user. The kick counter is a P1 feature described in the PRD (section 6.9) that becomes available from a clinically configured pregnancy week (typically later pregnancy). The screen displays the session interface where users can start counting baby kicks, view recent session history, and access educational content about fetal movement. It carries the parameters source_screen (recording where the user navigated from), week_number (Current pregnancy week, for example 28, 32, 38). The week_number parameter is essential for verifying that the kick counter is only being shown from the appropriate gestational age, as the PRD specifies the availability threshold should be 'clinically reviewed and configurable.' This is not a Key Event, but it measures reach and adoption of the kick counter feature. From a business perspective, it answers: How many users access the kick counter, and at what pregnancy weeks? Is there a natural adoption curve — do users start using it as soon as it becomes available, or does it take several weeks? What percentage of eligible users (those past the configured week threshold) actually open the kick counter? What is the source_screen that most commonly leads to the kick counter — dashboard shortcuts, notifications, or the AI assistant suggesting it? This event is relevant to the 'Experienced Busy Mum' persona who wants quick daily routines, the 'Anxious Planner' who wants reassurance about baby movement patterns, and the 'Symptom Checker' who may be concerned about reduced movements. Synonyms and related concepts include: kick counter opened, fetal movement screen, baby movement tracker view, kick counting page, movement counter display, baby kicks screen. This event fires after navigation from the dashboard (preg_dashboard_kick_counter_tap or similar) and precedes preg_kick_counter_start_tap when the user begins a session.</t>
+  </si>
+  <si>
+    <t>This event, preg_kick_counter_start_tap, is fired when the user taps the 'Start' button to begin a kick counting session. This is the moment of commitment — the user has navigated to the kick counter and actively chosen to begin tracking fetal movements. The session timer begins at this point. It carries the parameters source_screen (recording where the user navigated from), week_number (Current pregnancy week, for example 28, 32, 38), is_first_time (Whether this is the user's first kick counter session, for example true, false). The is_first_time parameter distinguishes whether this is the user's very first kick counting session ever, which is an important activation metric for the P1 kick counter feature. This is marked as a Key Event because starting a kick counting session represents meaningful health-tracking engagement. The PRD (section 6.9) specifies 'Start session, tap counts, duration' as core features, and this event captures the initiation step. From a business perspective, it answers: What is the conversion rate from viewing the kick counter screen to actually starting a session? How many first-time kick counter users are there per week? At what gestational week do most users start their first kick counting session? Do users who start kick counting sessions show higher retention than those who don't? Is there a drop-off between viewing the screen and starting — if so, the start button or instructions may need improvement. This event directly supports measuring the PRD's P1 kick counter adoption KPIs and the broader engagement goal of daily micro-actions forming habit loops. Synonyms and related concepts include: begin kick session, start counting kicks, initiate fetal movement tracking, kick timer start, baby movement session begin. This event fires after preg_kick_counter_screen_shown and is followed by preg_kick_counter_kick_tap events as the user records individual kicks, and eventually preg_kick_counter_session_saved when the session completes.</t>
+  </si>
+  <si>
+    <t>This event, preg_kick_counter_kick_tap, is fired each time the user taps the kick area to record an individual baby kick during an active session. This is the core interaction of the kick counter — each tap represents one perceived fetal movement. The event fires on every single tap throughout the session, generating a granular record of kick timing and frequency. It carries the parameters source_screen (recording where the user navigated from), kick_count (Running count of kicks in this session, for example 1, 5, 10), elapsed_seconds (Time elapsed since session started in seconds, for example 30, 120, 600). The kick_count parameter is the running cumulative count within the current session, and elapsed_seconds tracks how long the session has been active, together enabling analysis of kick frequency and patterns over time within a session. This is not a Key Event because it fires at very high frequency during a session. However, it is analytically valuable for understanding session dynamics. From a business perspective, it answers: What is the average number of kicks per session? What is the typical time distribution between kicks — are they clustered or evenly spaced? How long does the average session last before the user reaches their target kick count? Are there patterns in kick frequency by time of day, gestational week, or user segment? The PRD notes that if a user reports reduced movement, the app should show a safe triage template. The data from this event, combined with session history, could inform the threshold logic for the preg_kick_few_kicks_warning_shown event. Synonyms and related concepts include: record kick, baby movement tap, fetal movement logged, kick registered, movement count increment, baby kick recorded. This event fires repeatedly between preg_kick_counter_start_tap and preg_kick_counter_session_saved.</t>
+  </si>
+  <si>
+    <t>This event, preg_kick_counter_session_saved, is fired when a kick counting session is completed and saved. This represents the successful end of a kick counting session, where the user's recorded kicks, duration, and any notes are persisted. The PRD (section 6.9) specifies 'Save session notes' and 'Show trend and education' as requirements. It carries the parameters source_screen (recording where the user navigated from), kick_count (Total kicks recorded in the session, for example 5, 10, 20), duration_seconds (Total duration of the session in seconds, for example 300, 600, 1800), week_number (Current pregnancy week, for example 28, 32, 38). The kick_count records the total kicks in the session, duration_seconds captures the full session length, and week_number provides gestational context. These parameters together form the core data point for fetal movement trend analysis. This is marked as a Key Event because a completed and saved kick session represents a full engagement cycle with a health-tracking feature. From a business perspective, it answers: How many kick sessions are completed per user per day/week? What is the average kick count and session duration? Do kick counts trend lower as pregnancy progresses (which might indicate clinical concerns) or remain stable? What percentage of started sessions are actually saved versus abandoned? Are there users with consistently low kick counts who should receive educational content or triage prompts? This event directly supports the PRD's engagement metrics (daily micro-actions) and safety goals (monitoring for reduced fetal movements). Synonyms and related concepts include: kick session completed, save kick count, fetal movement session end, kick tracking saved, baby movement log saved, kick count recorded. This event fires after the final preg_kick_counter_kick_tap and may be followed by preg_kick_few_kicks_warning_shown if the kick count is below a safety threshold, or by preg_kick_prompt_sheet_shown for educational guidance.</t>
+  </si>
+  <si>
+    <t>This event, preg_kick_counter_view_all_tap, is fired when the user taps 'View All' to see their full kick counter history from the kick counter screen. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. From a business perspective, it measures user interest in reviewing their kick counting trends and history, which aligns with the PRD requirement to 'Show trend and education.' It answers: What percentage of kick counter users want to review their history? Do users who review history show better adherence to daily kick counting? Synonyms and related concepts include: view kick history, see all sessions, kick trend view, movement history tap, browse kick records. This event fires after preg_kick_counter_screen_shown or preg_kick_counter_session_saved and leads to preg_kick_history_screen_shown.</t>
+  </si>
+  <si>
+    <t>This event, preg_kick_counter_history_tap, is fired when the user taps on a specific kick history entry on the kick counter screen to expand or view its details. It carries the parameters source_screen (recording where the user navigated from), session_date (Date of the kick session tapped, for example 2025-05-10, 2025-05-09), position (Position in the history list, for example 0, 1, 2). The session_date identifies which historical session was tapped, and position records its placement in the history list, enabling analysis of whether users review recent or older sessions. This is not a Key Event. From a business perspective, it answers: Which historical sessions do users review most — recent ones or specific dates? Does position in the list affect tap rate? Are users reviewing sessions with low kick counts more frequently, suggesting concern? Synonyms and related concepts include: expand kick session, view session details, kick history detail tap, session entry click, movement record expand. This event fires on the kick counter screen when the user interacts with the inline history summary.</t>
+  </si>
+  <si>
+    <t>This event, preg_kick_counter_back_tap, is fired when the user taps the back button to leave the kick counter screen. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. It marks the end of the user's session with the kick counter and helps measure total time spent on the screen (when paired with preg_kick_counter_screen_shown). Synonyms and related concepts include: exit kick counter, leave movement tracker, close kick screen, back from kick counter, dismiss kick counter. This event fires after all kick counter interactions and returns the user to their previous screen.</t>
+  </si>
+  <si>
+    <t>This event, preg_kick_history_screen_shown, is fired when the dedicated kick counter history screen is displayed. This is the full history view showing all past kick counting sessions with dates, kick counts, durations, and trend visualizations. The PRD requires showing trends and education around fetal movements. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. From a business perspective, it answers: How often do users access the full kick history? Is this screen used for self-monitoring or in preparation for medical appointments (users may review patterns before seeing their clinician)? What is the typical navigation path — do users arrive from the kick counter directly or from other areas? Synonyms and related concepts include: kick history opened, movement history screen, kick sessions list view, fetal movement log screen, kick trend display. This event fires after preg_kick_counter_view_all_tap and precedes preg_kick_history_item_tap as the user browses individual sessions.</t>
+  </si>
+  <si>
+    <t>This event, preg_kick_history_item_tap, is fired when the user taps on a specific session entry in the kick history screen to expand or collapse its details. It carries the parameters source_screen (recording where the user navigated from), session_date (Date of the kick session, for example 2025-05-10), position (Position in the history list, for example 0, 1, 2), action (Expand or collapse, for example expand, collapse). The session_date identifies the specific historical session, and position tracks where it appeared in the list. This is not a Key Event. From a business perspective, it measures engagement with historical kick data and answers: Which sessions do users investigate most? Are users comparing sessions across different days? Do users focus on sessions with warning indicators (low kick counts)? Synonyms and related concepts include: kick session detail view, history entry expand, movement record click, session detail toggle. This event fires on the kick history screen after preg_kick_history_screen_shown.</t>
+  </si>
+  <si>
+    <t>This event, preg_kick_history_back_tap, is fired when the user taps the back button to leave the kick history screen. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. It marks the end of the history review session and helps calculate total time spent reviewing kick history. Synonyms and related concepts include: exit kick history, leave movement history, close history screen, back from kick records. This event fires after all kick history interactions.</t>
+  </si>
+  <si>
+    <t>This event, preg_kick_few_kicks_warning_shown, is fired when a 'few kicks' warning indicator is displayed on a kick history entry, signaling that a session recorded fewer kicks than the expected threshold. This is a safety-critical event tied directly to the PRD's triage system (section 6.5) and kick counter safety requirements (section 6.9). The PRD explicitly states: 'If user reports reduced movement → show safe triage template.' The warning indicator is the visual cue that alerts the user to a session that may warrant attention. It carries the parameters source_screen (recording where the user navigated from), session_date (Date of the session with warning, for example 2025-05-10), kick_count (Number of kicks in the session, for example 2, 3, 4). The session_date identifies which session triggered the warning, kick_count shows the actual count that was below the threshold, and threshold records what the minimum expected count was. This is not a Key Event on its own, but it is a critical safety monitoring event. From a business perspective and safety perspective, it answers: How often are low-kick warnings displayed? What is the distribution of kick counts that trigger warnings? Do warnings lead users to seek medical advice (can be correlated with subsequent app behaviour)? Are there specific gestational weeks where warnings are more frequent? Is the threshold calibrated correctly — too sensitive generates false alarms and anxiety (counter to the PRD's 'felt supported vs felt scared' safety metric), while too lenient misses genuine concerns. This event is particularly important for the 'Symptom Checker' and 'Anxious Planner' personas and must be tracked carefully to ensure the app fulfils its safety obligations without causing undue alarm. Synonyms and related concepts include: low kick count alert, reduced movement warning, fetal movement concern indicator, kick threshold warning, baby movement alert. This event fires in the context of kick history display and may lead to preg_kick_prompt_sheet_shown or direct the user to triage templates.</t>
+  </si>
+  <si>
+    <t>This event, preg_settings_screen_shown, is fired when the pregnancy settings screen is displayed. The settings screen allows users to view and modify their pregnancy configuration: due date calculation method (LMP or EDD), pregnancy date, and the option to remove pregnancy tracking entirely. The PRD (section 6.1) requires that setup inputs are 'Editable anytime.' It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. From a business perspective, it answers: How often do users visit pregnancy settings? Is there a spike in settings visits at specific weeks (e.g., after ultrasound scans when due dates may be revised per the PRD's edge case 'User updates due date after scan → recalc weeks without losing logs')? What source screens drive settings visits — dashboard toolbar, profile, or deep links? Synonyms and related concepts include: pregnancy settings opened, preferences screen, pregnancy configuration view, settings page, pregnancy profile screen. This event fires after navigation from the toolbar or profile and precedes setting modification events.</t>
+  </si>
+  <si>
+    <t>This event, preg_settings_back_tap, is fired when the user taps the back button to leave the pregnancy settings screen without making changes (or after viewing settings). It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. It helps measure settings screen session duration and whether users are browsing or actively editing. Synonyms and related concepts include: exit settings, leave pregnancy settings, close settings screen, back from settings. This event fires after preg_settings_screen_shown.</t>
+  </si>
+  <si>
+    <t>This event, preg_settings_method_selected, is fired when the user selects a due date calculation method in settings. The PRD (section 6.1) specifies two primary methods: LMP (last menstrual period) date or EDD (estimated due date). The settings also show IVF as an option. It carries the parameters source_screen (recording where the user navigated from), method (The calculation method selected, for example lmp, edd, ivf), position (Position of the item, for example 0, 1, 2). The method parameter records which calculation method was selected (lmp, edd, or ivf), and position records the selection index. This is not a Key Event. From a business perspective, it answers: What is the distribution of calculation methods among users changing settings? Are users switching methods (e.g., from LMP to EDD after receiving an ultrasound-based EDD)? How does the method selected in settings compare to the method chosen during onboarding — do many users change their approach? Synonyms and related concepts include: date method change, due date calculation switch, pregnancy method selection, EDD method pick, LMP method select. This event fires during active settings editing and precedes preg_settings_date_picker_tap and preg_settings_update_tap.</t>
+  </si>
+  <si>
+    <t>This event, preg_settings_date_picker_tap, is fired when the user taps on the date field to open the date picker in pregnancy settings. It carries the parameters source_screen (recording where the user navigated from), current_date (Currently selected date, for example 2025-01-15, 2025-03-01). The current_date parameter shows the date that was displayed before the user initiated the change. This is not a Key Event. It indicates intent to change the pregnancy date, which the PRD (section 11) addresses as an edge case: 'User updates due date after scan → recalc weeks without losing logs.' From a business perspective, it answers: How often do users attempt to change their pregnancy date? What is the current date at the time they attempt the change — are certain dates being changed more than others? Synonyms and related concepts include: open date selector, date field tap, calendar picker open, change date intent, date input tap. This event fires after preg_settings_screen_shown and may be followed by preg_settings_date_changed.</t>
+  </si>
+  <si>
+    <t>This event, preg_settings_date_changed, is fired when the user changes the pregnancy date in settings by selecting a new date from the date picker. It carries the parameters source_screen (recording where the user navigated from), old_date (Previously set date, for example 2025-01-15), new_date (Newly selected date, for example 2025-01-20), method (Calculation method used, for example lmp, edd, ivf). The old_date and new_date parameters capture the before and after values, enabling analysis of how far dates are being shifted. The method parameter records which calculation method applies. This is not a Key Event, but it is analytically significant for understanding due date corrections. The PRD explicitly addresses this scenario in the edge cases section: 'User updates due date after scan → recalc weeks without losing logs.' From a business perspective, it answers: How frequently are pregnancy dates revised? What is the average shift in days between old and new dates? Do date changes cluster around specific pregnancy weeks (e.g., after the 12-week or 20-week scan)? Does changing the date correlate with changes in engagement or content consumption patterns? Synonyms and related concepts include: due date updated, pregnancy date revised, date correction, due date adjusted, pregnancy timeline changed. This event fires after preg_settings_date_picker_tap and precedes preg_settings_update_tap.</t>
+  </si>
+  <si>
+    <t>This event, preg_settings_remove_tap, is fired when the user taps the 'Remove Pregnancy' text link in settings. This is a sensitive action that initiates the pregnancy deletion flow. The PRD (section 11) addresses this scenario under 'Loss / termination / complications' — the app must 'Provide a discreet pathway: Change module / pause pregnancy tracking' and 'hide week-by-week baby visuals if user chooses.' It carries the parameters source_screen (recording where the user navigated from), week_number (Current pregnancy week at time of tap, for example 12, 20, 36). The week_number records the user's gestational week at the time they initiated removal, which is analytically important for understanding when and why users leave pregnancy tracking. This is not a Key Event (the confirmation step preg_delete_sheet_proceed_tap is the Key Event). From a business perspective, it answers: At what pregnancy weeks do users consider removing pregnancy tracking? Is there a correlation between specific weeks and removal intent (e.g., early weeks might indicate miscarriage, later weeks might indicate birth or error correction)? How many users who tap 'Remove' actually proceed versus cancel? This event requires particular sensitivity in analysis due to the potential for pregnancy loss or other difficult circumstances. Synonyms and related concepts include: remove pregnancy tap, delete pregnancy intent, end pregnancy tracking, stop pregnancy mode, pregnancy removal initiated. This event fires after preg_settings_screen_shown and triggers preg_delete_sheet_shown for confirmation.</t>
+  </si>
+  <si>
+    <t>This event, preg_settings_update_tap, is fired when the user taps the 'Update Settings' button to save their pregnancy settings changes. It carries the parameters source_screen (recording where the user navigated from), method (Calculation method selected, for example lmp, edd, ivf), date_changed (Whether the date was changed, for example true, false). The method parameter records the selected calculation method, and date_changed indicates whether the date itself was modified (versus just viewing settings and saving without changes). This is marked as a Key Event because updating pregnancy settings can fundamentally change the user's gestational timeline, affecting all week-based content, trimester mapping, and personalization. From a business perspective, it answers: How often do users save settings changes? What percentage of settings visits result in an actual update? Are users primarily changing the method, the date, or both? Does date_changed=true correlate with different downstream engagement patterns compared to date_changed=false? Synonyms and related concepts include: save settings, update pregnancy configuration, confirm settings changes, apply settings, save date changes. This event fires after settings modifications and is followed by either preg_settings_update_success or preg_settings_update_failed.</t>
+  </si>
+  <si>
+    <t>This event, preg_settings_update_success, is fired when pregnancy settings are successfully updated and persisted. It carries the parameters source_screen (recording where the user navigated from), method (Method saved, for example lmp, edd, ivf). The method parameter confirms which calculation method was saved. This is not a Key Event. From a business perspective, it confirms the successful completion of a settings update and, when compared with preg_settings_update_tap, helps calculate the success rate of settings saves. A gap between update_tap and update_success counts would indicate server or validation failures. Synonyms and related concepts include: settings saved successfully, update confirmed, pregnancy settings persisted, settings save complete. This event fires immediately after preg_settings_update_tap when the save operation succeeds.</t>
+  </si>
+  <si>
+    <t>This event, preg_settings_update_failed, is fired when a pregnancy settings update fails due to a network error, server error, or validation issue. It carries the parameters source_screen (recording where the user navigated from), error_type (Type of error encountered, for example network, server, validation), error_message (Error message, for example No internet connection, Server error). The error_type categorizes the failure (network, server, validation), and error_message provides the specific message displayed to the user. This is not a Key Event. From a business perspective, it answers: What is the failure rate for settings updates? What error types are most common? Are failures concentrated on specific device types, OS versions, or network conditions? Do users who experience settings failures retry or abandon the flow? This event is important for reliability monitoring, as the PRD requires settings to be 'editable anytime' — failures undermine this promise. Synonyms and related concepts include: settings save error, update failed, pregnancy settings error, settings persistence failure. This event fires instead of preg_settings_update_success when the save operation fails, and may be followed by preg_retry_tap.</t>
+  </si>
+  <si>
+    <t>This event, preg_delete_sheet_shown, is fired when the 'Delete Pregnancy' confirmation bottom sheet is displayed after the user taps 'Remove Pregnancy' in settings. This confirmation step is a critical safeguard for a destructive, irreversible action. The PRD (section 11) emphasizes that this flow must be handled sensitively, especially for users experiencing pregnancy loss. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. From a business perspective, it answers: How many users reach the deletion confirmation step? What is the cancel-to-proceed ratio — a high cancel rate suggests users are exploring the option but not committing, while a high proceed rate may indicate the flow is not providing enough friction or support. Synonyms and related concepts include: delete confirmation shown, removal confirmation sheet, pregnancy deletion dialog, confirm remove pregnancy, deletion warning display. This event fires after preg_settings_remove_tap and is followed by either preg_delete_sheet_cancel_tap or preg_delete_sheet_proceed_tap.</t>
+  </si>
+  <si>
+    <t>This event, preg_delete_sheet_cancel_tap, is fired when the user taps 'Cancel' on the delete pregnancy confirmation sheet, choosing not to proceed with pregnancy removal. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. From a business perspective, it indicates the user reconsidered the deletion, which is generally a positive outcome. It helps calculate the cancel rate for pregnancy deletions. Synonyms and related concepts include: cancel pregnancy deletion, dismiss removal sheet, keep pregnancy tracking, abort deletion, decline removal. This event fires after preg_delete_sheet_shown and returns the user to the settings screen.</t>
+  </si>
+  <si>
+    <t>This event, preg_delete_sheet_proceed_tap, is fired when the user taps 'Proceed' to confirm pregnancy deletion. This is a destructive, irreversible action that removes all pregnancy tracking data and configuration. It carries the parameters source_screen (recording where the user navigated from), week_number (Pregnancy week at time of deletion, for example 12, 20, 36). The week_number records the gestational week at the time of deletion, which is critical for understanding at what stage users are leaving pregnancy tracking. This is marked as a Key Event because it represents a permanent, irreversible user action with significant implications. The PRD (section 11) requires the app to handle this sensitively under 'Loss / termination / complications,' providing a 'discreet pathway' and hiding pregnancy visuals. From a business perspective, it answers: How many users delete their pregnancy per week/month? At what gestational weeks does deletion occur — early weeks might indicate pregnancy loss, mid-pregnancy might indicate complications, and late weeks (38-42) might indicate delivery? Is there a pattern in source_screen or settings behaviour before deletion? Should the app offer a 'pause' option instead of deletion to retain users who may return? This event requires careful handling in analytics dashboards and should be treated with sensitivity in cohort analyses. Synonyms and related concepts include: confirm pregnancy deletion, remove pregnancy confirmed, pregnancy tracking ended, delete pregnancy data, permanent pregnancy removal. This event fires after preg_delete_sheet_shown and results in the user being transitioned out of the pregnancy module, potentially to the period module or a neutral state.</t>
+  </si>
+  <si>
+    <t>This event, preg_water_intake_screen_shown, is fired when the pregnancy water intake settings screen is displayed. Hydration is an important aspect of pregnancy health, and this screen allows users to configure their daily water intake target and preferred container size for tracking. This supports the PRD's goal of providing actionable daily micro-actions and the 'Healthy Pregnancy' persona's interest in nutrition and routine support. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. From a business perspective, it answers: How many users access water intake settings? What is the typical navigation path — do users find this from the dashboard, settings, or onboarding? Is water tracking a feature that drives daily engagement? Synonyms and related concepts include: water settings opened, hydration screen view, water intake configuration, hydration tracker settings, daily water goal screen. This event fires after navigation from settings or dashboard and precedes water target and container selection events.</t>
+  </si>
+  <si>
+    <t>This event, preg_water_intake_back_tap, is fired when the user taps the back button to leave the water intake settings screen. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. It marks the end of the water intake settings session. Synonyms and related concepts include: exit water settings, leave hydration screen, close water intake, back from water settings. This event fires after preg_water_intake_screen_shown.</t>
+  </si>
+  <si>
+    <t>This event, preg_water_target_dropdown_tap, is fired when the user taps the daily water target dropdown to view available target options. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. It indicates the user is actively configuring their hydration goal. From a business perspective, it measures the exploration rate of the target selector. Synonyms and related concepts include: open water target picker, daily goal dropdown, hydration target selector, water goal options, target amount picker. This event fires on the water intake screen and precedes preg_water_target_selected.</t>
+  </si>
+  <si>
+    <t>This event, preg_water_target_selected, is fired when the user selects a daily water target value from the dropdown. It carries the parameters source_screen (recording where the user navigated from), target_value (Water target value selected, for example 2000ml, 2500ml, 3000ml). The target_value records the selected goal (e.g., 2000ml, 2500ml, 3000ml), which helps understand user health preferences. This is not a Key Event. From a business perspective, it answers: What is the most commonly selected water target? Do targets vary by trimester or gestational week? Are the predefined options appropriate — if most users select the highest or lowest option, the range may need adjustment. Synonyms and related concepts include: water goal set, daily target chosen, hydration target selected, water amount picked. This event fires after preg_water_target_dropdown_tap and before preg_water_intake_save_tap.</t>
+  </si>
+  <si>
+    <t>This event, preg_water_container_dropdown_tap, is fired when the user taps the water container volume dropdown to view available container sizes. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. It indicates the user is configuring their preferred tracking unit — the container size determines how many 'glasses' or 'bottles' they need to consume daily. Synonyms and related concepts include: container size picker, glass size dropdown, water volume selector, bottle size options. This event fires on the water intake screen and precedes preg_water_container_selected.</t>
+  </si>
+  <si>
+    <t>This event, preg_water_container_selected, is fired when the user selects a container volume from the dropdown. It carries the parameters source_screen (recording where the user navigated from), container_volume (Container volume selected, for example 250ml, 500ml, 750ml). The container_volume records the selected size (e.g., 250ml, 500ml, 750ml). This is not a Key Event. From a business perspective, it answers: What container sizes are most popular? Does container size selection correlate with daily water target — users with larger targets may prefer larger containers for convenience. Synonyms and related concepts include: container size chosen, glass volume set, water unit selected, bottle volume picked. This event fires after preg_water_container_dropdown_tap and before preg_water_intake_save_tap.</t>
+  </si>
+  <si>
+    <t>This event, preg_water_intake_save_tap, is fired when the user taps the 'Save' button on the water intake settings screen to persist their hydration configuration. It carries the parameters source_screen (recording where the user navigated from), target_value (Water target saved, for example 2000ml, 2500ml), container_volume (Container volume saved, for example 250ml, 500ml). The target_value and container_volume together define the user's complete hydration tracking setup. This is marked as a Key Event because it represents the user completing the setup of a daily health habit — hydration tracking. This aligns with the PRD's goal of habit formation through daily micro-actions and supports the 'Healthy Pregnancy' persona. From a business perspective, it answers: How many users complete water intake setup? What are the most common target-container combinations? Do users who set up water tracking show higher daily engagement and retention? Is there a correlation between hydration tracking adoption and other engagement metrics like symptom logging? Synonyms and related concepts include: save water settings, confirm hydration setup, persist water goals, save water configuration. This event fires after target and container selection and is followed by either preg_water_intake_save_success or preg_water_intake_save_failed.</t>
+  </si>
+  <si>
+    <t>This event, preg_water_intake_save_success, is fired when water intake settings are saved successfully. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. It confirms the successful persistence of the user's hydration configuration. When compared with preg_water_intake_save_tap, it helps calculate the save success rate. Synonyms and related concepts include: water settings saved, hydration config confirmed, water setup complete, hydration save success. This event fires after a successful save and the user typically returns to their previous screen.</t>
+  </si>
+  <si>
+    <t>This event, preg_water_intake_save_failed, is fired when water intake settings fail to save due to a network, server, or validation error. It carries the parameters source_screen (recording where the user navigated from), error_type (Type of error, for example network, server, validation), error_message (Error message, for example No internet, Server error). The error_type and error_message provide diagnostic details. This is not a Key Event. From a business perspective, it measures the failure rate of water settings saves and helps identify reliability issues. Users who experience save failures may abandon the feature entirely. Synonyms and related concepts include: water save error, hydration settings failure, water config save failed, hydration persistence error. This event fires instead of preg_water_intake_save_success when the save fails.</t>
+  </si>
+  <si>
+    <t>This event, preg_get_pregnant_sheet_shown, is fired when the 'Get Pregnant Mode' bottom sheet is displayed to the user. This sheet appears when a pregnancy-mode user explores switching to 'trying to conceive' or fertility-tracking mode. The PRD (section 1.1) establishes that pregnancy is 'mutually exclusive with Period,' and the app needs transition flows between modules. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. From a business perspective, it answers: How many pregnancy users see the get-pregnant mode sheet? What triggers this — curiosity, mistaken navigation, or intentional mode exploration? At what pregnancy weeks does this appear, and does it correlate with early pregnancy loss or pre-conception interest? Synonyms and related concepts include: fertility mode prompt, get pregnant sheet, conception mode display, try to conceive sheet, mode switch prompt. This event fires when the user triggers the mode switch and precedes either preg_get_pregnant_sheet_close_tap or preg_get_pregnant_switch_tap.</t>
+  </si>
+  <si>
+    <t>This event, preg_get_pregnant_sheet_close_tap, is fired when the user taps the close button on the 'Get Pregnant Mode' sheet, dismissing it without switching modes. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. It indicates the user decided to remain in pregnancy mode after seeing the sheet. From a business perspective, it helps calculate the dismiss-vs-switch ratio. Synonyms and related concepts include: dismiss fertility sheet, close get pregnant prompt, cancel mode switch, reject fertility mode. This event fires after preg_get_pregnant_sheet_shown.</t>
+  </si>
+  <si>
+    <t>This event, preg_get_pregnant_switch_tap, is fired when the user taps the 'Switch Mode' button on the 'Get Pregnant Mode' sheet, confirming they want to switch from pregnancy tracking to fertility/conception mode. It carries the source_screen parameter (recording where the user navigated from). This is marked as a Key Event because it represents a module-level transition — the user is leaving pregnancy tracking entirely. This is a significant product decision that may indicate pregnancy loss, completed pregnancy, or user preference change. The PRD addresses module transitions under sensitive flows (section 11). From a business perspective, it answers: How many users switch from pregnancy to get-pregnant mode? At what gestational weeks? Is this correlated with pregnancy deletion, or do users switch modes without deleting? Does this represent a positive re-engagement pathway (user wanting to conceive again) or a loss scenario? Synonyms and related concepts include: switch to fertility mode, confirm mode change, leave pregnancy mode, get pregnant mode activated, conception mode switch. This event fires after preg_get_pregnant_sheet_shown and triggers the module transition.</t>
+  </si>
+  <si>
+    <t>This event, preg_track_sheet_shown, is fired when the 'Discover Pregnancy Mode' bottom sheet is displayed to the user. This sheet appears to users exploring the pregnancy tracking module, potentially from a non-pregnancy mode. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. From a business perspective, it measures how many users are presented with the option to enter or explore pregnancy tracking mode. Synonyms and related concepts include: pregnancy mode prompt, discover pregnancy sheet, track pregnancy display, pregnancy mode exploration. This event fires when the user triggers the exploration and precedes preg_track_sheet_close_tap or preg_track_sheet_switch_tap.</t>
+  </si>
+  <si>
+    <t>This event, preg_track_sheet_close_tap, is fired when the user taps the close button on the 'Discover Pregnancy Mode' sheet, dismissing it without switching. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. It indicates the user decided not to enter pregnancy tracking at this time. Synonyms and related concepts include: dismiss pregnancy prompt, close track sheet, cancel pregnancy mode, decline pregnancy tracking. This event fires after preg_track_sheet_shown.</t>
+  </si>
+  <si>
+    <t>This event, preg_track_sheet_switch_tap, is fired when the user taps the 'Switch Mode' button on the 'Discover Pregnancy Mode' sheet, confirming they want to enter pregnancy tracking mode. It carries the source_screen parameter (recording where the user navigated from). This is marked as a Key Event because it represents a new user entering the pregnancy module — a module-level activation event. The PRD describes the pregnancy module as 'mutually exclusive with Period,' so this switch initiates the full pregnancy onboarding journey. From a business perspective, it answers: How many users switch into pregnancy mode? What is the conversion rate from sheet shown to mode switch? What was the user's previous module — period tracking, trying to conceive, or none? This is a top-of-funnel acquisition metric for the pregnancy module. Synonyms and related concepts include: enter pregnancy mode, switch to pregnancy tracking, activate pregnancy module, confirm pregnancy mode, start pregnancy journey. This event fires after preg_track_sheet_shown and initiates the pregnancy onboarding flow.</t>
+  </si>
+  <si>
+    <t>This event, preg_kick_prompt_sheet_shown, is fired when the kick prompt bottom sheet is displayed to the user. This sheet may appear after a kick session completes to provide educational guidance, or when the system detects a session with low kick counts and wants to prompt the user with supportive information. The PRD (section 6.9) requires education around fetal movements and safe triage when reduced movement is reported. It carries the parameters source_screen (recording where the user navigated from), heading (Heading text of the prompt, for example Low kicks detected, Session complete). The heading parameter records the specific heading text shown (e.g., 'Low kicks detected' or 'Session complete'), which helps distinguish between routine session prompts and safety-related prompts. This is not a Key Event. From a business perspective, it answers: How often are kick prompts shown? What is the distribution of prompt types (routine vs. safety-related)? Do users who see safety-related kick prompts take different actions compared to those who see routine prompts? Synonyms and related concepts include: kick guidance prompt, movement education sheet, kick session feedback, fetal movement prompt, kick reminder display. This event fires after preg_kick_counter_session_saved or preg_kick_few_kicks_warning_shown and is followed by preg_kick_prompt_okay_tap.</t>
+  </si>
+  <si>
+    <t>This event, preg_kick_prompt_okay_tap, is fired when the user taps the 'Okay' button on the kick prompt bottom sheet to acknowledge and dismiss it. It carries the source_screen parameter (recording where the user navigated from). This is not a Key Event. It confirms that the user saw and acknowledged the kick prompt content. From a business perspective, it helps measure prompt completion rate and, when paired with preg_kick_prompt_sheet_shown, the time spent reading the prompt content. Synonyms and related concepts include: acknowledge kick prompt, dismiss kick guidance, okay on movement prompt, confirm kick prompt, close kick education. This event fires after preg_kick_prompt_sheet_shown and returns the user to the kick counter or previous screen.</t>
+  </si>
+  <si>
+    <t>This event, preg_symptom_log_screen_shown, is fired when the pregnancy symptom logging screen is displayed to the user. Symptom logging is a P0 core feature (PRD section 6.4) designed to be 'fast, judgement-free, optional notes' with 'severity-based where relevant' using 'chips + sliders.' The PRD sets an acceptance criterion that logging should be 'completed &lt; 15 seconds for common cases.' It carries the parameters source_screen (recording where the user navigated from), week_number (Current pregnancy week, for example 12, 20, 36). The week_number parameter provides gestational context for all symptoms logged in this session, enabling week-by-week symptom pattern analysis. This is not a Key Event (the submission event preg_symptom_log_submitted is the Key Event). From a business perspective, it answers: How many users open the symptom logger daily/weekly? What is the conversion rate from opening the logger to actually submitting symptoms? At what gestational weeks is symptom logging most frequent? What is the primary source_screen — do users arrive from the dashboard quick-log chips, notifications, or the AI assistant? This event is critical for measuring the PRD's activation KPI 'Symptom log completed in first 48 hours' and the engagement KPI 'Symptom logs per week.' All four user personas interact with symptom logging — the 'Anxious Planner' for reassurance, the 'Busy Mum' for quick logging, the 'Symptom Checker' for frequent monitoring, and the 'Healthy Pregnancy' user for routine tracking. Synonyms and related concepts include: symptom logger opened, log symptoms screen, symptom tracking view, pregnancy symptom entry, health log screen, symptom recorder display. This event fires after navigation from the dashboard or other screens and precedes preg_symptom_category_viewed and preg_symptom_chip_tap as the user interacts with symptom options.</t>
+  </si>
+  <si>
+    <t>This event, preg_symptom_category_viewed, is fired when a symptom category section becomes visible on the symptom logging screen. The PRD (section 6.4) specifies a baseline set of symptoms organized by category: physical symptoms (nausea, cramps, back pain, fatigue, headache, dizziness, heartburn, constipation), mood (anxious, low, irritable, calm), sleep quality (1-5 scale), appetite, and sensitive symptoms like discharge/spotting. It carries the parameters source_screen (recording where the user navigated from), category_name (Name of the symptom category, for example symptoms, mood, sleep, appetite). The category_name identifies which category became visible (e.g., symptoms, mood, sleep, appetite). This is not a Key Event. From a business perspective, it answers: Which symptom categories do users scroll through? Are certain categories consistently skipped (not scrolled to), suggesting they could be repositioned or removed? Does category visibility correlate with completion — do users who see all categories complete more thorough logs? Synonyms and related concepts include: category impression, symptom section visible, category scroll into view, symptom group viewed, logging category exposure. This event fires on the symptom logging screen as the user scrolls through categories, preceding preg_symptom_chip_tap for any chips within visible categories.</t>
+  </si>
+  <si>
+    <t>This event, preg_symptom_chip_tap, is fired when the user taps on a symptom chip to select or deselect it on the symptom logging screen. Symptom chips are the primary interaction element for the PRD's 'fast, judgement-free' logging experience (section 6.4). Each chip represents a specific symptom, and tapping toggles its selection state. It carries the parameters source_screen (recording where the user navigated from), symptom_id (Identifier of the symptom, for example nausea, cramps, back_pain, fatigue, headache), category_name (Category the symptom belongs to, for example symptoms, mood), action (Select or deselect, for example select, deselect), position (Position of the chip, for example 0, 1, 2, 3). The symptom_id identifies the specific symptom (e.g., nausea, cramps, back_pain, fatigue, headache), category_name groups it, and is_selected records whether the tap was a selection (true) or deselection (false). This is not a Key Event. From a business perspective, it answers: Which symptoms are most frequently logged across the user base? Which symptoms are most common per trimester or week? Are there symptom combinations that frequently co-occur (e.g., nausea + fatigue in first trimester)? What is the deselection rate — do users frequently toggle symptoms off, suggesting indecision or accidental taps? This data feeds directly into the PRD's personalisation engine (section 7.1-7.3), which uses symptom patterns for 'pattern detection examples' like 'nausea peaks at specific times/day' and 'back pain spikes after activity days.' Synonyms and related concepts include: symptom selected, health chip tap, symptom toggle, log symptom, symptom check/uncheck, symptom selection interaction. This event fires between preg_symptom_log_screen_shown and preg_symptom_log_submitted.</t>
+  </si>
+  <si>
+    <t>This event, preg_symptom_log_submitted, is fired when the user submits their completed symptom log. This is the culmination of the symptom logging flow — the user has selected symptoms, potentially set severity levels, and chosen to save their log. The PRD specifies that after submission, the app should provide a 'Daily summary' and '1 supportive tip personalised by trimester + user pattern.' It carries the parameters source_screen (recording where the user navigated from), symptom_count (Total number of symptoms logged, for example 1, 3, 7), severity_max (Maximum severity logged across symptoms, for example mild, moderate, severe), triage_shown (Whether a safety triage template was triggered, for example true, false), week_number (Current pregnancy week, for example 12, 20, 36). The symptom_count records the total number of symptoms logged, severity_max captures the highest severity across all logged symptoms (which may trigger triage logic), categories_count shows how many different categories the user logged across, and triage_triggered indicates whether the submission activated the safety triage system. This is marked as a Key Event because symptom logging submission is one of the most important engagement and health-tracking events in the pregnancy module. It directly maps to multiple PRD KPIs: 'Symptom log completed in first 48 hours' (activation), 'Symptom logs per week' (engagement), and the safety funnel 'Symptom log submitted → return next day/week' (retention). From a business perspective, it answers: How many symptom logs are submitted daily and weekly? What is the average symptom count per log? What percentage of submissions trigger triage templates? How does logging frequency change across trimesters? Do users who log symptoms regularly have higher retention than those who don't? What severity distribution suggests the user base's health profile? This event is foundational for the PRD's personalisation engine, feeding into the 'Short-term memory: last 14 days symptoms' and 'Long-term: recurring symptoms by trimester/week.' Synonyms and related concepts include: symptom log saved, submit health log, pregnancy symptoms recorded, daily symptom entry completed, health log confirmed, symptom data saved. This event fires after all preg_symptom_chip_tap interactions and may be followed by preg_symptom_triage_shown if triage_triggered=true, or by a return to the dashboard with a personalised tip.</t>
+  </si>
+  <si>
+    <t>This event, preg_symptom_triage_shown, is fired when a safety triage template — a 'when to seek care' informational card — is displayed to the user after symptom logging. This is one of the most safety-critical events in the entire pregnancy module. The PRD (section 6.5) establishes the core rule: 'Femverse must not diagnose. It must provide reassurance where appropriate, monitor and track guidance, and clear seek medical advice triggers.' The triage system uses an 'Alert ladder' from gentle self-care tips through 'Seek urgent care' for clear red-flag patterns. It carries the parameters source_screen (recording where the user navigated from), trigger_symptoms (Symptoms that triggered the triage, for example heavy_bleeding, severe_pain), triage_level (Severity level of the triage, for example self_care, monitor, clinician, urgent), week_number (Current pregnancy week, for example 12, 20, 36). The trigger_symptoms parameter records which specific symptoms or symptom combinations activated the triage (e.g., heavy_bleeding, severe_pain), the triage_level indicates the severity tier of the response shown, and trimester provides gestational context since triage thresholds may differ by trimester. This is marked as a Key Event because triage display is the app's primary safety intervention mechanism. The PRD's safety KPI 'Correct display rate of triage templates for flagged symptoms' directly depends on this event firing accurately and consistently. From a business perspective and safety perspective, it answers: How often are triage templates displayed? Which trigger symptoms are most common? What is the distribution of triage levels — are most gentle tips, or are urgent-care prompts frequent? Does triage display correlate with user satisfaction ('felt supported vs felt scared' safety metric)? Are there symptom combinations that should trigger triage but aren't, or that are triggering unnecessarily? What is the user's behaviour after seeing a triage template — do they return to the app, or does it cause disengagement? This event requires careful monitoring and regular review to ensure the triage system is calibrated correctly. Synonyms and related concepts include: safety alert shown, when to seek care displayed, triage template visible, medical guidance shown, symptom warning displayed, red flag alert, safety intervention. This event fires after preg_symptom_log_submitted when triage_triggered=true. The PRD specifies that triage templates must 'always show disclaimers' and 'always offer next step and support resources.'</t>
+  </si>
+  <si>
+    <t>This event, preg_error_state_shown, is fired when an error state is displayed on any pregnancy module screen, indicating that content failed to load or an operation failed. It carries the parameters source_screen (recording where the user navigated from), error_type (Type of error, for example network, server, timeout, unknown), error_message (Error message displayed, for example No internet connection, Something went wrong). The error_type categorizes the failure (network, server, timeout, unknown), error_message records what was shown to the user, and screen_name identifies which pregnancy screen encountered the error. This is not a Key Event but is critical for reliability monitoring. The PRD (section 12) specifies non-functional requirements including 'dashboard load fast' and 'log under 2 seconds.' Error states represent failures to meet these requirements. From a business perspective, it answers: What is the error rate across the pregnancy module? Which screens experience the most errors? Are errors concentrated on specific device types, OS versions, or network conditions? What is the trend — is reliability improving or degrading? Do error states correlate with churn — are users who encounter errors more likely to stop using the app? Synonyms and related concepts include: error displayed, failure state shown, loading error, content failure, screen error, module error, connectivity failure display. This event fires when content loading fails and may be followed by preg_retry_tap.</t>
+  </si>
+  <si>
+    <t>This event, preg_retry_tap, is fired when the user taps a retry button after encountering an error state on any pregnancy screen. It carries the parameters source_screen (recording where the user navigated from), error_type (Type of the original error, for example network, server, timeout). The error_type records the type of the original error that prompted the retry. This is not a Key Event. From a business perspective, it measures user persistence after errors and answers: What percentage of users who see error states attempt to retry? Does the retry succeed (measured by the absence of a subsequent preg_error_state_shown)? Are there error types where retrying is more or less likely to succeed? How many retries does a user attempt before abandoning? User willingness to retry is a proxy for app value — users who find the pregnancy module valuable will retry; those who don't will leave. Synonyms and related concepts include: retry after error, reload attempt, try again tap, error recovery attempt, refresh tap. This event fires after preg_error_state_shown and is followed by either a successful content load or another error state.</t>
+  </si>
+  <si>
+    <t>This event, preg_toolbar_action_tap, is fired when the user taps an action item in the toolbar on any pregnancy screen. The toolbar provides quick access to common actions across the pregnancy module, such as navigating to settings, calendar, or notifications. It carries the parameters source_screen (recording where the user navigated from), action_id (Identifier of the toolbar action, for example settings, calendar, notifications). The action_id identifies which toolbar action was tapped (e.g., settings, calendar, notifications). This is not a Key Event. From a business perspective, it answers: Which toolbar actions are most used? Is the toolbar an effective navigation mechanism, or are users primarily navigating through other paths? Are there toolbar actions that are rarely used and could be replaced with more popular shortcuts? Synonyms and related concepts include: toolbar click, action bar tap, toolbar navigation, quick action tap, header action click. This event fires from any pregnancy screen and leads to the corresponding destination screen.</t>
+  </si>
+  <si>
+    <t>This event, preg_dashboard_dwell_threshold, is fired when the user exceeds a configurable dwell time threshold on the pregnancy dashboard, indicating engaged browsing rather than a quick glance. Unlike preg_dashboard_screen_exited which fires once on exit with total time_spent, this event fires at specific threshold crossings (e.g., 30 seconds, 60 seconds, 120 seconds), providing real-time engagement signals without waiting for exit. It carries the parameters source_screen (recording where the user navigated from), threshold_seconds (Dwell time threshold crossed, for example 30, 60, 120), week_number (Current pregnancy week, for example 12, 20, 36). The threshold_seconds records which threshold was crossed, and week_number provides gestational context. This is not a Key Event. From a business perspective, it answers: What percentage of dashboard sessions exceed 30 seconds (meaningful engagement) versus 60 seconds (deep browsing) versus 120 seconds (extended session)? Do dwell thresholds vary by trimester or pregnancy week — do users in high-anxiety weeks spend more time on the dashboard? The PRD aims for 'fast today value within 60 seconds,' so this event helps validate whether users are getting value quickly or spending excessive time searching for information. Synonyms and related concepts include: engagement threshold, time on dashboard, dwell time milestone, session depth marker, engaged browsing indicator. This event fires during an active dashboard session and may fire multiple times as successive thresholds are crossed.</t>
+  </si>
+  <si>
+    <t>This event, preg_week_transition_occurred, is fired when the user's pregnancy advances to a new week, detected on app open or dashboard load. This is a system-generated event that marks the natural progression of pregnancy. The PRD (section 6.1) specifies that gestational age is 'computed (weeks + days)' and the 'Week content schedule unlocked' accordingly. Each week transition unlocks new content in the weekly guide system (section 6.3). It carries the parameters source_screen (recording where the user navigated from), previous_week (Previous pregnancy week, for example 11, 19, 35), new_week (New pregnancy week, for example 12, 20, 36), trimester (Current trimester, for example 1, 2, 3), trimester_changed (Whether the trimester changed, for example true, false). The previous_week and new_week track the transition, trimester records the current trimester, and trimester_changed flags whether this week transition also triggered a trimester change (a more significant milestone). This is not a Key Event (preg_trimester_changed is the Key Event for the more significant trimester transitions). From a business perspective, it answers: Are users actively using the app at the time of their week transitions — if users open the app on Monday (weekly anchor day) and see a new week, is this correlated with higher engagement? Does the app correctly detect and display week transitions? Are there week transitions that correlate with engagement drops (suggesting content gaps for specific weeks)? Synonyms and related concepts include: pregnancy week change, new week detected, gestational age advance, week rollover, pregnancy progress update, weekly milestone. This event fires on app open or dashboard load when the system detects the date has advanced past a week boundary. It may be accompanied by preg_trimester_changed if trimester_changed=true.</t>
+  </si>
+  <si>
+    <t>This event, preg_trimester_changed, is fired when the user transitions to a new trimester — a significant pregnancy milestone. Trimester transitions (from trimester 1 to 2 around week 13, and from trimester 2 to 3 around week 28) are major milestones that the PRD uses as a primary personalisation axis. The PRD references trimesters throughout: trimester mapping in setup (section 6.1), trimester display in the dashboard header (section 6.2), trimester-specific content in the weekly guide (section 6.3), trimester checklists (section 6.6), and the personalisation engine's input of 'Gestational age, trimester' (section 7.1). It carries the parameters source_screen (recording where the user navigated from), previous_trimester (Previous trimester, for example 1, 2), new_trimester (New trimester entered, for example 2, 3), week_number (Pregnancy week at transition, for example 13, 28). The previous_trimester and new_trimester record the transition (1→2 or 2→3), and week_number records the exact pregnancy week at which the transition was detected. This is marked as a Key Event because trimester transitions are the most significant milestones in pregnancy tracking and drive major content, personalisation, and feature changes. From a business perspective, it answers: How many users reach each trimester transition? What is the trimester-to-trimester retention rate — do users who enter trimester 2 continue to trimester 3? Is there an engagement pattern around trimester transitions — does engagement spike when new trimester content unlocks? Does the app correctly trigger trimester changes at the right weeks? The PRD's personalisation engine (section 7.2) records trimester changes as 'Important events: trimester change,' confirming their significance for the memory system and recommendation engine. Synonyms and related concepts include: trimester transition, pregnancy milestone, trimester boundary, new trimester entered, trimester progression, major pregnancy milestone. This event fires alongside or after preg_week_transition_occurred when the week transition crosses a trimester boundary. It may trigger new content, checklists, and personalisation updates across the app.</t>
   </si>
 </sst>
 </file>
@@ -2233,7 +2233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2288,46 +2288,42 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2670,21 +2666,21 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="I1" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="33">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="29">
         <v>1</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="22" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="4" t="s">
@@ -2696,10 +2692,10 @@
       <c r="G2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="37" t="s">
+      <c r="I2" t="s">
         <v>567</v>
       </c>
     </row>
@@ -2767,17 +2763,17 @@
       </c>
       <c r="H6" s="24"/>
     </row>
-    <row r="7" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="30">
         <v>2</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="28" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="27" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="9" t="s">
@@ -2789,10 +2785,10 @@
       <c r="G7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="37" t="s">
+      <c r="H7" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" t="s">
         <v>568</v>
       </c>
     </row>
@@ -2828,7 +2824,7 @@
       </c>
       <c r="H9" s="24"/>
     </row>
-    <row r="10" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="12">
         <v>3</v>
       </c>
@@ -2853,21 +2849,21 @@
       <c r="H10" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="37" t="s">
+      <c r="I10" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="30">
         <v>4</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="28" t="s">
         <v>40</v>
       </c>
       <c r="C11" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="27" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="9" t="s">
@@ -2879,10 +2875,10 @@
       <c r="G11" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="37" t="s">
+      <c r="H11" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" t="s">
         <v>570</v>
       </c>
     </row>
@@ -2934,17 +2930,17 @@
       </c>
       <c r="H14" s="24"/>
     </row>
-    <row r="15" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="22">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="25">
         <v>5</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="33" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="14" t="s">
@@ -2956,10 +2952,10 @@
       <c r="G15" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H15" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="37" t="s">
+      <c r="H15" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" t="s">
         <v>571</v>
       </c>
     </row>
@@ -2995,17 +2991,17 @@
       </c>
       <c r="H17" s="24"/>
     </row>
-    <row r="18" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="30">
         <v>6</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="28" t="s">
         <v>53</v>
       </c>
       <c r="C18" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D18" s="27" t="s">
         <v>10</v>
       </c>
       <c r="E18" s="9" t="s">
@@ -3017,10 +3013,10 @@
       <c r="G18" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H18" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="37" t="s">
+      <c r="H18" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" t="s">
         <v>572</v>
       </c>
     </row>
@@ -3056,17 +3052,17 @@
       </c>
       <c r="H20" s="24"/>
     </row>
-    <row r="21" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="22">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="25">
         <v>7</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="33" t="s">
         <v>10</v>
       </c>
       <c r="E21" s="14" t="s">
@@ -3078,10 +3074,10 @@
       <c r="G21" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="37" t="s">
+      <c r="H21" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" t="s">
         <v>573</v>
       </c>
     </row>
@@ -3117,17 +3113,17 @@
       </c>
       <c r="H23" s="24"/>
     </row>
-    <row r="24" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="30">
         <v>8</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="28" t="s">
         <v>64</v>
       </c>
       <c r="C24" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="27" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="9" t="s">
@@ -3139,10 +3135,10 @@
       <c r="G24" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="37" t="s">
+      <c r="H24" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" t="s">
         <v>574</v>
       </c>
     </row>
@@ -3178,17 +3174,17 @@
       </c>
       <c r="H26" s="24"/>
     </row>
-    <row r="27" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="22">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="25">
         <v>9</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" s="33" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="14" t="s">
@@ -3200,10 +3196,10 @@
       <c r="G27" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H27" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="37" t="s">
+      <c r="H27" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" t="s">
         <v>575</v>
       </c>
     </row>
@@ -3239,17 +3235,17 @@
       </c>
       <c r="H29" s="24"/>
     </row>
-    <row r="30" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="30">
         <v>10</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="28" t="s">
         <v>72</v>
       </c>
       <c r="C30" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="D30" s="29" t="s">
+      <c r="D30" s="27" t="s">
         <v>10</v>
       </c>
       <c r="E30" s="9" t="s">
@@ -3261,10 +3257,10 @@
       <c r="G30" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H30" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I30" s="37" t="s">
+      <c r="H30" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" t="s">
         <v>576</v>
       </c>
     </row>
@@ -3300,17 +3296,17 @@
       </c>
       <c r="H32" s="24"/>
     </row>
-    <row r="33" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="22">
-        <v>11</v>
-      </c>
-      <c r="B33" s="25" t="s">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="25">
+        <v>11</v>
+      </c>
+      <c r="B33" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="D33" s="33" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="14" t="s">
@@ -3322,10 +3318,10 @@
       <c r="G33" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H33" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I33" s="37" t="s">
+      <c r="H33" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I33" t="s">
         <v>577</v>
       </c>
     </row>
@@ -3345,17 +3341,17 @@
       </c>
       <c r="H34" s="24"/>
     </row>
-    <row r="35" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="30">
         <v>12</v>
       </c>
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="28" t="s">
         <v>77</v>
       </c>
       <c r="C35" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="D35" s="29" t="s">
+      <c r="D35" s="27" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="9" t="s">
@@ -3367,10 +3363,10 @@
       <c r="G35" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H35" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I35" s="37" t="s">
+      <c r="H35" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I35" t="s">
         <v>578</v>
       </c>
     </row>
@@ -3422,17 +3418,17 @@
       </c>
       <c r="H38" s="24"/>
     </row>
-    <row r="39" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="22">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="25">
         <v>13</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="C39" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="28" t="s">
+      <c r="D39" s="33" t="s">
         <v>10</v>
       </c>
       <c r="E39" s="14" t="s">
@@ -3444,10 +3440,10 @@
       <c r="G39" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H39" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I39" s="37" t="s">
+      <c r="H39" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I39" t="s">
         <v>579</v>
       </c>
     </row>
@@ -3483,17 +3479,17 @@
       </c>
       <c r="H41" s="24"/>
     </row>
-    <row r="42" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="30">
         <v>14</v>
       </c>
-      <c r="B42" s="27" t="s">
+      <c r="B42" s="28" t="s">
         <v>89</v>
       </c>
       <c r="C42" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="D42" s="29" t="s">
+      <c r="D42" s="27" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="9" t="s">
@@ -3505,10 +3501,10 @@
       <c r="G42" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H42" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I42" s="37" t="s">
+      <c r="H42" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I42" t="s">
         <v>580</v>
       </c>
     </row>
@@ -3560,17 +3556,17 @@
       </c>
       <c r="H45" s="24"/>
     </row>
-    <row r="46" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="22">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="25">
         <v>15</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B46" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="C46" s="22" t="s">
+      <c r="C46" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="D46" s="28" t="s">
+      <c r="D46" s="33" t="s">
         <v>10</v>
       </c>
       <c r="E46" s="14" t="s">
@@ -3582,10 +3578,10 @@
       <c r="G46" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H46" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I46" s="37" t="s">
+      <c r="H46" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I46" t="s">
         <v>581</v>
       </c>
     </row>
@@ -3637,17 +3633,17 @@
       </c>
       <c r="H49" s="24"/>
     </row>
-    <row r="50" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="30">
         <v>16</v>
       </c>
-      <c r="B50" s="27" t="s">
+      <c r="B50" s="28" t="s">
         <v>106</v>
       </c>
       <c r="C50" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="D50" s="29" t="s">
+      <c r="D50" s="27" t="s">
         <v>10</v>
       </c>
       <c r="E50" s="9" t="s">
@@ -3659,10 +3655,10 @@
       <c r="G50" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H50" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I50" s="37" t="s">
+      <c r="H50" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I50" t="s">
         <v>582</v>
       </c>
     </row>
@@ -3698,17 +3694,17 @@
       </c>
       <c r="H52" s="24"/>
     </row>
-    <row r="53" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="22">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="25">
         <v>17</v>
       </c>
-      <c r="B53" s="25" t="s">
+      <c r="B53" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="C53" s="22" t="s">
+      <c r="C53" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="D53" s="28" t="s">
+      <c r="D53" s="33" t="s">
         <v>10</v>
       </c>
       <c r="E53" s="14" t="s">
@@ -3720,10 +3716,10 @@
       <c r="G53" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H53" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I53" s="37" t="s">
+      <c r="H53" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I53" t="s">
         <v>583</v>
       </c>
     </row>
@@ -3743,17 +3739,17 @@
       </c>
       <c r="H54" s="24"/>
     </row>
-    <row r="55" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="30">
         <v>18</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="28" t="s">
         <v>115</v>
       </c>
       <c r="C55" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="D55" s="29" t="s">
+      <c r="D55" s="27" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="9" t="s">
@@ -3765,10 +3761,10 @@
       <c r="G55" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H55" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I55" s="37" t="s">
+      <c r="H55" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I55" t="s">
         <v>584</v>
       </c>
     </row>
@@ -3788,17 +3784,17 @@
       </c>
       <c r="H56" s="24"/>
     </row>
-    <row r="57" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="22">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="25">
         <v>19</v>
       </c>
-      <c r="B57" s="25" t="s">
+      <c r="B57" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="C57" s="22" t="s">
+      <c r="C57" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="D57" s="28" t="s">
+      <c r="D57" s="33" t="s">
         <v>10</v>
       </c>
       <c r="E57" s="14" t="s">
@@ -3810,10 +3806,10 @@
       <c r="G57" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H57" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I57" s="37" t="s">
+      <c r="H57" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I57" t="s">
         <v>585</v>
       </c>
     </row>
@@ -3833,17 +3829,17 @@
       </c>
       <c r="H58" s="24"/>
     </row>
-    <row r="59" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="30">
         <v>20</v>
       </c>
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="28" t="s">
         <v>123</v>
       </c>
       <c r="C59" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="D59" s="29" t="s">
+      <c r="D59" s="27" t="s">
         <v>10</v>
       </c>
       <c r="E59" s="9" t="s">
@@ -3855,10 +3851,10 @@
       <c r="G59" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H59" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I59" s="37" t="s">
+      <c r="H59" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I59" t="s">
         <v>586</v>
       </c>
     </row>
@@ -3894,17 +3890,17 @@
       </c>
       <c r="H61" s="24"/>
     </row>
-    <row r="62" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="22">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="25">
         <v>21</v>
       </c>
-      <c r="B62" s="25" t="s">
+      <c r="B62" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="C62" s="22" t="s">
+      <c r="C62" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="D62" s="28" t="s">
+      <c r="D62" s="33" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="14" t="s">
@@ -3916,10 +3912,10 @@
       <c r="G62" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H62" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I62" s="37" t="s">
+      <c r="H62" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I62" t="s">
         <v>587</v>
       </c>
     </row>
@@ -3939,17 +3935,17 @@
       </c>
       <c r="H63" s="24"/>
     </row>
-    <row r="64" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="30">
         <v>22</v>
       </c>
-      <c r="B64" s="27" t="s">
+      <c r="B64" s="28" t="s">
         <v>128</v>
       </c>
       <c r="C64" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="D64" s="29" t="s">
+      <c r="D64" s="27" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="9" t="s">
@@ -3961,10 +3957,10 @@
       <c r="G64" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H64" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I64" s="37" t="s">
+      <c r="H64" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I64" t="s">
         <v>588</v>
       </c>
     </row>
@@ -3984,17 +3980,17 @@
       </c>
       <c r="H65" s="24"/>
     </row>
-    <row r="66" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="22">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="25">
         <v>23</v>
       </c>
-      <c r="B66" s="25" t="s">
+      <c r="B66" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="C66" s="22" t="s">
+      <c r="C66" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="D66" s="28" t="s">
+      <c r="D66" s="33" t="s">
         <v>10</v>
       </c>
       <c r="E66" s="14" t="s">
@@ -4006,10 +4002,10 @@
       <c r="G66" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H66" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I66" s="37" t="s">
+      <c r="H66" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I66" t="s">
         <v>589</v>
       </c>
     </row>
@@ -4029,17 +4025,17 @@
       </c>
       <c r="H67" s="24"/>
     </row>
-    <row r="68" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="30">
         <v>24</v>
       </c>
-      <c r="B68" s="27" t="s">
+      <c r="B68" s="28" t="s">
         <v>136</v>
       </c>
       <c r="C68" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="D68" s="29" t="s">
+      <c r="D68" s="27" t="s">
         <v>10</v>
       </c>
       <c r="E68" s="9" t="s">
@@ -4051,10 +4047,10 @@
       <c r="G68" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H68" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I68" s="37" t="s">
+      <c r="H68" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I68" t="s">
         <v>590</v>
       </c>
     </row>
@@ -4074,7 +4070,7 @@
       </c>
       <c r="H69" s="24"/>
     </row>
-    <row r="70" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A70" s="12">
         <v>25</v>
       </c>
@@ -4099,11 +4095,11 @@
       <c r="H70" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I70" s="37" t="s">
+      <c r="I70" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
         <v>26</v>
       </c>
@@ -4128,21 +4124,21 @@
       <c r="H71" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I71" s="37" t="s">
+      <c r="I71" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="33">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" s="29">
         <v>27</v>
       </c>
-      <c r="B72" s="35" t="s">
+      <c r="B72" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="C72" s="33" t="s">
+      <c r="C72" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="D72" s="34" t="s">
+      <c r="D72" s="22" t="s">
         <v>10</v>
       </c>
       <c r="E72" s="4" t="s">
@@ -4154,10 +4150,10 @@
       <c r="G72" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H72" s="32" t="s">
+      <c r="H72" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="I72" s="37" t="s">
+      <c r="I72" t="s">
         <v>593</v>
       </c>
     </row>
@@ -4177,7 +4173,7 @@
       </c>
       <c r="H73" s="24"/>
     </row>
-    <row r="74" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
         <v>28</v>
       </c>
@@ -4202,11 +4198,11 @@
       <c r="H74" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I74" s="37" t="s">
+      <c r="I74" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A75" s="12">
         <v>29</v>
       </c>
@@ -4231,21 +4227,21 @@
       <c r="H75" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I75" s="37" t="s">
+      <c r="I75" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="30">
         <v>30</v>
       </c>
-      <c r="B76" s="27" t="s">
+      <c r="B76" s="28" t="s">
         <v>154</v>
       </c>
       <c r="C76" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="D76" s="29" t="s">
+      <c r="D76" s="27" t="s">
         <v>10</v>
       </c>
       <c r="E76" s="9" t="s">
@@ -4257,10 +4253,10 @@
       <c r="G76" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="H76" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I76" s="37" t="s">
+      <c r="H76" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I76" t="s">
         <v>596</v>
       </c>
     </row>
@@ -4296,7 +4292,7 @@
       </c>
       <c r="H78" s="24"/>
     </row>
-    <row r="79" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A79" s="12">
         <v>31</v>
       </c>
@@ -4321,21 +4317,21 @@
       <c r="H79" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I79" s="37" t="s">
+      <c r="I79" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A80" s="33">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" s="29">
         <v>32</v>
       </c>
-      <c r="B80" s="35" t="s">
+      <c r="B80" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="C80" s="33" t="s">
+      <c r="C80" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="D80" s="34" t="s">
+      <c r="D80" s="22" t="s">
         <v>165</v>
       </c>
       <c r="E80" s="4" t="s">
@@ -4347,10 +4343,10 @@
       <c r="G80" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="H80" s="32" t="s">
+      <c r="H80" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="I80" s="37" t="s">
+      <c r="I80" t="s">
         <v>598</v>
       </c>
     </row>
@@ -4386,7 +4382,7 @@
       </c>
       <c r="H82" s="24"/>
     </row>
-    <row r="83" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A83" s="12">
         <v>33</v>
       </c>
@@ -4411,11 +4407,11 @@
       <c r="H83" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I83" s="37" t="s">
+      <c r="I83" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A84" s="7">
         <v>34</v>
       </c>
@@ -4440,21 +4436,21 @@
       <c r="H84" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I84" s="37" t="s">
+      <c r="I84" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A85" s="33">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A85" s="29">
         <v>35</v>
       </c>
-      <c r="B85" s="35" t="s">
+      <c r="B85" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="C85" s="33" t="s">
+      <c r="C85" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="D85" s="34" t="s">
+      <c r="D85" s="22" t="s">
         <v>177</v>
       </c>
       <c r="E85" s="4" t="s">
@@ -4466,10 +4462,10 @@
       <c r="G85" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="H85" s="32" t="s">
+      <c r="H85" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="I85" s="37" t="s">
+      <c r="I85" t="s">
         <v>601</v>
       </c>
     </row>
@@ -4505,7 +4501,7 @@
       </c>
       <c r="H87" s="24"/>
     </row>
-    <row r="88" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="7">
         <v>36</v>
       </c>
@@ -4530,21 +4526,21 @@
       <c r="H88" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I88" s="37" t="s">
+      <c r="I88" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A89" s="33">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A89" s="29">
         <v>37</v>
       </c>
-      <c r="B89" s="35" t="s">
+      <c r="B89" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="C89" s="33" t="s">
+      <c r="C89" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="D89" s="34" t="s">
+      <c r="D89" s="22" t="s">
         <v>186</v>
       </c>
       <c r="E89" s="4" t="s">
@@ -4556,10 +4552,10 @@
       <c r="G89" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="H89" s="32" t="s">
+      <c r="H89" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="I89" s="37" t="s">
+      <c r="I89" t="s">
         <v>603</v>
       </c>
     </row>
@@ -4579,17 +4575,17 @@
       </c>
       <c r="H90" s="24"/>
     </row>
-    <row r="91" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="30">
         <v>38</v>
       </c>
-      <c r="B91" s="27" t="s">
+      <c r="B91" s="28" t="s">
         <v>192</v>
       </c>
       <c r="C91" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="D91" s="29" t="s">
+      <c r="D91" s="27" t="s">
         <v>186</v>
       </c>
       <c r="E91" s="9" t="s">
@@ -4601,10 +4597,10 @@
       <c r="G91" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="H91" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I91" s="37" t="s">
+      <c r="H91" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I91" t="s">
         <v>604</v>
       </c>
     </row>
@@ -4624,7 +4620,7 @@
       </c>
       <c r="H92" s="24"/>
     </row>
-    <row r="93" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A93" s="12">
         <v>39</v>
       </c>
@@ -4649,21 +4645,21 @@
       <c r="H93" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I93" s="37" t="s">
+      <c r="I93" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A94" s="33">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A94" s="29">
         <v>40</v>
       </c>
-      <c r="B94" s="35" t="s">
+      <c r="B94" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="C94" s="33" t="s">
+      <c r="C94" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="D94" s="34" t="s">
+      <c r="D94" s="22" t="s">
         <v>199</v>
       </c>
       <c r="E94" s="4" t="s">
@@ -4675,10 +4671,10 @@
       <c r="G94" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="H94" s="32" t="s">
+      <c r="H94" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="I94" s="37" t="s">
+      <c r="I94" t="s">
         <v>606</v>
       </c>
     </row>
@@ -4698,17 +4694,17 @@
       </c>
       <c r="H95" s="24"/>
     </row>
-    <row r="96" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A96" s="22">
+    <row r="96" spans="1:9" ht="24" x14ac:dyDescent="0.3">
+      <c r="A96" s="25">
         <v>41</v>
       </c>
-      <c r="B96" s="25" t="s">
+      <c r="B96" s="32" t="s">
         <v>204</v>
       </c>
-      <c r="C96" s="22" t="s">
+      <c r="C96" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="D96" s="28" t="s">
+      <c r="D96" s="33" t="s">
         <v>206</v>
       </c>
       <c r="E96" s="14" t="s">
@@ -4720,10 +4716,10 @@
       <c r="G96" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="H96" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I96" s="37" t="s">
+      <c r="H96" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I96" t="s">
         <v>607</v>
       </c>
     </row>
@@ -4743,7 +4739,7 @@
       </c>
       <c r="H97" s="24"/>
     </row>
-    <row r="98" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A98" s="7">
         <v>42</v>
       </c>
@@ -4768,11 +4764,11 @@
       <c r="H98" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I98" s="37" t="s">
+      <c r="I98" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A99" s="12">
         <v>43</v>
       </c>
@@ -4797,21 +4793,21 @@
       <c r="H99" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I99" s="37" t="s">
+      <c r="I99" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="30">
         <v>44</v>
       </c>
-      <c r="B100" s="27" t="s">
+      <c r="B100" s="28" t="s">
         <v>212</v>
       </c>
       <c r="C100" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="D100" s="29" t="s">
+      <c r="D100" s="27" t="s">
         <v>206</v>
       </c>
       <c r="E100" s="9" t="s">
@@ -4823,10 +4819,10 @@
       <c r="G100" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H100" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I100" s="37" t="s">
+      <c r="H100" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I100" t="s">
         <v>610</v>
       </c>
     </row>
@@ -4878,7 +4874,7 @@
       </c>
       <c r="H103" s="24"/>
     </row>
-    <row r="104" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A104" s="12">
         <v>45</v>
       </c>
@@ -4903,21 +4899,21 @@
       <c r="H104" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I104" s="37" t="s">
+      <c r="I104" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="30">
         <v>46</v>
       </c>
-      <c r="B105" s="27" t="s">
+      <c r="B105" s="28" t="s">
         <v>221</v>
       </c>
       <c r="C105" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="D105" s="29" t="s">
+      <c r="D105" s="27" t="s">
         <v>206</v>
       </c>
       <c r="E105" s="9" t="s">
@@ -4929,10 +4925,10 @@
       <c r="G105" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H105" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I105" s="37" t="s">
+      <c r="H105" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I105" t="s">
         <v>612</v>
       </c>
     </row>
@@ -4984,17 +4980,17 @@
       </c>
       <c r="H108" s="24"/>
     </row>
-    <row r="109" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A109" s="22">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A109" s="25">
         <v>47</v>
       </c>
-      <c r="B109" s="25" t="s">
+      <c r="B109" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="C109" s="22" t="s">
+      <c r="C109" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="D109" s="28" t="s">
+      <c r="D109" s="33" t="s">
         <v>206</v>
       </c>
       <c r="E109" s="14" t="s">
@@ -5006,10 +5002,10 @@
       <c r="G109" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="H109" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I109" s="37" t="s">
+      <c r="H109" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I109" t="s">
         <v>613</v>
       </c>
     </row>
@@ -5029,17 +5025,17 @@
       </c>
       <c r="H110" s="24"/>
     </row>
-    <row r="111" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="30">
         <v>48</v>
       </c>
-      <c r="B111" s="27" t="s">
+      <c r="B111" s="28" t="s">
         <v>236</v>
       </c>
       <c r="C111" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="D111" s="29" t="s">
+      <c r="D111" s="27" t="s">
         <v>206</v>
       </c>
       <c r="E111" s="9" t="s">
@@ -5051,10 +5047,10 @@
       <c r="G111" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H111" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I111" s="37" t="s">
+      <c r="H111" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I111" t="s">
         <v>614</v>
       </c>
     </row>
@@ -5090,17 +5086,17 @@
       </c>
       <c r="H113" s="24"/>
     </row>
-    <row r="114" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A114" s="22">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A114" s="25">
         <v>49</v>
       </c>
-      <c r="B114" s="25" t="s">
+      <c r="B114" s="32" t="s">
         <v>242</v>
       </c>
-      <c r="C114" s="22" t="s">
+      <c r="C114" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="D114" s="28" t="s">
+      <c r="D114" s="33" t="s">
         <v>206</v>
       </c>
       <c r="E114" s="14" t="s">
@@ -5112,10 +5108,10 @@
       <c r="G114" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="H114" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I114" s="37" t="s">
+      <c r="H114" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I114" t="s">
         <v>615</v>
       </c>
     </row>
@@ -5135,17 +5131,17 @@
       </c>
       <c r="H115" s="24"/>
     </row>
-    <row r="116" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="30">
         <v>50</v>
       </c>
-      <c r="B116" s="27" t="s">
+      <c r="B116" s="28" t="s">
         <v>245</v>
       </c>
       <c r="C116" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="D116" s="29" t="s">
+      <c r="D116" s="27" t="s">
         <v>206</v>
       </c>
       <c r="E116" s="9" t="s">
@@ -5157,10 +5153,10 @@
       <c r="G116" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H116" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I116" s="37" t="s">
+      <c r="H116" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I116" t="s">
         <v>616</v>
       </c>
     </row>
@@ -5196,17 +5192,17 @@
       </c>
       <c r="H118" s="24"/>
     </row>
-    <row r="119" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A119" s="22">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A119" s="25">
         <v>51</v>
       </c>
-      <c r="B119" s="25" t="s">
+      <c r="B119" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="C119" s="22" t="s">
+      <c r="C119" s="25" t="s">
         <v>252</v>
       </c>
-      <c r="D119" s="28" t="s">
+      <c r="D119" s="33" t="s">
         <v>206</v>
       </c>
       <c r="E119" s="14" t="s">
@@ -5218,10 +5214,10 @@
       <c r="G119" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="H119" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I119" s="37" t="s">
+      <c r="H119" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I119" t="s">
         <v>617</v>
       </c>
     </row>
@@ -5241,17 +5237,17 @@
       </c>
       <c r="H120" s="24"/>
     </row>
-    <row r="121" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="30">
         <v>52</v>
       </c>
-      <c r="B121" s="27" t="s">
+      <c r="B121" s="28" t="s">
         <v>256</v>
       </c>
       <c r="C121" s="30" t="s">
         <v>257</v>
       </c>
-      <c r="D121" s="29" t="s">
+      <c r="D121" s="27" t="s">
         <v>206</v>
       </c>
       <c r="E121" s="9" t="s">
@@ -5263,10 +5259,10 @@
       <c r="G121" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H121" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I121" s="37" t="s">
+      <c r="H121" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I121" t="s">
         <v>618</v>
       </c>
     </row>
@@ -5302,7 +5298,7 @@
       </c>
       <c r="H123" s="24"/>
     </row>
-    <row r="124" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="12">
         <v>53</v>
       </c>
@@ -5327,11 +5323,11 @@
       <c r="H124" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I124" s="37" t="s">
+      <c r="I124" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A125" s="7">
         <v>54</v>
       </c>
@@ -5356,11 +5352,11 @@
       <c r="H125" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I125" s="37" t="s">
+      <c r="I125" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A126" s="12">
         <v>55</v>
       </c>
@@ -5385,21 +5381,21 @@
       <c r="H126" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I126" s="37" t="s">
+      <c r="I126" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="30">
         <v>56</v>
       </c>
-      <c r="B127" s="27" t="s">
+      <c r="B127" s="28" t="s">
         <v>271</v>
       </c>
       <c r="C127" s="30" t="s">
         <v>272</v>
       </c>
-      <c r="D127" s="29" t="s">
+      <c r="D127" s="27" t="s">
         <v>266</v>
       </c>
       <c r="E127" s="9" t="s">
@@ -5411,10 +5407,10 @@
       <c r="G127" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="H127" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I127" s="37" t="s">
+      <c r="H127" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I127" t="s">
         <v>622</v>
       </c>
     </row>
@@ -5434,7 +5430,7 @@
       </c>
       <c r="H128" s="24"/>
     </row>
-    <row r="129" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>57</v>
       </c>
@@ -5459,21 +5455,21 @@
       <c r="H129" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I129" s="37" t="s">
+      <c r="I129" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A130" s="30">
         <v>58</v>
       </c>
-      <c r="B130" s="27" t="s">
+      <c r="B130" s="28" t="s">
         <v>275</v>
       </c>
       <c r="C130" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="D130" s="29" t="s">
+      <c r="D130" s="27" t="s">
         <v>277</v>
       </c>
       <c r="E130" s="9" t="s">
@@ -5485,10 +5481,10 @@
       <c r="G130" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="H130" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I130" s="37" t="s">
+      <c r="H130" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I130" t="s">
         <v>624</v>
       </c>
     </row>
@@ -5524,17 +5520,17 @@
       </c>
       <c r="H132" s="24"/>
     </row>
-    <row r="133" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A133" s="22">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A133" s="25">
         <v>59</v>
       </c>
-      <c r="B133" s="25" t="s">
+      <c r="B133" s="32" t="s">
         <v>280</v>
       </c>
-      <c r="C133" s="22" t="s">
+      <c r="C133" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="D133" s="28" t="s">
+      <c r="D133" s="33" t="s">
         <v>277</v>
       </c>
       <c r="E133" s="14" t="s">
@@ -5546,10 +5542,10 @@
       <c r="G133" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="H133" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I133" s="37" t="s">
+      <c r="H133" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I133" t="s">
         <v>625</v>
       </c>
     </row>
@@ -5585,17 +5581,17 @@
       </c>
       <c r="H135" s="24"/>
     </row>
-    <row r="136" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="30">
         <v>60</v>
       </c>
-      <c r="B136" s="27" t="s">
+      <c r="B136" s="28" t="s">
         <v>288</v>
       </c>
       <c r="C136" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="D136" s="29" t="s">
+      <c r="D136" s="27" t="s">
         <v>277</v>
       </c>
       <c r="E136" s="9" t="s">
@@ -5607,10 +5603,10 @@
       <c r="G136" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="H136" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I136" s="37" t="s">
+      <c r="H136" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I136" t="s">
         <v>626</v>
       </c>
     </row>
@@ -5630,17 +5626,17 @@
       </c>
       <c r="H137" s="24"/>
     </row>
-    <row r="138" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A138" s="22">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A138" s="25">
         <v>61</v>
       </c>
-      <c r="B138" s="25" t="s">
+      <c r="B138" s="32" t="s">
         <v>291</v>
       </c>
-      <c r="C138" s="22" t="s">
+      <c r="C138" s="25" t="s">
         <v>292</v>
       </c>
-      <c r="D138" s="28" t="s">
+      <c r="D138" s="33" t="s">
         <v>277</v>
       </c>
       <c r="E138" s="14" t="s">
@@ -5652,10 +5648,10 @@
       <c r="G138" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="H138" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I138" s="37" t="s">
+      <c r="H138" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I138" t="s">
         <v>627</v>
       </c>
     </row>
@@ -5675,17 +5671,17 @@
       </c>
       <c r="H139" s="24"/>
     </row>
-    <row r="140" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="30">
         <v>62</v>
       </c>
-      <c r="B140" s="27" t="s">
+      <c r="B140" s="28" t="s">
         <v>293</v>
       </c>
       <c r="C140" s="30" t="s">
         <v>294</v>
       </c>
-      <c r="D140" s="29" t="s">
+      <c r="D140" s="27" t="s">
         <v>277</v>
       </c>
       <c r="E140" s="9" t="s">
@@ -5697,10 +5693,10 @@
       <c r="G140" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="H140" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I140" s="37" t="s">
+      <c r="H140" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I140" t="s">
         <v>628</v>
       </c>
     </row>
@@ -5752,17 +5748,17 @@
       </c>
       <c r="H143" s="24"/>
     </row>
-    <row r="144" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A144" s="22">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A144" s="25">
         <v>63</v>
       </c>
-      <c r="B144" s="25" t="s">
+      <c r="B144" s="32" t="s">
         <v>300</v>
       </c>
-      <c r="C144" s="22" t="s">
+      <c r="C144" s="25" t="s">
         <v>301</v>
       </c>
-      <c r="D144" s="28" t="s">
+      <c r="D144" s="33" t="s">
         <v>277</v>
       </c>
       <c r="E144" s="14" t="s">
@@ -5774,10 +5770,10 @@
       <c r="G144" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="H144" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I144" s="37" t="s">
+      <c r="H144" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I144" t="s">
         <v>629</v>
       </c>
     </row>
@@ -5813,17 +5809,17 @@
       </c>
       <c r="H146" s="24"/>
     </row>
-    <row r="147" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="30">
         <v>64</v>
       </c>
-      <c r="B147" s="27" t="s">
+      <c r="B147" s="28" t="s">
         <v>302</v>
       </c>
       <c r="C147" s="30" t="s">
         <v>303</v>
       </c>
-      <c r="D147" s="29" t="s">
+      <c r="D147" s="27" t="s">
         <v>277</v>
       </c>
       <c r="E147" s="9" t="s">
@@ -5835,10 +5831,10 @@
       <c r="G147" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="H147" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I147" s="37" t="s">
+      <c r="H147" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I147" t="s">
         <v>630</v>
       </c>
     </row>
@@ -5874,7 +5870,7 @@
       </c>
       <c r="H149" s="24"/>
     </row>
-    <row r="150" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A150" s="12">
         <v>65</v>
       </c>
@@ -5899,21 +5895,21 @@
       <c r="H150" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I150" s="37" t="s">
+      <c r="I150" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="30">
         <v>66</v>
       </c>
-      <c r="B151" s="27" t="s">
+      <c r="B151" s="28" t="s">
         <v>307</v>
       </c>
       <c r="C151" s="30" t="s">
         <v>308</v>
       </c>
-      <c r="D151" s="29" t="s">
+      <c r="D151" s="27" t="s">
         <v>309</v>
       </c>
       <c r="E151" s="9" t="s">
@@ -5925,10 +5921,10 @@
       <c r="G151" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="H151" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I151" s="37" t="s">
+      <c r="H151" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I151" t="s">
         <v>632</v>
       </c>
     </row>
@@ -5948,17 +5944,17 @@
       </c>
       <c r="H152" s="24"/>
     </row>
-    <row r="153" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A153" s="22">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A153" s="25">
         <v>67</v>
       </c>
-      <c r="B153" s="25" t="s">
+      <c r="B153" s="32" t="s">
         <v>312</v>
       </c>
-      <c r="C153" s="22" t="s">
+      <c r="C153" s="25" t="s">
         <v>313</v>
       </c>
-      <c r="D153" s="28" t="s">
+      <c r="D153" s="33" t="s">
         <v>309</v>
       </c>
       <c r="E153" s="14" t="s">
@@ -5970,10 +5966,10 @@
       <c r="G153" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="H153" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I153" s="37" t="s">
+      <c r="H153" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I153" t="s">
         <v>633</v>
       </c>
     </row>
@@ -6009,17 +6005,17 @@
       </c>
       <c r="H155" s="24"/>
     </row>
-    <row r="156" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="30">
         <v>68</v>
       </c>
-      <c r="B156" s="27" t="s">
+      <c r="B156" s="28" t="s">
         <v>318</v>
       </c>
       <c r="C156" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="D156" s="29" t="s">
+      <c r="D156" s="27" t="s">
         <v>309</v>
       </c>
       <c r="E156" s="9" t="s">
@@ -6031,10 +6027,10 @@
       <c r="G156" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="H156" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I156" s="37" t="s">
+      <c r="H156" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I156" t="s">
         <v>634</v>
       </c>
     </row>
@@ -6102,17 +6098,17 @@
       </c>
       <c r="H160" s="24"/>
     </row>
-    <row r="161" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A161" s="22">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A161" s="25">
         <v>69</v>
       </c>
-      <c r="B161" s="25" t="s">
+      <c r="B161" s="32" t="s">
         <v>328</v>
       </c>
-      <c r="C161" s="22" t="s">
+      <c r="C161" s="25" t="s">
         <v>329</v>
       </c>
-      <c r="D161" s="28" t="s">
+      <c r="D161" s="33" t="s">
         <v>309</v>
       </c>
       <c r="E161" s="14" t="s">
@@ -6124,10 +6120,10 @@
       <c r="G161" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="H161" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I161" s="37" t="s">
+      <c r="H161" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I161" t="s">
         <v>635</v>
       </c>
     </row>
@@ -6163,7 +6159,7 @@
       </c>
       <c r="H163" s="24"/>
     </row>
-    <row r="164" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A164" s="7">
         <v>70</v>
       </c>
@@ -6188,21 +6184,21 @@
       <c r="H164" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I164" s="37" t="s">
+      <c r="I164" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A165" s="22">
+    <row r="165" spans="1:9" ht="24" x14ac:dyDescent="0.3">
+      <c r="A165" s="25">
         <v>71</v>
       </c>
-      <c r="B165" s="25" t="s">
+      <c r="B165" s="32" t="s">
         <v>332</v>
       </c>
-      <c r="C165" s="22" t="s">
+      <c r="C165" s="25" t="s">
         <v>333</v>
       </c>
-      <c r="D165" s="28" t="s">
+      <c r="D165" s="33" t="s">
         <v>334</v>
       </c>
       <c r="E165" s="14" t="s">
@@ -6214,10 +6210,10 @@
       <c r="G165" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="H165" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I165" s="37" t="s">
+      <c r="H165" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I165" t="s">
         <v>637</v>
       </c>
     </row>
@@ -6237,17 +6233,17 @@
       </c>
       <c r="H166" s="24"/>
     </row>
-    <row r="167" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A167" s="33">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A167" s="29">
         <v>72</v>
       </c>
-      <c r="B167" s="35" t="s">
+      <c r="B167" s="34" t="s">
         <v>336</v>
       </c>
-      <c r="C167" s="33" t="s">
+      <c r="C167" s="29" t="s">
         <v>337</v>
       </c>
-      <c r="D167" s="34" t="s">
+      <c r="D167" s="22" t="s">
         <v>334</v>
       </c>
       <c r="E167" s="4" t="s">
@@ -6259,10 +6255,10 @@
       <c r="G167" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="H167" s="32" t="s">
+      <c r="H167" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="I167" s="37" t="s">
+      <c r="I167" t="s">
         <v>638</v>
       </c>
     </row>
@@ -6298,17 +6294,17 @@
       </c>
       <c r="H169" s="24"/>
     </row>
-    <row r="170" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A170" s="22">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A170" s="25">
         <v>73</v>
       </c>
-      <c r="B170" s="25" t="s">
+      <c r="B170" s="32" t="s">
         <v>339</v>
       </c>
-      <c r="C170" s="22" t="s">
+      <c r="C170" s="25" t="s">
         <v>340</v>
       </c>
-      <c r="D170" s="28" t="s">
+      <c r="D170" s="33" t="s">
         <v>334</v>
       </c>
       <c r="E170" s="14" t="s">
@@ -6320,10 +6316,10 @@
       <c r="G170" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="H170" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I170" s="37" t="s">
+      <c r="H170" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I170" t="s">
         <v>639</v>
       </c>
     </row>
@@ -6359,17 +6355,17 @@
       </c>
       <c r="H172" s="24"/>
     </row>
-    <row r="173" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A173" s="33">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A173" s="29">
         <v>74</v>
       </c>
-      <c r="B173" s="35" t="s">
+      <c r="B173" s="34" t="s">
         <v>347</v>
       </c>
-      <c r="C173" s="33" t="s">
+      <c r="C173" s="29" t="s">
         <v>348</v>
       </c>
-      <c r="D173" s="34" t="s">
+      <c r="D173" s="22" t="s">
         <v>334</v>
       </c>
       <c r="E173" s="4" t="s">
@@ -6381,10 +6377,10 @@
       <c r="G173" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="H173" s="32" t="s">
+      <c r="H173" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="I173" s="37" t="s">
+      <c r="I173" t="s">
         <v>640</v>
       </c>
     </row>
@@ -6436,7 +6432,7 @@
       </c>
       <c r="H176" s="24"/>
     </row>
-    <row r="177" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="12">
         <v>75</v>
       </c>
@@ -6461,21 +6457,21 @@
       <c r="H177" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I177" s="37" t="s">
+      <c r="I177" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="30">
         <v>76</v>
       </c>
-      <c r="B178" s="27" t="s">
+      <c r="B178" s="28" t="s">
         <v>356</v>
       </c>
       <c r="C178" s="30" t="s">
         <v>357</v>
       </c>
-      <c r="D178" s="29" t="s">
+      <c r="D178" s="27" t="s">
         <v>334</v>
       </c>
       <c r="E178" s="9" t="s">
@@ -6487,10 +6483,10 @@
       <c r="G178" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="H178" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I178" s="37" t="s">
+      <c r="H178" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I178" t="s">
         <v>642</v>
       </c>
     </row>
@@ -6526,7 +6522,7 @@
       </c>
       <c r="H180" s="24"/>
     </row>
-    <row r="181" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A181" s="12">
         <v>77</v>
       </c>
@@ -6551,11 +6547,11 @@
       <c r="H181" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I181" s="37" t="s">
+      <c r="I181" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="7">
         <v>78</v>
       </c>
@@ -6580,21 +6576,21 @@
       <c r="H182" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I182" s="37" t="s">
+      <c r="I182" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A183" s="22">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A183" s="25">
         <v>79</v>
       </c>
-      <c r="B183" s="25" t="s">
+      <c r="B183" s="32" t="s">
         <v>367</v>
       </c>
-      <c r="C183" s="22" t="s">
+      <c r="C183" s="25" t="s">
         <v>368</v>
       </c>
-      <c r="D183" s="28" t="s">
+      <c r="D183" s="33" t="s">
         <v>366</v>
       </c>
       <c r="E183" s="14" t="s">
@@ -6606,10 +6602,10 @@
       <c r="G183" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="H183" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I183" s="37" t="s">
+      <c r="H183" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I183" t="s">
         <v>645</v>
       </c>
     </row>
@@ -6661,7 +6657,7 @@
       </c>
       <c r="H186" s="24"/>
     </row>
-    <row r="187" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A187" s="7">
         <v>80</v>
       </c>
@@ -6686,21 +6682,21 @@
       <c r="H187" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I187" s="37" t="s">
+      <c r="I187" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A188" s="22">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A188" s="25">
         <v>81</v>
       </c>
-      <c r="B188" s="25" t="s">
+      <c r="B188" s="32" t="s">
         <v>372</v>
       </c>
-      <c r="C188" s="22" t="s">
+      <c r="C188" s="25" t="s">
         <v>373</v>
       </c>
-      <c r="D188" s="28" t="s">
+      <c r="D188" s="33" t="s">
         <v>334</v>
       </c>
       <c r="E188" s="14" t="s">
@@ -6712,10 +6708,10 @@
       <c r="G188" s="15" t="s">
         <v>374</v>
       </c>
-      <c r="H188" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I188" s="37" t="s">
+      <c r="H188" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I188" t="s">
         <v>647</v>
       </c>
     </row>
@@ -6751,7 +6747,7 @@
       </c>
       <c r="H190" s="24"/>
     </row>
-    <row r="191" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="7">
         <v>82</v>
       </c>
@@ -6776,11 +6772,11 @@
       <c r="H191" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I191" s="37" t="s">
+      <c r="I191" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A192" s="12">
         <v>83</v>
       </c>
@@ -6805,21 +6801,21 @@
       <c r="H192" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I192" s="37" t="s">
+      <c r="I192" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="30">
         <v>84</v>
       </c>
-      <c r="B193" s="27" t="s">
+      <c r="B193" s="28" t="s">
         <v>384</v>
       </c>
       <c r="C193" s="30" t="s">
         <v>385</v>
       </c>
-      <c r="D193" s="29" t="s">
+      <c r="D193" s="27" t="s">
         <v>380</v>
       </c>
       <c r="E193" s="9" t="s">
@@ -6831,10 +6827,10 @@
       <c r="G193" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="H193" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I193" s="37" t="s">
+      <c r="H193" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I193" t="s">
         <v>650</v>
       </c>
     </row>
@@ -6870,17 +6866,17 @@
       </c>
       <c r="H195" s="24"/>
     </row>
-    <row r="196" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A196" s="22">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A196" s="25">
         <v>85</v>
       </c>
-      <c r="B196" s="25" t="s">
+      <c r="B196" s="32" t="s">
         <v>387</v>
       </c>
-      <c r="C196" s="22" t="s">
+      <c r="C196" s="25" t="s">
         <v>388</v>
       </c>
-      <c r="D196" s="28" t="s">
+      <c r="D196" s="33" t="s">
         <v>380</v>
       </c>
       <c r="E196" s="14" t="s">
@@ -6892,10 +6888,10 @@
       <c r="G196" s="15" t="s">
         <v>380</v>
       </c>
-      <c r="H196" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I196" s="37" t="s">
+      <c r="H196" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I196" t="s">
         <v>651</v>
       </c>
     </row>
@@ -6915,17 +6911,17 @@
       </c>
       <c r="H197" s="24"/>
     </row>
-    <row r="198" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="30">
         <v>86</v>
       </c>
-      <c r="B198" s="27" t="s">
+      <c r="B198" s="28" t="s">
         <v>391</v>
       </c>
       <c r="C198" s="30" t="s">
         <v>392</v>
       </c>
-      <c r="D198" s="29" t="s">
+      <c r="D198" s="27" t="s">
         <v>380</v>
       </c>
       <c r="E198" s="9" t="s">
@@ -6937,10 +6933,10 @@
       <c r="G198" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="H198" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I198" s="37" t="s">
+      <c r="H198" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I198" t="s">
         <v>652</v>
       </c>
     </row>
@@ -6992,17 +6988,17 @@
       </c>
       <c r="H201" s="24"/>
     </row>
-    <row r="202" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A202" s="22">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A202" s="25">
         <v>87</v>
       </c>
-      <c r="B202" s="25" t="s">
+      <c r="B202" s="32" t="s">
         <v>400</v>
       </c>
-      <c r="C202" s="22" t="s">
+      <c r="C202" s="25" t="s">
         <v>401</v>
       </c>
-      <c r="D202" s="28" t="s">
+      <c r="D202" s="33" t="s">
         <v>380</v>
       </c>
       <c r="E202" s="14" t="s">
@@ -7014,10 +7010,10 @@
       <c r="G202" s="15" t="s">
         <v>380</v>
       </c>
-      <c r="H202" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I202" s="37" t="s">
+      <c r="H202" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I202" t="s">
         <v>653</v>
       </c>
     </row>
@@ -7037,17 +7033,17 @@
       </c>
       <c r="H203" s="24"/>
     </row>
-    <row r="204" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A204" s="33">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A204" s="29">
         <v>88</v>
       </c>
-      <c r="B204" s="35" t="s">
+      <c r="B204" s="34" t="s">
         <v>403</v>
       </c>
-      <c r="C204" s="33" t="s">
+      <c r="C204" s="29" t="s">
         <v>404</v>
       </c>
-      <c r="D204" s="34" t="s">
+      <c r="D204" s="22" t="s">
         <v>380</v>
       </c>
       <c r="E204" s="4" t="s">
@@ -7059,10 +7055,10 @@
       <c r="G204" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="H204" s="32" t="s">
+      <c r="H204" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="I204" s="37" t="s">
+      <c r="I204" t="s">
         <v>654</v>
       </c>
     </row>
@@ -7098,17 +7094,17 @@
       </c>
       <c r="H206" s="24"/>
     </row>
-    <row r="207" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A207" s="22">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A207" s="25">
         <v>89</v>
       </c>
-      <c r="B207" s="25" t="s">
+      <c r="B207" s="32" t="s">
         <v>408</v>
       </c>
-      <c r="C207" s="22" t="s">
+      <c r="C207" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="D207" s="28" t="s">
+      <c r="D207" s="33" t="s">
         <v>380</v>
       </c>
       <c r="E207" s="14" t="s">
@@ -7120,10 +7116,10 @@
       <c r="G207" s="15" t="s">
         <v>380</v>
       </c>
-      <c r="H207" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I207" s="37" t="s">
+      <c r="H207" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I207" t="s">
         <v>655</v>
       </c>
     </row>
@@ -7143,17 +7139,17 @@
       </c>
       <c r="H208" s="24"/>
     </row>
-    <row r="209" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="30">
         <v>90</v>
       </c>
-      <c r="B209" s="27" t="s">
+      <c r="B209" s="28" t="s">
         <v>411</v>
       </c>
       <c r="C209" s="30" t="s">
         <v>412</v>
       </c>
-      <c r="D209" s="29" t="s">
+      <c r="D209" s="27" t="s">
         <v>380</v>
       </c>
       <c r="E209" s="9" t="s">
@@ -7165,10 +7161,10 @@
       <c r="G209" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="H209" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I209" s="37" t="s">
+      <c r="H209" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I209" t="s">
         <v>656</v>
       </c>
     </row>
@@ -7204,7 +7200,7 @@
       </c>
       <c r="H211" s="24"/>
     </row>
-    <row r="212" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A212" s="12">
         <v>91</v>
       </c>
@@ -7229,11 +7225,11 @@
       <c r="H212" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I212" s="37" t="s">
+      <c r="I212" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A213" s="7">
         <v>92</v>
       </c>
@@ -7258,21 +7254,21 @@
       <c r="H213" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I213" s="37" t="s">
+      <c r="I213" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A214" s="33">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A214" s="29">
         <v>93</v>
       </c>
-      <c r="B214" s="35" t="s">
+      <c r="B214" s="34" t="s">
         <v>423</v>
       </c>
-      <c r="C214" s="33" t="s">
+      <c r="C214" s="29" t="s">
         <v>424</v>
       </c>
-      <c r="D214" s="34" t="s">
+      <c r="D214" s="22" t="s">
         <v>380</v>
       </c>
       <c r="E214" s="4" t="s">
@@ -7284,10 +7280,10 @@
       <c r="G214" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="H214" s="32" t="s">
+      <c r="H214" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="I214" s="37" t="s">
+      <c r="I214" t="s">
         <v>659</v>
       </c>
     </row>
@@ -7307,7 +7303,7 @@
       </c>
       <c r="H215" s="24"/>
     </row>
-    <row r="216" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A216" s="7">
         <v>94</v>
       </c>
@@ -7332,11 +7328,11 @@
       <c r="H216" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I216" s="37" t="s">
+      <c r="I216" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A217" s="12">
         <v>95</v>
       </c>
@@ -7361,11 +7357,11 @@
       <c r="H217" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I217" s="37" t="s">
+      <c r="I217" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="7">
         <v>96</v>
       </c>
@@ -7390,21 +7386,21 @@
       <c r="H218" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I218" s="37" t="s">
+      <c r="I218" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A219" s="22">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A219" s="25">
         <v>97</v>
       </c>
-      <c r="B219" s="25" t="s">
+      <c r="B219" s="32" t="s">
         <v>434</v>
       </c>
-      <c r="C219" s="22" t="s">
+      <c r="C219" s="25" t="s">
         <v>435</v>
       </c>
-      <c r="D219" s="28" t="s">
+      <c r="D219" s="33" t="s">
         <v>428</v>
       </c>
       <c r="E219" s="14" t="s">
@@ -7416,10 +7412,10 @@
       <c r="G219" s="15" t="s">
         <v>428</v>
       </c>
-      <c r="H219" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I219" s="37" t="s">
+      <c r="H219" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I219" t="s">
         <v>663</v>
       </c>
     </row>
@@ -7439,7 +7435,7 @@
       </c>
       <c r="H220" s="24"/>
     </row>
-    <row r="221" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="7">
         <v>98</v>
       </c>
@@ -7464,21 +7460,21 @@
       <c r="H221" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I221" s="37" t="s">
+      <c r="I221" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A222" s="22">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A222" s="25">
         <v>99</v>
       </c>
-      <c r="B222" s="25" t="s">
+      <c r="B222" s="32" t="s">
         <v>441</v>
       </c>
-      <c r="C222" s="22" t="s">
+      <c r="C222" s="25" t="s">
         <v>442</v>
       </c>
-      <c r="D222" s="28" t="s">
+      <c r="D222" s="33" t="s">
         <v>428</v>
       </c>
       <c r="E222" s="14" t="s">
@@ -7490,10 +7486,10 @@
       <c r="G222" s="15" t="s">
         <v>428</v>
       </c>
-      <c r="H222" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I222" s="37" t="s">
+      <c r="H222" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I222" t="s">
         <v>665</v>
       </c>
     </row>
@@ -7513,17 +7509,17 @@
       </c>
       <c r="H223" s="24"/>
     </row>
-    <row r="224" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A224" s="33">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A224" s="29">
         <v>100</v>
       </c>
-      <c r="B224" s="35" t="s">
+      <c r="B224" s="34" t="s">
         <v>446</v>
       </c>
-      <c r="C224" s="33" t="s">
+      <c r="C224" s="29" t="s">
         <v>447</v>
       </c>
-      <c r="D224" s="34" t="s">
+      <c r="D224" s="22" t="s">
         <v>428</v>
       </c>
       <c r="E224" s="4" t="s">
@@ -7535,10 +7531,10 @@
       <c r="G224" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="H224" s="32" t="s">
+      <c r="H224" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="I224" s="37" t="s">
+      <c r="I224" t="s">
         <v>666</v>
       </c>
     </row>
@@ -7574,7 +7570,7 @@
       </c>
       <c r="H226" s="24"/>
     </row>
-    <row r="227" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="12">
         <v>101</v>
       </c>
@@ -7599,21 +7595,21 @@
       <c r="H227" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I227" s="37" t="s">
+      <c r="I227" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="30">
         <v>102</v>
       </c>
-      <c r="B228" s="27" t="s">
+      <c r="B228" s="28" t="s">
         <v>454</v>
       </c>
       <c r="C228" s="30" t="s">
         <v>455</v>
       </c>
-      <c r="D228" s="29" t="s">
+      <c r="D228" s="27" t="s">
         <v>428</v>
       </c>
       <c r="E228" s="9" t="s">
@@ -7625,10 +7621,10 @@
       <c r="G228" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="H228" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I228" s="37" t="s">
+      <c r="H228" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I228" t="s">
         <v>668</v>
       </c>
     </row>
@@ -7664,7 +7660,7 @@
       </c>
       <c r="H230" s="24"/>
     </row>
-    <row r="231" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A231" s="12">
         <v>103</v>
       </c>
@@ -7689,11 +7685,11 @@
       <c r="H231" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I231" s="37" t="s">
+      <c r="I231" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A232" s="7">
         <v>104</v>
       </c>
@@ -7718,11 +7714,11 @@
       <c r="H232" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I232" s="37" t="s">
+      <c r="I232" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A233" s="2">
         <v>105</v>
       </c>
@@ -7747,11 +7743,11 @@
       <c r="H233" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I233" s="37" t="s">
+      <c r="I233" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A234" s="7">
         <v>106</v>
       </c>
@@ -7776,11 +7772,11 @@
       <c r="H234" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I234" s="37" t="s">
+      <c r="I234" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A235" s="12">
         <v>107</v>
       </c>
@@ -7805,11 +7801,11 @@
       <c r="H235" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I235" s="37" t="s">
+      <c r="I235" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A236" s="2">
         <v>108</v>
       </c>
@@ -7834,21 +7830,21 @@
       <c r="H236" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I236" s="37" t="s">
+      <c r="I236" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A237" s="22">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A237" s="25">
         <v>109</v>
       </c>
-      <c r="B237" s="25" t="s">
+      <c r="B237" s="32" t="s">
         <v>475</v>
       </c>
-      <c r="C237" s="22" t="s">
+      <c r="C237" s="25" t="s">
         <v>476</v>
       </c>
-      <c r="D237" s="28" t="s">
+      <c r="D237" s="33" t="s">
         <v>477</v>
       </c>
       <c r="E237" s="14" t="s">
@@ -7860,10 +7856,10 @@
       <c r="G237" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="H237" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I237" s="37" t="s">
+      <c r="H237" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I237" t="s">
         <v>675</v>
       </c>
     </row>
@@ -7883,7 +7879,7 @@
       </c>
       <c r="H238" s="24"/>
     </row>
-    <row r="239" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A239" s="7">
         <v>110</v>
       </c>
@@ -7908,21 +7904,21 @@
       <c r="H239" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I239" s="37" t="s">
+      <c r="I239" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A240" s="22">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A240" s="25">
         <v>111</v>
       </c>
-      <c r="B240" s="25" t="s">
+      <c r="B240" s="32" t="s">
         <v>483</v>
       </c>
-      <c r="C240" s="22" t="s">
+      <c r="C240" s="25" t="s">
         <v>484</v>
       </c>
-      <c r="D240" s="28" t="s">
+      <c r="D240" s="33" t="s">
         <v>485</v>
       </c>
       <c r="E240" s="14" t="s">
@@ -7934,10 +7930,10 @@
       <c r="G240" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="H240" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I240" s="37" t="s">
+      <c r="H240" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I240" t="s">
         <v>677</v>
       </c>
     </row>
@@ -7957,17 +7953,17 @@
       </c>
       <c r="H241" s="24"/>
     </row>
-    <row r="242" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="30">
         <v>112</v>
       </c>
-      <c r="B242" s="27" t="s">
+      <c r="B242" s="28" t="s">
         <v>486</v>
       </c>
       <c r="C242" s="30" t="s">
         <v>487</v>
       </c>
-      <c r="D242" s="29" t="s">
+      <c r="D242" s="27" t="s">
         <v>485</v>
       </c>
       <c r="E242" s="9" t="s">
@@ -7979,10 +7975,10 @@
       <c r="G242" s="10" t="s">
         <v>485</v>
       </c>
-      <c r="H242" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I242" s="37" t="s">
+      <c r="H242" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I242" t="s">
         <v>678</v>
       </c>
     </row>
@@ -8002,17 +7998,17 @@
       </c>
       <c r="H243" s="24"/>
     </row>
-    <row r="244" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A244" s="22">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A244" s="25">
         <v>113</v>
       </c>
-      <c r="B244" s="25" t="s">
+      <c r="B244" s="32" t="s">
         <v>491</v>
       </c>
-      <c r="C244" s="22" t="s">
+      <c r="C244" s="25" t="s">
         <v>492</v>
       </c>
-      <c r="D244" s="28" t="s">
+      <c r="D244" s="33" t="s">
         <v>485</v>
       </c>
       <c r="E244" s="14" t="s">
@@ -8024,10 +8020,10 @@
       <c r="G244" s="15" t="s">
         <v>485</v>
       </c>
-      <c r="H244" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I244" s="37" t="s">
+      <c r="H244" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I244" t="s">
         <v>679</v>
       </c>
     </row>
@@ -8095,17 +8091,17 @@
       </c>
       <c r="H248" s="24"/>
     </row>
-    <row r="249" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A249" s="33">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A249" s="29">
         <v>114</v>
       </c>
-      <c r="B249" s="35" t="s">
+      <c r="B249" s="34" t="s">
         <v>499</v>
       </c>
-      <c r="C249" s="33" t="s">
+      <c r="C249" s="29" t="s">
         <v>500</v>
       </c>
-      <c r="D249" s="34" t="s">
+      <c r="D249" s="22" t="s">
         <v>485</v>
       </c>
       <c r="E249" s="4" t="s">
@@ -8117,10 +8113,10 @@
       <c r="G249" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="H249" s="32" t="s">
+      <c r="H249" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="I249" s="37" t="s">
+      <c r="I249" t="s">
         <v>680</v>
       </c>
     </row>
@@ -8188,17 +8184,17 @@
       </c>
       <c r="H253" s="24"/>
     </row>
-    <row r="254" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A254" s="33">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A254" s="29">
         <v>115</v>
       </c>
-      <c r="B254" s="35" t="s">
+      <c r="B254" s="34" t="s">
         <v>508</v>
       </c>
-      <c r="C254" s="33" t="s">
+      <c r="C254" s="29" t="s">
         <v>509</v>
       </c>
-      <c r="D254" s="34" t="s">
+      <c r="D254" s="22" t="s">
         <v>485</v>
       </c>
       <c r="E254" s="4" t="s">
@@ -8210,10 +8206,10 @@
       <c r="G254" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="H254" s="32" t="s">
+      <c r="H254" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="I254" s="37" t="s">
+      <c r="I254" t="s">
         <v>681</v>
       </c>
     </row>
@@ -8265,17 +8261,17 @@
       </c>
       <c r="H257" s="24"/>
     </row>
-    <row r="258" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" ht="24" x14ac:dyDescent="0.3">
       <c r="A258" s="30">
         <v>116</v>
       </c>
-      <c r="B258" s="27" t="s">
+      <c r="B258" s="28" t="s">
         <v>516</v>
       </c>
       <c r="C258" s="30" t="s">
         <v>517</v>
       </c>
-      <c r="D258" s="29" t="s">
+      <c r="D258" s="27" t="s">
         <v>10</v>
       </c>
       <c r="E258" s="9" t="s">
@@ -8287,10 +8283,10 @@
       <c r="G258" s="10" t="s">
         <v>519</v>
       </c>
-      <c r="H258" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I258" s="37" t="s">
+      <c r="H258" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I258" t="s">
         <v>682</v>
       </c>
     </row>
@@ -8326,17 +8322,17 @@
       </c>
       <c r="H260" s="24"/>
     </row>
-    <row r="261" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A261" s="22">
+    <row r="261" spans="1:9" ht="24" x14ac:dyDescent="0.3">
+      <c r="A261" s="25">
         <v>117</v>
       </c>
-      <c r="B261" s="25" t="s">
+      <c r="B261" s="32" t="s">
         <v>523</v>
       </c>
-      <c r="C261" s="22" t="s">
+      <c r="C261" s="25" t="s">
         <v>524</v>
       </c>
-      <c r="D261" s="28" t="s">
+      <c r="D261" s="33" t="s">
         <v>10</v>
       </c>
       <c r="E261" s="14" t="s">
@@ -8348,10 +8344,10 @@
       <c r="G261" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="H261" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I261" s="37" t="s">
+      <c r="H261" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I261" t="s">
         <v>683</v>
       </c>
     </row>
@@ -8371,17 +8367,17 @@
       </c>
       <c r="H262" s="24"/>
     </row>
-    <row r="263" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" s="30">
         <v>118</v>
       </c>
-      <c r="B263" s="27" t="s">
+      <c r="B263" s="28" t="s">
         <v>528</v>
       </c>
       <c r="C263" s="30" t="s">
         <v>529</v>
       </c>
-      <c r="D263" s="29" t="s">
+      <c r="D263" s="27" t="s">
         <v>10</v>
       </c>
       <c r="E263" s="9" t="s">
@@ -8393,10 +8389,10 @@
       <c r="G263" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="H263" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I263" s="37" t="s">
+      <c r="H263" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I263" t="s">
         <v>684</v>
       </c>
     </row>
@@ -8416,17 +8412,17 @@
       </c>
       <c r="H264" s="24"/>
     </row>
-    <row r="265" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A265" s="22">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A265" s="25">
         <v>119</v>
       </c>
-      <c r="B265" s="25" t="s">
+      <c r="B265" s="32" t="s">
         <v>534</v>
       </c>
-      <c r="C265" s="22" t="s">
+      <c r="C265" s="25" t="s">
         <v>535</v>
       </c>
-      <c r="D265" s="28" t="s">
+      <c r="D265" s="33" t="s">
         <v>10</v>
       </c>
       <c r="E265" s="14" t="s">
@@ -8438,10 +8434,10 @@
       <c r="G265" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H265" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I265" s="37" t="s">
+      <c r="H265" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I265" t="s">
         <v>685</v>
       </c>
     </row>
@@ -8477,17 +8473,17 @@
       </c>
       <c r="H267" s="24"/>
     </row>
-    <row r="268" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" s="30">
         <v>120</v>
       </c>
-      <c r="B268" s="27" t="s">
+      <c r="B268" s="28" t="s">
         <v>539</v>
       </c>
       <c r="C268" s="30" t="s">
         <v>540</v>
       </c>
-      <c r="D268" s="29" t="s">
+      <c r="D268" s="27" t="s">
         <v>10</v>
       </c>
       <c r="E268" s="9" t="s">
@@ -8499,10 +8495,10 @@
       <c r="G268" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H268" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I268" s="37" t="s">
+      <c r="H268" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="I268" t="s">
         <v>686</v>
       </c>
     </row>
@@ -8570,17 +8566,17 @@
       </c>
       <c r="H272" s="24"/>
     </row>
-    <row r="273" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A273" s="33">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A273" s="29">
         <v>121</v>
       </c>
-      <c r="B273" s="35" t="s">
+      <c r="B273" s="34" t="s">
         <v>547</v>
       </c>
-      <c r="C273" s="33" t="s">
+      <c r="C273" s="29" t="s">
         <v>548</v>
       </c>
-      <c r="D273" s="34" t="s">
+      <c r="D273" s="22" t="s">
         <v>10</v>
       </c>
       <c r="E273" s="4" t="s">
@@ -8592,10 +8588,10 @@
       <c r="G273" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H273" s="32" t="s">
+      <c r="H273" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="I273" s="37" t="s">
+      <c r="I273" t="s">
         <v>687</v>
       </c>
     </row>
@@ -8650,31 +8646,344 @@
   </sheetData>
   <autoFilter ref="A1:H276" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="410">
-    <mergeCell ref="D2:D6"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="H188:H190"/>
-    <mergeCell ref="D35:D38"/>
-    <mergeCell ref="B147:B149"/>
-    <mergeCell ref="D76:D78"/>
-    <mergeCell ref="D147:D149"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="C80:C82"/>
-    <mergeCell ref="H196:H197"/>
-    <mergeCell ref="A244:A248"/>
-    <mergeCell ref="A85:A87"/>
-    <mergeCell ref="C244:C248"/>
-    <mergeCell ref="H114:H115"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D214:D215"/>
-    <mergeCell ref="C119:C120"/>
-    <mergeCell ref="H242:H243"/>
-    <mergeCell ref="B170:B172"/>
-    <mergeCell ref="D170:D172"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="D89:D90"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="D138:D139"/>
+    <mergeCell ref="B263:B264"/>
+    <mergeCell ref="D46:D49"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="B240:B241"/>
+    <mergeCell ref="H153:H155"/>
+    <mergeCell ref="H204:H206"/>
+    <mergeCell ref="H173:H176"/>
+    <mergeCell ref="H100:H103"/>
+    <mergeCell ref="H133:H135"/>
+    <mergeCell ref="H151:H152"/>
+    <mergeCell ref="H85:H87"/>
+    <mergeCell ref="H240:H241"/>
+    <mergeCell ref="D109:D110"/>
+    <mergeCell ref="H202:H203"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="H80:H82"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="A228:A230"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="D64:D65"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="B183:B186"/>
+    <mergeCell ref="B244:B248"/>
+    <mergeCell ref="B178:B180"/>
+    <mergeCell ref="D209:D211"/>
+    <mergeCell ref="D105:D108"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="A183:A186"/>
+    <mergeCell ref="A170:A172"/>
+    <mergeCell ref="C183:C186"/>
+    <mergeCell ref="C170:C172"/>
+    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D222:D223"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="A144:A146"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="C144:C146"/>
+    <mergeCell ref="D273:D276"/>
+    <mergeCell ref="H193:H195"/>
+    <mergeCell ref="C147:C149"/>
+    <mergeCell ref="H263:H264"/>
+    <mergeCell ref="B198:B201"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="A268:A272"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="D224:D226"/>
+    <mergeCell ref="D136:D137"/>
+    <mergeCell ref="D161:D163"/>
+    <mergeCell ref="H249:H253"/>
+    <mergeCell ref="H244:H248"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="B121:B123"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="A254:A257"/>
+    <mergeCell ref="D258:D260"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="A178:A180"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="D207:D208"/>
+    <mergeCell ref="B116:B118"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="C105:C108"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="C136:C137"/>
+    <mergeCell ref="C167:C169"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="A156:A160"/>
+    <mergeCell ref="A165:A166"/>
+    <mergeCell ref="A151:A152"/>
+    <mergeCell ref="B165:B166"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A265:A267"/>
+    <mergeCell ref="A121:A123"/>
+    <mergeCell ref="H111:H113"/>
+    <mergeCell ref="A258:A260"/>
+    <mergeCell ref="C258:C260"/>
+    <mergeCell ref="C214:C215"/>
+    <mergeCell ref="D144:D146"/>
+    <mergeCell ref="C222:C223"/>
+    <mergeCell ref="H183:H186"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="A261:A262"/>
+    <mergeCell ref="A188:A190"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A147:A149"/>
+    <mergeCell ref="A196:A197"/>
+    <mergeCell ref="D167:D169"/>
+    <mergeCell ref="A237:A238"/>
+    <mergeCell ref="C207:C208"/>
+    <mergeCell ref="A214:A215"/>
+    <mergeCell ref="A198:A201"/>
+    <mergeCell ref="C198:C201"/>
+    <mergeCell ref="B237:B238"/>
+    <mergeCell ref="B265:B267"/>
+    <mergeCell ref="D265:D267"/>
+    <mergeCell ref="H11:H14"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="H94:H95"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="B119:B120"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C116:C118"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="D114:D115"/>
+    <mergeCell ref="A119:A120"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="B258:B260"/>
+    <mergeCell ref="D193:D195"/>
+    <mergeCell ref="D242:D243"/>
+    <mergeCell ref="C100:C103"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="C209:C211"/>
+    <mergeCell ref="C196:C197"/>
+    <mergeCell ref="C127:C128"/>
+    <mergeCell ref="H219:H220"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="H228:H230"/>
+    <mergeCell ref="D116:D118"/>
+    <mergeCell ref="D156:D160"/>
+    <mergeCell ref="D130:D132"/>
+    <mergeCell ref="D91:D92"/>
+    <mergeCell ref="H127:H128"/>
+    <mergeCell ref="A273:A276"/>
+    <mergeCell ref="C273:C276"/>
+    <mergeCell ref="H66:H67"/>
+    <mergeCell ref="H237:H238"/>
+    <mergeCell ref="H140:H143"/>
+    <mergeCell ref="H214:H215"/>
+    <mergeCell ref="A193:A195"/>
+    <mergeCell ref="H198:H201"/>
+    <mergeCell ref="H39:H41"/>
+    <mergeCell ref="D204:D206"/>
+    <mergeCell ref="D42:D45"/>
+    <mergeCell ref="B173:B176"/>
+    <mergeCell ref="D173:D176"/>
+    <mergeCell ref="B100:B103"/>
+    <mergeCell ref="D100:D103"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B273:B276"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="H268:H272"/>
+    <mergeCell ref="B105:B108"/>
+    <mergeCell ref="B188:B190"/>
+    <mergeCell ref="D188:D190"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="H265:H267"/>
+    <mergeCell ref="H121:H123"/>
+    <mergeCell ref="B224:B226"/>
+    <mergeCell ref="C237:C238"/>
+    <mergeCell ref="D249:D253"/>
+    <mergeCell ref="B161:B163"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="C151:C152"/>
+    <mergeCell ref="H68:H69"/>
+    <mergeCell ref="C130:C132"/>
+    <mergeCell ref="A224:A226"/>
+    <mergeCell ref="C224:C226"/>
+    <mergeCell ref="A249:A253"/>
+    <mergeCell ref="C249:C253"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="B193:B195"/>
+    <mergeCell ref="C161:C163"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="B156:B160"/>
+    <mergeCell ref="B130:B132"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="D111:D113"/>
+    <mergeCell ref="B153:B155"/>
+    <mergeCell ref="D153:D155"/>
+    <mergeCell ref="H2:H6"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="C153:C155"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="D263:D264"/>
+    <mergeCell ref="B151:B152"/>
+    <mergeCell ref="A105:A108"/>
+    <mergeCell ref="D151:D152"/>
+    <mergeCell ref="D202:D203"/>
+    <mergeCell ref="C173:C176"/>
+    <mergeCell ref="A100:A103"/>
+    <mergeCell ref="D80:D82"/>
+    <mergeCell ref="B167:B169"/>
+    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="C193:C195"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="H144:H146"/>
+    <mergeCell ref="C263:C264"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="H30:H32"/>
+    <mergeCell ref="C204:C206"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="H273:H276"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="B249:B253"/>
+    <mergeCell ref="A207:A208"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="A222:A223"/>
+    <mergeCell ref="D183:D186"/>
+    <mergeCell ref="H261:H262"/>
+    <mergeCell ref="H170:H172"/>
+    <mergeCell ref="H138:H139"/>
+    <mergeCell ref="C202:C203"/>
+    <mergeCell ref="A111:A113"/>
+    <mergeCell ref="C111:C113"/>
+    <mergeCell ref="H76:H78"/>
+    <mergeCell ref="H209:H211"/>
+    <mergeCell ref="H147:H149"/>
+    <mergeCell ref="A167:A169"/>
+    <mergeCell ref="B59:B61"/>
+    <mergeCell ref="D228:D230"/>
+    <mergeCell ref="D59:D61"/>
+    <mergeCell ref="D165:D166"/>
+    <mergeCell ref="B207:B208"/>
+    <mergeCell ref="D240:D241"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C228:C230"/>
+    <mergeCell ref="H89:H90"/>
+    <mergeCell ref="H64:H65"/>
+    <mergeCell ref="C261:C262"/>
+    <mergeCell ref="B133:B135"/>
+    <mergeCell ref="D254:D257"/>
+    <mergeCell ref="D178:D180"/>
+    <mergeCell ref="B209:B211"/>
+    <mergeCell ref="H105:H108"/>
+    <mergeCell ref="C165:C166"/>
+    <mergeCell ref="C85:C87"/>
+    <mergeCell ref="C254:C257"/>
+    <mergeCell ref="H62:H63"/>
+    <mergeCell ref="H167:H169"/>
+    <mergeCell ref="D244:D248"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="D196:D197"/>
+    <mergeCell ref="B127:B128"/>
+    <mergeCell ref="D127:D128"/>
+    <mergeCell ref="H254:H257"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="C156:C160"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="A140:A143"/>
+    <mergeCell ref="C133:C135"/>
+    <mergeCell ref="C140:C143"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D66:D67"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D219:D220"/>
+    <mergeCell ref="H50:H52"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="H35:H38"/>
+    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="H46:H49"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="C188:C190"/>
+    <mergeCell ref="H178:H180"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="A76:A78"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="C268:C272"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="H59:H61"/>
+    <mergeCell ref="A219:A220"/>
+    <mergeCell ref="H224:H226"/>
+    <mergeCell ref="H136:H137"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="H161:H163"/>
+    <mergeCell ref="B228:B230"/>
+    <mergeCell ref="A127:A128"/>
+    <mergeCell ref="B261:B262"/>
+    <mergeCell ref="A133:A135"/>
+    <mergeCell ref="D261:D262"/>
+    <mergeCell ref="D121:D123"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="B222:B223"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="D237:D238"/>
+    <mergeCell ref="B140:B143"/>
+    <mergeCell ref="D133:D135"/>
+    <mergeCell ref="D140:D143"/>
+    <mergeCell ref="A130:A132"/>
+    <mergeCell ref="D198:D201"/>
+    <mergeCell ref="D268:D272"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="H258:H260"/>
+    <mergeCell ref="C178:C180"/>
+    <mergeCell ref="H27:H29"/>
+    <mergeCell ref="C35:C38"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="H207:H208"/>
+    <mergeCell ref="H18:H20"/>
+    <mergeCell ref="H116:H118"/>
+    <mergeCell ref="H222:H223"/>
+    <mergeCell ref="B85:B87"/>
+    <mergeCell ref="D85:D87"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="B254:B257"/>
+    <mergeCell ref="H96:H97"/>
+    <mergeCell ref="A153:A155"/>
+    <mergeCell ref="B55:B56"/>
     <mergeCell ref="B268:B272"/>
     <mergeCell ref="A136:A137"/>
     <mergeCell ref="A263:A264"/>
@@ -8699,367 +9008,54 @@
     <mergeCell ref="A27:A29"/>
     <mergeCell ref="C89:C90"/>
     <mergeCell ref="B219:B220"/>
-    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="A244:A248"/>
+    <mergeCell ref="A85:A87"/>
+    <mergeCell ref="C244:C248"/>
+    <mergeCell ref="H114:H115"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D214:D215"/>
+    <mergeCell ref="C119:C120"/>
+    <mergeCell ref="H242:H243"/>
+    <mergeCell ref="B170:B172"/>
+    <mergeCell ref="D170:D172"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="D89:D90"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="D138:D139"/>
     <mergeCell ref="B242:B243"/>
     <mergeCell ref="A204:A206"/>
     <mergeCell ref="A173:A176"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B46:B49"/>
     <mergeCell ref="B80:B82"/>
     <mergeCell ref="A59:A61"/>
     <mergeCell ref="B144:B146"/>
+    <mergeCell ref="A242:A243"/>
+    <mergeCell ref="C242:C243"/>
+    <mergeCell ref="B204:B206"/>
+    <mergeCell ref="D2:D6"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="H188:H190"/>
+    <mergeCell ref="D35:D38"/>
+    <mergeCell ref="B147:B149"/>
+    <mergeCell ref="D76:D78"/>
+    <mergeCell ref="D147:D149"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="C80:C82"/>
+    <mergeCell ref="H196:H197"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B46:B49"/>
     <mergeCell ref="B30:B32"/>
     <mergeCell ref="B2:B6"/>
-    <mergeCell ref="D268:D272"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="H258:H260"/>
-    <mergeCell ref="C178:C180"/>
-    <mergeCell ref="H27:H29"/>
-    <mergeCell ref="C35:C38"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="H207:H208"/>
-    <mergeCell ref="H18:H20"/>
-    <mergeCell ref="H116:H118"/>
-    <mergeCell ref="H222:H223"/>
-    <mergeCell ref="B85:B87"/>
-    <mergeCell ref="D85:D87"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="H109:H110"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="B254:B257"/>
-    <mergeCell ref="H96:H97"/>
-    <mergeCell ref="A153:A155"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="A242:A243"/>
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="D39:D41"/>
-    <mergeCell ref="C242:C243"/>
-    <mergeCell ref="B204:B206"/>
     <mergeCell ref="D72:D73"/>
     <mergeCell ref="A15:A17"/>
-    <mergeCell ref="C268:C272"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="H59:H61"/>
-    <mergeCell ref="A219:A220"/>
-    <mergeCell ref="H224:H226"/>
-    <mergeCell ref="H136:H137"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="H161:H163"/>
-    <mergeCell ref="B228:B230"/>
-    <mergeCell ref="A127:A128"/>
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="D7:D9"/>
-    <mergeCell ref="B261:B262"/>
-    <mergeCell ref="A133:A135"/>
-    <mergeCell ref="D261:D262"/>
-    <mergeCell ref="D121:D123"/>
     <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="B222:B223"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="D237:D238"/>
-    <mergeCell ref="B140:B143"/>
-    <mergeCell ref="D133:D135"/>
-    <mergeCell ref="D140:D143"/>
     <mergeCell ref="B11:B14"/>
     <mergeCell ref="D11:D14"/>
-    <mergeCell ref="A130:A132"/>
-    <mergeCell ref="D198:D201"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="A140:A143"/>
-    <mergeCell ref="C133:C135"/>
-    <mergeCell ref="C140:C143"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D219:D220"/>
-    <mergeCell ref="H50:H52"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="D240:D241"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C228:C230"/>
-    <mergeCell ref="H89:H90"/>
-    <mergeCell ref="H64:H65"/>
-    <mergeCell ref="C261:C262"/>
-    <mergeCell ref="B133:B135"/>
-    <mergeCell ref="D254:D257"/>
-    <mergeCell ref="D178:D180"/>
-    <mergeCell ref="B209:B211"/>
-    <mergeCell ref="H105:H108"/>
-    <mergeCell ref="C165:C166"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="H35:H38"/>
-    <mergeCell ref="C254:C257"/>
-    <mergeCell ref="H62:H63"/>
-    <mergeCell ref="H167:H169"/>
-    <mergeCell ref="H42:H45"/>
-    <mergeCell ref="H273:H276"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="B249:B253"/>
-    <mergeCell ref="A207:A208"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A116:A118"/>
-    <mergeCell ref="A222:A223"/>
-    <mergeCell ref="D183:D186"/>
-    <mergeCell ref="H261:H262"/>
-    <mergeCell ref="H170:H172"/>
-    <mergeCell ref="H138:H139"/>
-    <mergeCell ref="C202:C203"/>
-    <mergeCell ref="A111:A113"/>
-    <mergeCell ref="C111:C113"/>
-    <mergeCell ref="H76:H78"/>
-    <mergeCell ref="H209:H211"/>
-    <mergeCell ref="H147:H149"/>
-    <mergeCell ref="A167:A169"/>
-    <mergeCell ref="B59:B61"/>
-    <mergeCell ref="D228:D230"/>
-    <mergeCell ref="D59:D61"/>
-    <mergeCell ref="D165:D166"/>
-    <mergeCell ref="B207:B208"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="D244:D248"/>
-    <mergeCell ref="H2:H6"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="C153:C155"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="D263:D264"/>
-    <mergeCell ref="B151:B152"/>
-    <mergeCell ref="A105:A108"/>
-    <mergeCell ref="D151:D152"/>
-    <mergeCell ref="D202:D203"/>
-    <mergeCell ref="C173:C176"/>
-    <mergeCell ref="A100:A103"/>
-    <mergeCell ref="D80:D82"/>
-    <mergeCell ref="B167:B169"/>
-    <mergeCell ref="C59:C61"/>
-    <mergeCell ref="C193:C195"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="H144:H146"/>
-    <mergeCell ref="C263:C264"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="H30:H32"/>
-    <mergeCell ref="C204:C206"/>
-    <mergeCell ref="H265:H267"/>
-    <mergeCell ref="H121:H123"/>
-    <mergeCell ref="B224:B226"/>
-    <mergeCell ref="C237:C238"/>
-    <mergeCell ref="D249:D253"/>
-    <mergeCell ref="B161:B163"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="C151:C152"/>
-    <mergeCell ref="H68:H69"/>
-    <mergeCell ref="C130:C132"/>
-    <mergeCell ref="A224:A226"/>
-    <mergeCell ref="C224:C226"/>
-    <mergeCell ref="A249:A253"/>
-    <mergeCell ref="C249:C253"/>
-    <mergeCell ref="A161:A163"/>
-    <mergeCell ref="B193:B195"/>
-    <mergeCell ref="C161:C163"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="B156:B160"/>
-    <mergeCell ref="B130:B132"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="D111:D113"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="B153:B155"/>
-    <mergeCell ref="D153:D155"/>
-    <mergeCell ref="H46:H49"/>
-    <mergeCell ref="A273:A276"/>
-    <mergeCell ref="C273:C276"/>
-    <mergeCell ref="H66:H67"/>
-    <mergeCell ref="H237:H238"/>
-    <mergeCell ref="H140:H143"/>
-    <mergeCell ref="H214:H215"/>
-    <mergeCell ref="A193:A195"/>
-    <mergeCell ref="H198:H201"/>
-    <mergeCell ref="H39:H41"/>
-    <mergeCell ref="D204:D206"/>
-    <mergeCell ref="D42:D45"/>
-    <mergeCell ref="B173:B176"/>
-    <mergeCell ref="D173:D176"/>
-    <mergeCell ref="B100:B103"/>
-    <mergeCell ref="D100:D103"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B273:B276"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="H268:H272"/>
-    <mergeCell ref="B105:B108"/>
-    <mergeCell ref="B188:B190"/>
-    <mergeCell ref="D188:D190"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="D196:D197"/>
-    <mergeCell ref="B127:B128"/>
-    <mergeCell ref="D127:D128"/>
-    <mergeCell ref="H254:H257"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="C156:C160"/>
-    <mergeCell ref="C188:C190"/>
-    <mergeCell ref="H178:H180"/>
-    <mergeCell ref="B258:B260"/>
-    <mergeCell ref="D193:D195"/>
-    <mergeCell ref="D242:D243"/>
-    <mergeCell ref="C100:C103"/>
-    <mergeCell ref="C76:C78"/>
-    <mergeCell ref="C209:C211"/>
-    <mergeCell ref="C196:C197"/>
-    <mergeCell ref="C127:C128"/>
-    <mergeCell ref="H219:H220"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="H11:H14"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="H94:H95"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="B119:B120"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C116:C118"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="D114:D115"/>
-    <mergeCell ref="A119:A120"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="C42:C45"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="H228:H230"/>
-    <mergeCell ref="D116:D118"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="D156:D160"/>
-    <mergeCell ref="D130:D132"/>
-    <mergeCell ref="A265:A267"/>
-    <mergeCell ref="A121:A123"/>
-    <mergeCell ref="H111:H113"/>
-    <mergeCell ref="A258:A260"/>
-    <mergeCell ref="C258:C260"/>
-    <mergeCell ref="C214:C215"/>
-    <mergeCell ref="D144:D146"/>
-    <mergeCell ref="C222:C223"/>
-    <mergeCell ref="H183:H186"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="A261:A262"/>
-    <mergeCell ref="A188:A190"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="A76:A78"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="A147:A149"/>
-    <mergeCell ref="A196:A197"/>
-    <mergeCell ref="D167:D169"/>
-    <mergeCell ref="A237:A238"/>
-    <mergeCell ref="C207:C208"/>
-    <mergeCell ref="D91:D92"/>
-    <mergeCell ref="A214:A215"/>
-    <mergeCell ref="A198:A201"/>
-    <mergeCell ref="C198:C201"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="C105:C108"/>
-    <mergeCell ref="A109:A110"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="C136:C137"/>
-    <mergeCell ref="C167:C169"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="B237:B238"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="A156:A160"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="D273:D276"/>
-    <mergeCell ref="H193:H195"/>
-    <mergeCell ref="C147:C149"/>
-    <mergeCell ref="H263:H264"/>
-    <mergeCell ref="B198:B201"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="A268:A272"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="D224:D226"/>
-    <mergeCell ref="D136:D137"/>
-    <mergeCell ref="D161:D163"/>
-    <mergeCell ref="H249:H253"/>
-    <mergeCell ref="H244:H248"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="B121:B123"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="A254:A257"/>
-    <mergeCell ref="D258:D260"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="A178:A180"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="D207:D208"/>
-    <mergeCell ref="B116:B118"/>
-    <mergeCell ref="B265:B267"/>
-    <mergeCell ref="D265:D267"/>
-    <mergeCell ref="A151:A152"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="A228:A230"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="B183:B186"/>
-    <mergeCell ref="B244:B248"/>
-    <mergeCell ref="B178:B180"/>
-    <mergeCell ref="D209:D211"/>
-    <mergeCell ref="D105:D108"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="A183:A186"/>
-    <mergeCell ref="A170:A172"/>
-    <mergeCell ref="C183:C186"/>
-    <mergeCell ref="C170:C172"/>
-    <mergeCell ref="A89:A90"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="D222:D223"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="A144:A146"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="C144:C146"/>
-    <mergeCell ref="B165:B166"/>
-    <mergeCell ref="H127:H128"/>
-    <mergeCell ref="B263:B264"/>
-    <mergeCell ref="D46:D49"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="B240:B241"/>
-    <mergeCell ref="H153:H155"/>
-    <mergeCell ref="H204:H206"/>
-    <mergeCell ref="H173:H176"/>
-    <mergeCell ref="H100:H103"/>
-    <mergeCell ref="H133:H135"/>
-    <mergeCell ref="H151:H152"/>
-    <mergeCell ref="H85:H87"/>
-    <mergeCell ref="H240:H241"/>
-    <mergeCell ref="D109:D110"/>
-    <mergeCell ref="H202:H203"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="H80:H82"/>
-    <mergeCell ref="A66:A67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
